--- a/Financial Analysis/SOFI.xlsx
+++ b/Financial Analysis/SOFI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD320D3-5B89-4D57-8FA2-1E54B0B9B66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CB1D60-14B1-48AB-8607-53BF14EDB4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{42D26EF4-2D58-4793-8C51-B0C7F6F93649}"/>
   </bookViews>
@@ -744,14 +744,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>12.7</v>
+        <v>13.43</v>
       </c>
       <c r="E3" s="3">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
         <v>45874</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>13944.599999999999</v>
+        <v>14746.14</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -816,7 +816,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>12121.699999999997</v>
+        <v>12923.239999999998</v>
       </c>
     </row>
   </sheetData>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AN28" s="4">
         <f>Main!D3</f>
-        <v>12.7</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="29" spans="2:152" x14ac:dyDescent="0.3">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AN29" s="10">
         <f>AN27/AN28-1</f>
-        <v>-0.32894234972067471</v>
+        <v>-0.36541830539483011</v>
       </c>
     </row>
     <row r="30" spans="2:152" x14ac:dyDescent="0.3">

--- a/Financial Analysis/SOFI.xlsx
+++ b/Financial Analysis/SOFI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CB1D60-14B1-48AB-8607-53BF14EDB4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B5EE6F-17AC-493A-B50D-0FF5EE8F0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{42D26EF4-2D58-4793-8C51-B0C7F6F93649}"/>
   </bookViews>
@@ -217,10 +217,10 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Q125 8K</t>
-  </si>
-  <si>
-    <t>Overvalued</t>
+    <t>Q225 8K</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -320,14 +320,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -344,7 +344,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10081260" y="7620"/>
+          <a:off x="10683240" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -744,17 +744,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>13.43</v>
+        <v>24.38</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45867</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45867</v>
       </c>
       <c r="G3" s="3">
-        <v>45874</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -762,7 +762,8 @@
         <v>1</v>
       </c>
       <c r="D4" s="5">
-        <v>1098</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>63</v>
@@ -774,7 +775,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>14746.14</v>
+        <v>26988.66</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -816,7 +817,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>12923.239999999998</v>
+        <v>25165.759999999998</v>
       </c>
     </row>
   </sheetData>
@@ -832,7 +833,7 @@
   <cols>
     <col min="2" max="2" width="22.109375" customWidth="1"/>
     <col min="39" max="39" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:36" x14ac:dyDescent="0.3">
@@ -980,16 +981,15 @@
         <v>763.8</v>
       </c>
       <c r="P3" s="5">
-        <f>L3*1.15</f>
-        <v>775.79</v>
+        <v>792.4</v>
       </c>
       <c r="Q3" s="5">
-        <f>M3*1.12</f>
-        <v>810.20800000000008</v>
+        <f>M3*1.14</f>
+        <v>824.67599999999993</v>
       </c>
       <c r="R3" s="5">
-        <f>N3*1.11</f>
-        <v>825.72900000000004</v>
+        <f>N3*1.12</f>
+        <v>833.16800000000001</v>
       </c>
       <c r="T3" s="5">
         <v>608.20000000000005</v>
@@ -1014,47 +1014,47 @@
       </c>
       <c r="Z3" s="5">
         <f>SUM(O3:R3)</f>
-        <v>3175.527</v>
+        <v>3214.0439999999999</v>
       </c>
       <c r="AA3" s="5">
         <f>Z3*1.09</f>
-        <v>3461.3244300000001</v>
+        <v>3503.3079600000001</v>
       </c>
       <c r="AB3" s="5">
         <f>AA3*1.06</f>
-        <v>3669.0038958000005</v>
+        <v>3713.5064376000005</v>
       </c>
       <c r="AC3" s="5">
         <f>AB3*1.04</f>
-        <v>3815.7640516320007</v>
+        <v>3862.0466951040007</v>
       </c>
       <c r="AD3" s="5">
         <f>AC3*1.03</f>
-        <v>3930.2369731809608</v>
+        <v>3977.9080959571206</v>
       </c>
       <c r="AE3" s="5">
         <f>AD3*1.02</f>
-        <v>4008.8417126445802</v>
+        <v>4057.4662578762632</v>
       </c>
       <c r="AF3" s="5">
         <f>AE3*1.01</f>
-        <v>4048.9301297710258</v>
+        <v>4098.040920455026</v>
       </c>
       <c r="AG3" s="5">
         <f t="shared" ref="AG3:AJ3" si="0">AF3*1.01</f>
-        <v>4089.4194310687362</v>
+        <v>4139.0213296595766</v>
       </c>
       <c r="AH3" s="5">
         <f t="shared" si="0"/>
-        <v>4130.3136253794237</v>
+        <v>4180.4115429561725</v>
       </c>
       <c r="AI3" s="5">
         <f t="shared" si="0"/>
-        <v>4171.6167616332177</v>
+        <v>4222.2156583857341</v>
       </c>
       <c r="AJ3" s="5">
         <f t="shared" si="0"/>
-        <v>4213.33292924955</v>
+        <v>4264.4378149695913</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
@@ -1101,16 +1101,15 @@
         <v>265.10000000000002</v>
       </c>
       <c r="P4" s="5">
-        <f t="shared" ref="P4:R4" si="1">P3-P5</f>
-        <v>287.04229999999995</v>
+        <v>274.60000000000002</v>
       </c>
       <c r="Q4" s="5">
-        <f t="shared" si="1"/>
-        <v>299.77696000000003</v>
+        <f t="shared" ref="P4:R4" si="1">Q3-Q5</f>
+        <v>288.63659999999993</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" si="1"/>
-        <v>305.51972999999998</v>
+        <v>291.60879999999997</v>
       </c>
       <c r="T4" s="5">
         <v>278.39999999999998</v>
@@ -1135,47 +1134,47 @@
       </c>
       <c r="Z4" s="5">
         <f>SUM(O4:R4)</f>
-        <v>1157.4389900000001</v>
+        <v>1119.9454000000001</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" ref="AA4:AJ4" si="2">AA3-AA5</f>
-        <v>1280.6900390999999</v>
+        <v>1226.1577859999998</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="2"/>
-        <v>1357.5314414460004</v>
+        <v>1299.7272531600001</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" si="2"/>
-        <v>1411.8326991038402</v>
+        <v>1351.7163432864004</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="2"/>
-        <v>1454.1876800769555</v>
+        <v>1392.2678335849923</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="2"/>
-        <v>1483.2714336784948</v>
+        <v>1420.1131902566922</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" si="2"/>
-        <v>1498.1041480152794</v>
+        <v>1434.3143221592591</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="2"/>
-        <v>1513.0851894954326</v>
+        <v>1448.6574653808516</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="2"/>
-        <v>1528.2160413903866</v>
+        <v>1463.1440400346601</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="2"/>
-        <v>1543.4982018042906</v>
+        <v>1477.775480435007</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="2"/>
-        <v>1558.9331838223334</v>
+        <v>1492.553235239357</v>
       </c>
     </row>
     <row r="5" spans="2:36" x14ac:dyDescent="0.3">
@@ -1183,7 +1182,7 @@
         <v>37</v>
       </c>
       <c r="C5" s="5">
-        <f t="shared" ref="C5:O5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:P5" si="3">C3-C4</f>
         <v>94.9</v>
       </c>
       <c r="D5" s="5">
@@ -1235,84 +1234,84 @@
         <v>498.69999999999993</v>
       </c>
       <c r="P5" s="5">
-        <f>P3*0.63</f>
-        <v>488.74770000000001</v>
+        <f t="shared" si="3"/>
+        <v>517.79999999999995</v>
       </c>
       <c r="Q5" s="5">
-        <f t="shared" ref="Q5:R5" si="4">Q3*0.63</f>
-        <v>510.43104000000005</v>
+        <f>Q3*0.65</f>
+        <v>536.0394</v>
       </c>
       <c r="R5" s="5">
+        <f>R3*0.65</f>
+        <v>541.55920000000003</v>
+      </c>
+      <c r="T5" s="5">
+        <f t="shared" ref="T5:Y5" si="4">T3-T4</f>
+        <v>329.80000000000007</v>
+      </c>
+      <c r="U5" s="5">
         <f t="shared" si="4"/>
-        <v>520.20927000000006</v>
-      </c>
-      <c r="T5" s="5">
-        <f t="shared" ref="T5:Y5" si="5">T3-T4</f>
-        <v>329.80000000000007</v>
-      </c>
-      <c r="U5" s="5">
-        <f t="shared" si="5"/>
         <v>177.9</v>
       </c>
       <c r="V5" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>252.2</v>
       </c>
       <c r="W5" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>584</v>
       </c>
       <c r="X5" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1261.7000000000003</v>
       </c>
       <c r="Y5" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1716.4</v>
       </c>
       <c r="Z5" s="5">
         <f>SUM(O5:R5)</f>
-        <v>2018.0880100000002</v>
+        <v>2094.0985999999998</v>
       </c>
       <c r="AA5" s="5">
-        <f>AA3*0.63</f>
-        <v>2180.6343909000002</v>
+        <f>AA3*0.65</f>
+        <v>2277.1501740000003</v>
       </c>
       <c r="AB5" s="5">
-        <f t="shared" ref="AB5:AJ5" si="6">AB3*0.63</f>
-        <v>2311.4724543540001</v>
+        <f t="shared" ref="AB5:AJ5" si="5">AB3*0.65</f>
+        <v>2413.7791844400003</v>
       </c>
       <c r="AC5" s="5">
-        <f t="shared" si="6"/>
-        <v>2403.9313525281605</v>
+        <f t="shared" si="5"/>
+        <v>2510.3303518176003</v>
       </c>
       <c r="AD5" s="5">
-        <f t="shared" si="6"/>
-        <v>2476.0492931040053</v>
+        <f t="shared" si="5"/>
+        <v>2585.6402623721283</v>
       </c>
       <c r="AE5" s="5">
-        <f t="shared" si="6"/>
-        <v>2525.5702789660854</v>
+        <f t="shared" si="5"/>
+        <v>2637.353067619571</v>
       </c>
       <c r="AF5" s="5">
-        <f t="shared" si="6"/>
-        <v>2550.8259817557464</v>
+        <f t="shared" si="5"/>
+        <v>2663.726598295767</v>
       </c>
       <c r="AG5" s="5">
-        <f t="shared" si="6"/>
-        <v>2576.3342415733036</v>
+        <f t="shared" si="5"/>
+        <v>2690.363864278725</v>
       </c>
       <c r="AH5" s="5">
-        <f t="shared" si="6"/>
-        <v>2602.097583989037</v>
+        <f t="shared" si="5"/>
+        <v>2717.2675029215125</v>
       </c>
       <c r="AI5" s="5">
-        <f t="shared" si="6"/>
-        <v>2628.1185598289271</v>
+        <f t="shared" si="5"/>
+        <v>2744.440177950727</v>
       </c>
       <c r="AJ5" s="5">
-        <f t="shared" si="6"/>
-        <v>2654.3997454272167</v>
+        <f t="shared" si="5"/>
+        <v>2771.8845797302342</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
@@ -1359,16 +1358,15 @@
         <v>273</v>
       </c>
       <c r="P6" s="5">
-        <f>L6*1.5</f>
-        <v>279</v>
+        <v>337.1</v>
       </c>
       <c r="Q6" s="5">
-        <f>M6*1.08</f>
-        <v>287.38800000000003</v>
+        <f>M6*1.35</f>
+        <v>359.23500000000007</v>
       </c>
       <c r="R6" s="5">
-        <f t="shared" ref="R6" si="7">N6*1.15</f>
-        <v>303.59999999999997</v>
+        <f>N6*1.45</f>
+        <v>382.8</v>
       </c>
       <c r="T6" s="5">
         <v>112.8</v>
@@ -1393,47 +1391,47 @@
       </c>
       <c r="Z6" s="5">
         <f>SUM(O6:R6)</f>
-        <v>1142.9880000000001</v>
+        <v>1352.135</v>
       </c>
       <c r="AA6" s="5">
-        <f>Z6*1.09</f>
-        <v>1245.8569200000002</v>
+        <f>Z6*1.22</f>
+        <v>1649.6046999999999</v>
       </c>
       <c r="AB6" s="5">
-        <f>AA6*1.07</f>
-        <v>1333.0669044000003</v>
+        <f>AA6*1.1</f>
+        <v>1814.5651700000001</v>
       </c>
       <c r="AC6" s="5">
-        <f>AB6*1.05</f>
-        <v>1399.7202496200005</v>
+        <f>AB6*1.07</f>
+        <v>1941.5847319000002</v>
       </c>
       <c r="AD6" s="5">
         <f>AC6*1.04</f>
-        <v>1455.7090596048006</v>
+        <v>2019.2481211760003</v>
       </c>
       <c r="AE6" s="5">
         <f>AD6*1.03</f>
-        <v>1499.3803313929448</v>
+        <v>2079.8255648112804</v>
       </c>
       <c r="AF6" s="5">
         <f>AE6*1.02</f>
-        <v>1529.3679380208036</v>
+        <v>2121.4220761075062</v>
       </c>
       <c r="AG6" s="5">
-        <f t="shared" ref="AG6:AJ6" si="8">AF6*1.02</f>
-        <v>1559.9552967812197</v>
+        <f t="shared" ref="AG6:AJ6" si="6">AF6*1.02</f>
+        <v>2163.8505176296562</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" si="8"/>
-        <v>1591.1544027168441</v>
+        <f t="shared" si="6"/>
+        <v>2207.1275279822494</v>
       </c>
       <c r="AI6" s="5">
-        <f t="shared" si="8"/>
-        <v>1622.977490771181</v>
+        <f t="shared" si="6"/>
+        <v>2251.2700785418942</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" si="8"/>
-        <v>1655.4370405866046</v>
+        <f t="shared" si="6"/>
+        <v>2296.2954801127321</v>
       </c>
     </row>
     <row r="7" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1441,136 +1439,136 @@
         <v>26</v>
       </c>
       <c r="C7" s="8">
-        <f t="shared" ref="C7:L7" si="9">C3+C6</f>
+        <f t="shared" ref="C7:L7" si="7">C3+C6</f>
         <v>353.8</v>
       </c>
       <c r="D7" s="8">
+        <f t="shared" si="7"/>
+        <v>389.2</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="7"/>
+        <v>464.1</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="7"/>
+        <v>555.5</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="7"/>
+        <v>607.70000000000005</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="7"/>
+        <v>676.9</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="7"/>
+        <v>756.5</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="7"/>
+        <v>871</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="7"/>
+        <v>908.2</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" si="7"/>
+        <v>860.6</v>
+      </c>
+      <c r="M7" s="8">
+        <f t="shared" ref="M7:N7" si="8">M3+M6</f>
+        <v>989.5</v>
+      </c>
+      <c r="N7" s="8">
+        <f t="shared" si="8"/>
+        <v>1007.9</v>
+      </c>
+      <c r="O7" s="8">
+        <f t="shared" ref="O7:R7" si="9">O3+O6</f>
+        <v>1036.8</v>
+      </c>
+      <c r="P7" s="8">
         <f t="shared" si="9"/>
-        <v>389.2</v>
-      </c>
-      <c r="E7" s="8">
+        <v>1129.5</v>
+      </c>
+      <c r="Q7" s="8">
         <f t="shared" si="9"/>
-        <v>464.1</v>
-      </c>
-      <c r="F7" s="8">
+        <v>1183.9110000000001</v>
+      </c>
+      <c r="R7" s="8">
         <f t="shared" si="9"/>
-        <v>555.5</v>
-      </c>
-      <c r="G7" s="8">
-        <f t="shared" si="9"/>
-        <v>607.70000000000005</v>
-      </c>
-      <c r="H7" s="8">
-        <f t="shared" si="9"/>
-        <v>676.9</v>
-      </c>
-      <c r="I7" s="8">
-        <f t="shared" si="9"/>
-        <v>756.5</v>
-      </c>
-      <c r="J7" s="8">
-        <f t="shared" si="9"/>
-        <v>871</v>
-      </c>
-      <c r="K7" s="8">
-        <f t="shared" si="9"/>
-        <v>908.2</v>
-      </c>
-      <c r="L7" s="8">
-        <f t="shared" si="9"/>
-        <v>860.6</v>
-      </c>
-      <c r="M7" s="8">
-        <f t="shared" ref="M7:N7" si="10">M3+M6</f>
-        <v>989.5</v>
-      </c>
-      <c r="N7" s="8">
+        <v>1215.9680000000001</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" ref="T7:Y7" si="10">T3+T6</f>
+        <v>721</v>
+      </c>
+      <c r="U7" s="8">
         <f t="shared" si="10"/>
-        <v>1007.9</v>
-      </c>
-      <c r="O7" s="8">
-        <f t="shared" ref="O7:R7" si="11">O3+O6</f>
-        <v>1036.8</v>
-      </c>
-      <c r="P7" s="8">
+        <v>751.1</v>
+      </c>
+      <c r="V7" s="8">
+        <f t="shared" si="10"/>
+        <v>1087.5999999999999</v>
+      </c>
+      <c r="W7" s="8">
+        <f t="shared" si="10"/>
+        <v>1762.6</v>
+      </c>
+      <c r="X7" s="8">
+        <f t="shared" si="10"/>
+        <v>2912.1000000000004</v>
+      </c>
+      <c r="Y7" s="8">
+        <f t="shared" si="10"/>
+        <v>3766.2000000000003</v>
+      </c>
+      <c r="Z7" s="8">
+        <f t="shared" ref="Z7:AJ7" si="11">Z3+Z6</f>
+        <v>4566.1790000000001</v>
+      </c>
+      <c r="AA7" s="8">
         <f t="shared" si="11"/>
-        <v>1054.79</v>
-      </c>
-      <c r="Q7" s="8">
+        <v>5152.91266</v>
+      </c>
+      <c r="AB7" s="8">
         <f t="shared" si="11"/>
-        <v>1097.596</v>
-      </c>
-      <c r="R7" s="8">
+        <v>5528.0716076000008</v>
+      </c>
+      <c r="AC7" s="8">
         <f t="shared" si="11"/>
-        <v>1129.329</v>
-      </c>
-      <c r="T7" s="8">
-        <f t="shared" ref="T7:Y7" si="12">T3+T6</f>
-        <v>721</v>
-      </c>
-      <c r="U7" s="8">
-        <f t="shared" si="12"/>
-        <v>751.1</v>
-      </c>
-      <c r="V7" s="8">
-        <f t="shared" si="12"/>
-        <v>1087.5999999999999</v>
-      </c>
-      <c r="W7" s="8">
-        <f t="shared" si="12"/>
-        <v>1762.6</v>
-      </c>
-      <c r="X7" s="8">
-        <f t="shared" si="12"/>
-        <v>2912.1000000000004</v>
-      </c>
-      <c r="Y7" s="8">
-        <f t="shared" si="12"/>
-        <v>3766.2000000000003</v>
-      </c>
-      <c r="Z7" s="8">
-        <f t="shared" ref="Z7:AJ7" si="13">Z3+Z6</f>
-        <v>4318.5150000000003</v>
-      </c>
-      <c r="AA7" s="8">
-        <f t="shared" si="13"/>
-        <v>4707.1813500000007</v>
-      </c>
-      <c r="AB7" s="8">
-        <f t="shared" si="13"/>
-        <v>5002.070800200001</v>
-      </c>
-      <c r="AC7" s="8">
-        <f t="shared" si="13"/>
-        <v>5215.4843012520014</v>
+        <v>5803.6314270040011</v>
       </c>
       <c r="AD7" s="8">
-        <f t="shared" si="13"/>
-        <v>5385.9460327857614</v>
+        <f t="shared" si="11"/>
+        <v>5997.1562171331207</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" si="13"/>
-        <v>5508.2220440375249</v>
+        <f t="shared" si="11"/>
+        <v>6137.2918226875436</v>
       </c>
       <c r="AF7" s="8">
-        <f t="shared" si="13"/>
-        <v>5578.2980677918295</v>
+        <f t="shared" si="11"/>
+        <v>6219.4629965625318</v>
       </c>
       <c r="AG7" s="8">
-        <f t="shared" si="13"/>
-        <v>5649.3747278499559</v>
+        <f t="shared" si="11"/>
+        <v>6302.8718472892324</v>
       </c>
       <c r="AH7" s="8">
-        <f t="shared" si="13"/>
-        <v>5721.4680280962675</v>
+        <f t="shared" si="11"/>
+        <v>6387.5390709384219</v>
       </c>
       <c r="AI7" s="8">
-        <f t="shared" si="13"/>
-        <v>5794.5942524043985</v>
+        <f t="shared" si="11"/>
+        <v>6473.4857369276287</v>
       </c>
       <c r="AJ7" s="8">
-        <f t="shared" si="13"/>
-        <v>5868.7699698361548</v>
+        <f t="shared" si="11"/>
+        <v>6560.7332950823238</v>
       </c>
     </row>
     <row r="8" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1578,136 +1576,136 @@
         <v>58</v>
       </c>
       <c r="C8" s="8">
-        <f t="shared" ref="C8:L8" si="14">C5+C6</f>
+        <f t="shared" ref="C8:L8" si="12">C5+C6</f>
         <v>330.3</v>
       </c>
       <c r="D8" s="8">
+        <f t="shared" si="12"/>
+        <v>362.4</v>
+      </c>
+      <c r="E8" s="8">
+        <f t="shared" si="12"/>
+        <v>423.90000000000003</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="12"/>
+        <v>456.69999999999993</v>
+      </c>
+      <c r="G8" s="8">
+        <f t="shared" si="12"/>
+        <v>472.1</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="12"/>
+        <v>498</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="12"/>
+        <v>537.19999999999993</v>
+      </c>
+      <c r="J8" s="8">
+        <f t="shared" si="12"/>
+        <v>615.40000000000009</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="12"/>
+        <v>645</v>
+      </c>
+      <c r="L8" s="8">
+        <f t="shared" si="12"/>
+        <v>598.6</v>
+      </c>
+      <c r="M8" s="8">
+        <f t="shared" ref="M8:N8" si="13">M5+M6</f>
+        <v>697.1</v>
+      </c>
+      <c r="N8" s="8">
+        <f t="shared" si="13"/>
+        <v>734.09999999999991</v>
+      </c>
+      <c r="O8" s="8">
+        <f t="shared" ref="O8:R8" si="14">O5+O6</f>
+        <v>771.69999999999993</v>
+      </c>
+      <c r="P8" s="8">
         <f t="shared" si="14"/>
-        <v>362.4</v>
-      </c>
-      <c r="E8" s="8">
+        <v>854.9</v>
+      </c>
+      <c r="Q8" s="8">
         <f t="shared" si="14"/>
-        <v>423.90000000000003</v>
-      </c>
-      <c r="F8" s="8">
+        <v>895.27440000000001</v>
+      </c>
+      <c r="R8" s="8">
         <f t="shared" si="14"/>
-        <v>456.69999999999993</v>
-      </c>
-      <c r="G8" s="8">
-        <f t="shared" si="14"/>
-        <v>472.1</v>
-      </c>
-      <c r="H8" s="8">
-        <f t="shared" si="14"/>
-        <v>498</v>
-      </c>
-      <c r="I8" s="8">
-        <f t="shared" si="14"/>
-        <v>537.19999999999993</v>
-      </c>
-      <c r="J8" s="8">
-        <f t="shared" si="14"/>
-        <v>615.40000000000009</v>
-      </c>
-      <c r="K8" s="8">
-        <f t="shared" si="14"/>
-        <v>645</v>
-      </c>
-      <c r="L8" s="8">
-        <f t="shared" si="14"/>
-        <v>598.6</v>
-      </c>
-      <c r="M8" s="8">
-        <f t="shared" ref="M8:N8" si="15">M5+M6</f>
-        <v>697.1</v>
-      </c>
-      <c r="N8" s="8">
+        <v>924.3592000000001</v>
+      </c>
+      <c r="T8" s="8">
+        <f t="shared" ref="T8:Y8" si="15">T5+T6</f>
+        <v>442.60000000000008</v>
+      </c>
+      <c r="U8" s="8">
         <f t="shared" si="15"/>
-        <v>734.09999999999991</v>
-      </c>
-      <c r="O8" s="8">
-        <f t="shared" ref="O8:R8" si="16">O5+O6</f>
-        <v>771.69999999999993</v>
-      </c>
-      <c r="P8" s="8">
+        <v>565.5</v>
+      </c>
+      <c r="V8" s="8">
+        <f t="shared" si="15"/>
+        <v>984.8</v>
+      </c>
+      <c r="W8" s="8">
+        <f t="shared" si="15"/>
+        <v>1573.3000000000002</v>
+      </c>
+      <c r="X8" s="8">
+        <f t="shared" si="15"/>
+        <v>2122.7000000000003</v>
+      </c>
+      <c r="Y8" s="8">
+        <f t="shared" si="15"/>
+        <v>2674.8</v>
+      </c>
+      <c r="Z8" s="8">
+        <f t="shared" ref="Z8:AJ8" si="16">Z5+Z6</f>
+        <v>3446.2335999999996</v>
+      </c>
+      <c r="AA8" s="8">
         <f t="shared" si="16"/>
-        <v>767.74770000000001</v>
-      </c>
-      <c r="Q8" s="8">
+        <v>3926.7548740000002</v>
+      </c>
+      <c r="AB8" s="8">
         <f t="shared" si="16"/>
-        <v>797.81904000000009</v>
-      </c>
-      <c r="R8" s="8">
+        <v>4228.3443544400006</v>
+      </c>
+      <c r="AC8" s="8">
         <f t="shared" si="16"/>
-        <v>823.80926999999997</v>
-      </c>
-      <c r="T8" s="8">
-        <f t="shared" ref="T8:Y8" si="17">T5+T6</f>
-        <v>442.60000000000008</v>
-      </c>
-      <c r="U8" s="8">
-        <f t="shared" si="17"/>
-        <v>565.5</v>
-      </c>
-      <c r="V8" s="8">
-        <f t="shared" si="17"/>
-        <v>984.8</v>
-      </c>
-      <c r="W8" s="8">
-        <f t="shared" si="17"/>
-        <v>1573.3000000000002</v>
-      </c>
-      <c r="X8" s="8">
-        <f t="shared" si="17"/>
-        <v>2122.7000000000003</v>
-      </c>
-      <c r="Y8" s="8">
-        <f t="shared" si="17"/>
-        <v>2674.8</v>
-      </c>
-      <c r="Z8" s="8">
-        <f t="shared" ref="Z8:AJ8" si="18">Z5+Z6</f>
-        <v>3161.0760100000002</v>
-      </c>
-      <c r="AA8" s="8">
-        <f t="shared" si="18"/>
-        <v>3426.4913109000004</v>
-      </c>
-      <c r="AB8" s="8">
-        <f t="shared" si="18"/>
-        <v>3644.5393587540002</v>
-      </c>
-      <c r="AC8" s="8">
-        <f t="shared" si="18"/>
-        <v>3803.6516021481611</v>
+        <v>4451.9150837176003</v>
       </c>
       <c r="AD8" s="8">
-        <f t="shared" si="18"/>
-        <v>3931.7583527088059</v>
+        <f t="shared" si="16"/>
+        <v>4604.8883835481283</v>
       </c>
       <c r="AE8" s="8">
-        <f t="shared" si="18"/>
-        <v>4024.9506103590302</v>
+        <f t="shared" si="16"/>
+        <v>4717.1786324308514</v>
       </c>
       <c r="AF8" s="8">
-        <f t="shared" si="18"/>
-        <v>4080.19391977655</v>
+        <f t="shared" si="16"/>
+        <v>4785.1486744032736</v>
       </c>
       <c r="AG8" s="8">
-        <f t="shared" si="18"/>
-        <v>4136.2895383545238</v>
+        <f t="shared" si="16"/>
+        <v>4854.2143819083813</v>
       </c>
       <c r="AH8" s="8">
-        <f t="shared" si="18"/>
-        <v>4193.2519867058809</v>
+        <f t="shared" si="16"/>
+        <v>4924.3950309037618</v>
       </c>
       <c r="AI8" s="8">
-        <f t="shared" si="18"/>
-        <v>4251.0960506001084</v>
+        <f t="shared" si="16"/>
+        <v>4995.7102564926208</v>
       </c>
       <c r="AJ8" s="8">
-        <f t="shared" si="18"/>
-        <v>4309.8367860138214</v>
+        <f t="shared" si="16"/>
+        <v>5068.1800598429663</v>
       </c>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.3">
@@ -1754,16 +1752,15 @@
         <v>156.19999999999999</v>
       </c>
       <c r="P9" s="5">
-        <f t="shared" ref="P9:R9" si="19">L9*1.05</f>
-        <v>138.81</v>
+        <v>152.1</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" si="19"/>
-        <v>146.685</v>
+        <f>M9*1.13</f>
+        <v>157.86099999999996</v>
       </c>
       <c r="R9" s="5">
-        <f t="shared" si="19"/>
-        <v>156.45000000000002</v>
+        <f>N9*1.12</f>
+        <v>166.88000000000002</v>
       </c>
       <c r="T9" s="5">
         <v>147.5</v>
@@ -1788,47 +1785,47 @@
       </c>
       <c r="Z9" s="5">
         <f>SUM(O9:R9)</f>
-        <v>598.14499999999998</v>
+        <v>633.04099999999994</v>
       </c>
       <c r="AA9" s="5">
-        <f>Z9*1.03</f>
-        <v>616.08934999999997</v>
+        <f>Z9*1.07</f>
+        <v>677.35387000000003</v>
       </c>
       <c r="AB9" s="5">
-        <f>AA9*1.02</f>
-        <v>628.41113699999994</v>
+        <f>AA9*1.05</f>
+        <v>711.22156350000012</v>
       </c>
       <c r="AC9" s="5">
-        <f>AB9*1.02</f>
-        <v>640.97935973999995</v>
+        <f>AB9*1.03</f>
+        <v>732.55821040500018</v>
       </c>
       <c r="AD9" s="5">
         <f>AC9*1.01</f>
-        <v>647.38915333739999</v>
+        <v>739.88379250905018</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" ref="AE9:AJ9" si="20">AD9*1.01</f>
-        <v>653.86304487077405</v>
+        <f t="shared" ref="AE9:AJ9" si="17">AD9*1.01</f>
+        <v>747.28263043414074</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" si="20"/>
-        <v>660.4016753194818</v>
+        <f t="shared" si="17"/>
+        <v>754.75545673848217</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" si="20"/>
-        <v>667.00569207267665</v>
+        <f t="shared" si="17"/>
+        <v>762.30301130586702</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" si="20"/>
-        <v>673.67574899340343</v>
+        <f t="shared" si="17"/>
+        <v>769.92604141892571</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" si="20"/>
-        <v>680.41250648333744</v>
+        <f t="shared" si="17"/>
+        <v>777.62530183311492</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" si="20"/>
-        <v>687.21663154817077</v>
+        <f t="shared" si="17"/>
+        <v>785.40155485144612</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
@@ -1875,16 +1872,15 @@
         <v>238.2</v>
       </c>
       <c r="P10" s="5">
-        <f>P7*0.24</f>
-        <v>253.14959999999999</v>
+        <v>264.7</v>
       </c>
       <c r="Q10" s="5">
-        <f>Q7*0.22</f>
-        <v>241.47112000000001</v>
+        <f>Q7*0.23</f>
+        <v>272.29953</v>
       </c>
       <c r="R10" s="5">
-        <f>R7*0.22</f>
-        <v>248.45237999999998</v>
+        <f>R7*0.23</f>
+        <v>279.67264</v>
       </c>
       <c r="T10" s="5">
         <v>266.2</v>
@@ -1909,47 +1905,47 @@
       </c>
       <c r="Z10" s="5">
         <f>SUM(O10:R10)</f>
-        <v>981.2731</v>
+        <v>1054.8721700000001</v>
       </c>
       <c r="AA10" s="5">
-        <f>AA7*0.21</f>
-        <v>988.50808350000011</v>
+        <f>AA7*0.22</f>
+        <v>1133.6407852</v>
       </c>
       <c r="AB10" s="5">
-        <f>AB7*0.2</f>
-        <v>1000.4141600400003</v>
+        <f>AB7*0.21</f>
+        <v>1160.8950375960001</v>
       </c>
       <c r="AC10" s="5">
         <f>AC7*0.2</f>
-        <v>1043.0968602504004</v>
+        <v>1160.7262854008002</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" ref="AD10:AJ10" si="21">AD7*0.2</f>
-        <v>1077.1892065571524</v>
+        <f t="shared" ref="AD10:AJ10" si="18">AD7*0.2</f>
+        <v>1199.4312434266242</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="21"/>
-        <v>1101.644408807505</v>
+        <f t="shared" si="18"/>
+        <v>1227.4583645375087</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="21"/>
-        <v>1115.6596135583659</v>
+        <f t="shared" si="18"/>
+        <v>1243.8925993125065</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="21"/>
-        <v>1129.8749455699913</v>
+        <f t="shared" si="18"/>
+        <v>1260.5743694578466</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="21"/>
-        <v>1144.2936056192536</v>
+        <f t="shared" si="18"/>
+        <v>1277.5078141876845</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="21"/>
-        <v>1158.9188504808797</v>
+        <f t="shared" si="18"/>
+        <v>1294.6971473855258</v>
       </c>
       <c r="AJ10" s="5">
-        <f t="shared" si="21"/>
-        <v>1173.7539939672311</v>
+        <f t="shared" si="18"/>
+        <v>1312.1466590164648</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
@@ -1996,16 +1992,15 @@
         <v>135.5</v>
       </c>
       <c r="P11" s="5">
-        <f t="shared" ref="P11:R11" si="22">P7*0.13</f>
-        <v>137.12270000000001</v>
+        <v>150.4</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" si="22"/>
-        <v>142.68747999999999</v>
+        <f t="shared" ref="P11:R11" si="19">Q7*0.13</f>
+        <v>153.90843000000001</v>
       </c>
       <c r="R11" s="5">
-        <f t="shared" si="22"/>
-        <v>146.81277</v>
+        <f t="shared" si="19"/>
+        <v>158.07584000000003</v>
       </c>
       <c r="T11" s="5">
         <v>116.3</v>
@@ -2030,47 +2025,47 @@
       </c>
       <c r="Z11" s="5">
         <f>SUM(O11:R11)</f>
-        <v>562.12294999999995</v>
+        <v>597.88427000000001</v>
       </c>
       <c r="AA11" s="5">
-        <f>AA7*0.12</f>
-        <v>564.86176200000011</v>
+        <f>AA7*0.13</f>
+        <v>669.87864580000007</v>
       </c>
       <c r="AB11" s="5">
-        <f t="shared" ref="AB11:AJ11" si="23">AB7*0.12</f>
-        <v>600.24849602400013</v>
+        <f t="shared" ref="AB11:AJ11" si="20">AB7*0.13</f>
+        <v>718.64930898800014</v>
       </c>
       <c r="AC11" s="5">
-        <f t="shared" si="23"/>
-        <v>625.85811615024011</v>
+        <f t="shared" si="20"/>
+        <v>754.47208551052017</v>
       </c>
       <c r="AD11" s="5">
-        <f t="shared" si="23"/>
-        <v>646.31352393429131</v>
+        <f t="shared" si="20"/>
+        <v>779.6303082273057</v>
       </c>
       <c r="AE11" s="5">
-        <f t="shared" si="23"/>
-        <v>660.98664528450297</v>
+        <f t="shared" si="20"/>
+        <v>797.84793694938071</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" si="23"/>
-        <v>669.39576813501947</v>
+        <f t="shared" si="20"/>
+        <v>808.53018955312916</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" si="23"/>
-        <v>677.92496734199472</v>
+        <f t="shared" si="20"/>
+        <v>819.37334014760029</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="23"/>
-        <v>686.57616337155207</v>
+        <f t="shared" si="20"/>
+        <v>830.38007922199483</v>
       </c>
       <c r="AI11" s="5">
-        <f t="shared" si="23"/>
-        <v>695.35131028852777</v>
+        <f t="shared" si="20"/>
+        <v>841.55314580059178</v>
       </c>
       <c r="AJ11" s="5">
-        <f t="shared" si="23"/>
-        <v>704.2523963803385</v>
+        <f t="shared" si="20"/>
+        <v>852.89532836070214</v>
       </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.3">
@@ -2117,16 +2112,15 @@
         <v>156.4</v>
       </c>
       <c r="P12" s="5">
-        <f>L12*1.1</f>
-        <v>159.5</v>
+        <v>165.4</v>
       </c>
       <c r="Q12" s="5">
-        <f>M12*1.1</f>
-        <v>163.79000000000002</v>
+        <f>M12*1.12</f>
+        <v>166.76800000000003</v>
       </c>
       <c r="R12" s="5">
-        <f t="shared" ref="R12" si="24">N12*1.08</f>
-        <v>173.77200000000002</v>
+        <f>N12*1.1</f>
+        <v>176.99</v>
       </c>
       <c r="T12" s="5">
         <v>152.30000000000001</v>
@@ -2151,47 +2145,47 @@
       </c>
       <c r="Z12" s="5">
         <f>SUM(O12:R12)</f>
-        <v>653.46199999999999</v>
+        <v>665.55799999999999</v>
       </c>
       <c r="AA12" s="5">
         <f>Z12*1.09</f>
-        <v>712.27358000000004</v>
+        <v>725.4582200000001</v>
       </c>
       <c r="AB12" s="5">
         <f>AA12*1.05</f>
-        <v>747.88725900000009</v>
+        <v>761.73113100000012</v>
       </c>
       <c r="AC12" s="5">
         <f>AB12*1.03</f>
-        <v>770.32387677000008</v>
+        <v>784.58306493000009</v>
       </c>
       <c r="AD12" s="5">
         <f>AC12*1.02</f>
-        <v>785.73035430540006</v>
+        <v>800.27472622860012</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" ref="AE12" si="25">AD12*1.02</f>
-        <v>801.44496139150806</v>
+        <f t="shared" ref="AE12" si="21">AD12*1.02</f>
+        <v>816.2802207531721</v>
       </c>
       <c r="AF12" s="5">
         <f>AE12*1.01</f>
-        <v>809.45941100542314</v>
+        <v>824.44302296070384</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" ref="AG12:AJ12" si="26">AF12*1.01</f>
-        <v>817.55400511547737</v>
+        <f t="shared" ref="AG12:AJ12" si="22">AF12*1.01</f>
+        <v>832.68745319031086</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="26"/>
-        <v>825.72954516663219</v>
+        <f t="shared" si="22"/>
+        <v>841.01432772221403</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="26"/>
-        <v>833.98684061829852</v>
+        <f t="shared" si="22"/>
+        <v>849.42447099943615</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="26"/>
-        <v>842.32670902448149</v>
+        <f t="shared" si="22"/>
+        <v>857.91871570943056</v>
       </c>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.3">
@@ -2239,7 +2233,7 @@
         <v>5.7</v>
       </c>
       <c r="P13" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q13" s="5">
         <v>8</v>
@@ -2270,37 +2264,47 @@
       </c>
       <c r="Z13" s="5">
         <f>SUM(O13:R13)</f>
-        <v>29.7</v>
+        <v>31.7</v>
       </c>
       <c r="AA13" s="5">
-        <v>50</v>
+        <f>Z13*1.1</f>
+        <v>34.870000000000005</v>
       </c>
       <c r="AB13" s="5">
-        <v>50</v>
+        <f t="shared" ref="AB13:AJ13" si="23">AA13*1.1</f>
+        <v>38.357000000000006</v>
       </c>
       <c r="AC13" s="5">
-        <v>50</v>
+        <f t="shared" si="23"/>
+        <v>42.192700000000009</v>
       </c>
       <c r="AD13" s="5">
-        <v>50</v>
+        <f t="shared" si="23"/>
+        <v>46.411970000000011</v>
       </c>
       <c r="AE13" s="5">
-        <v>50</v>
+        <f t="shared" si="23"/>
+        <v>51.053167000000016</v>
       </c>
       <c r="AF13" s="5">
-        <v>50</v>
+        <f t="shared" si="23"/>
+        <v>56.158483700000019</v>
       </c>
       <c r="AG13" s="5">
-        <v>50</v>
+        <f t="shared" si="23"/>
+        <v>61.774332070000028</v>
       </c>
       <c r="AH13" s="5">
-        <v>50</v>
+        <f t="shared" si="23"/>
+        <v>67.951765277000035</v>
       </c>
       <c r="AI13" s="5">
-        <v>50</v>
+        <f t="shared" si="23"/>
+        <v>74.746941804700043</v>
       </c>
       <c r="AJ13" s="5">
-        <v>50</v>
+        <f t="shared" si="23"/>
+        <v>82.221635985170053</v>
       </c>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.3">
@@ -2308,136 +2312,136 @@
         <v>32</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" ref="C14:L14" si="27">SUM(C9:C13)</f>
+        <f t="shared" ref="C14:L14" si="24">SUM(C9:C13)</f>
         <v>439.9</v>
       </c>
       <c r="D14" s="5">
+        <f t="shared" si="24"/>
+        <v>458.3</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="24"/>
+        <v>498.4</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="24"/>
+        <v>495.6</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="24"/>
+        <v>508.2999999999999</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="24"/>
+        <v>547.30000000000007</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="24"/>
+        <v>804.2</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="24"/>
+        <v>564.19999999999993</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="24"/>
+        <v>550.79999999999995</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="24"/>
+        <v>583.30000000000007</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" ref="M14:N14" si="25">SUM(M9:M13)</f>
+        <v>633.20000000000005</v>
+      </c>
+      <c r="N14" s="5">
+        <f t="shared" si="25"/>
+        <v>674.3</v>
+      </c>
+      <c r="O14" s="5">
+        <f t="shared" ref="O14:R14" si="26">SUM(O9:O13)</f>
+        <v>692</v>
+      </c>
+      <c r="P14" s="5">
+        <f t="shared" si="26"/>
+        <v>742.59999999999991</v>
+      </c>
+      <c r="Q14" s="5">
+        <f t="shared" si="26"/>
+        <v>758.83696000000009</v>
+      </c>
+      <c r="R14" s="5">
+        <f t="shared" si="26"/>
+        <v>789.61848000000009</v>
+      </c>
+      <c r="T14" s="5">
+        <f t="shared" ref="T14:Y14" si="27">SUM(T9:T13)</f>
+        <v>682.3</v>
+      </c>
+      <c r="U14" s="5">
         <f t="shared" si="27"/>
-        <v>458.3</v>
-      </c>
-      <c r="E14" s="5">
+        <v>894.1</v>
+      </c>
+      <c r="V14" s="5">
         <f t="shared" si="27"/>
-        <v>498.4</v>
-      </c>
-      <c r="F14" s="5">
+        <v>1466.1</v>
+      </c>
+      <c r="W14" s="5">
         <f t="shared" si="27"/>
-        <v>495.6</v>
-      </c>
-      <c r="G14" s="5">
+        <v>1892.2</v>
+      </c>
+      <c r="X14" s="5">
         <f t="shared" si="27"/>
-        <v>508.2999999999999</v>
-      </c>
-      <c r="H14" s="5">
+        <v>2424</v>
+      </c>
+      <c r="Y14" s="5">
         <f t="shared" si="27"/>
-        <v>547.30000000000007</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="27"/>
-        <v>804.2</v>
-      </c>
-      <c r="J14" s="5">
-        <f t="shared" si="27"/>
-        <v>564.19999999999993</v>
-      </c>
-      <c r="K14" s="5">
-        <f t="shared" si="27"/>
-        <v>550.79999999999995</v>
-      </c>
-      <c r="L14" s="5">
-        <f t="shared" si="27"/>
-        <v>583.30000000000007</v>
-      </c>
-      <c r="M14" s="5">
-        <f t="shared" ref="M14:N14" si="28">SUM(M9:M13)</f>
-        <v>633.20000000000005</v>
-      </c>
-      <c r="N14" s="5">
+        <v>2441.6</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" ref="Z14:AJ14" si="28">SUM(Z9:Z13)</f>
+        <v>2983.0554400000001</v>
+      </c>
+      <c r="AA14" s="5">
         <f t="shared" si="28"/>
-        <v>674.3</v>
-      </c>
-      <c r="O14" s="5">
-        <f t="shared" ref="O14:R14" si="29">SUM(O9:O13)</f>
-        <v>692</v>
-      </c>
-      <c r="P14" s="5">
-        <f t="shared" si="29"/>
-        <v>696.58230000000003</v>
-      </c>
-      <c r="Q14" s="5">
-        <f t="shared" si="29"/>
-        <v>702.63359999999989</v>
-      </c>
-      <c r="R14" s="5">
-        <f t="shared" si="29"/>
-        <v>733.48715000000004</v>
-      </c>
-      <c r="T14" s="5">
-        <f t="shared" ref="T14:Y14" si="30">SUM(T9:T13)</f>
-        <v>682.3</v>
-      </c>
-      <c r="U14" s="5">
-        <f t="shared" si="30"/>
-        <v>894.1</v>
-      </c>
-      <c r="V14" s="5">
-        <f t="shared" si="30"/>
-        <v>1466.1</v>
-      </c>
-      <c r="W14" s="5">
-        <f t="shared" si="30"/>
-        <v>1892.2</v>
-      </c>
-      <c r="X14" s="5">
-        <f t="shared" si="30"/>
-        <v>2424</v>
-      </c>
-      <c r="Y14" s="5">
-        <f t="shared" si="30"/>
-        <v>2441.6</v>
-      </c>
-      <c r="Z14" s="5">
-        <f t="shared" ref="Z14:AJ14" si="31">SUM(Z9:Z13)</f>
-        <v>2824.7030499999996</v>
-      </c>
-      <c r="AA14" s="5">
-        <f t="shared" si="31"/>
-        <v>2931.7327755000001</v>
+        <v>3241.201521</v>
       </c>
       <c r="AB14" s="5">
-        <f t="shared" si="31"/>
-        <v>3026.9610520640008</v>
+        <f t="shared" si="28"/>
+        <v>3390.8540410840001</v>
       </c>
       <c r="AC14" s="5">
-        <f t="shared" si="31"/>
-        <v>3130.2582129106404</v>
+        <f t="shared" si="28"/>
+        <v>3474.5323462463207</v>
       </c>
       <c r="AD14" s="5">
-        <f t="shared" si="31"/>
-        <v>3206.6222381342436</v>
+        <f t="shared" si="28"/>
+        <v>3565.6320403915806</v>
       </c>
       <c r="AE14" s="5">
-        <f t="shared" si="31"/>
-        <v>3267.9390603542902</v>
+        <f t="shared" si="28"/>
+        <v>3639.9223196742023</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" si="31"/>
-        <v>3304.9164680182903</v>
+        <f t="shared" si="28"/>
+        <v>3687.7797522648216</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="31"/>
-        <v>3342.3596101001403</v>
+        <f t="shared" si="28"/>
+        <v>3736.7125061716247</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="31"/>
-        <v>3380.2750631508416</v>
+        <f t="shared" si="28"/>
+        <v>3786.7800278278191</v>
       </c>
       <c r="AI14" s="5">
-        <f t="shared" si="31"/>
-        <v>3418.6695078710436</v>
+        <f t="shared" si="28"/>
+        <v>3838.0470078233689</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" si="31"/>
-        <v>3457.5497309202219</v>
+        <f t="shared" si="28"/>
+        <v>3890.5838939232135</v>
       </c>
     </row>
     <row r="15" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2445,136 +2449,136 @@
         <v>33</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:L15" si="32">C8-C14</f>
+        <f t="shared" ref="C15:L15" si="29">C8-C14</f>
         <v>-109.59999999999997</v>
       </c>
       <c r="D15" s="8">
+        <f t="shared" si="29"/>
+        <v>-95.900000000000034</v>
+      </c>
+      <c r="E15" s="8">
+        <f t="shared" si="29"/>
+        <v>-74.499999999999943</v>
+      </c>
+      <c r="F15" s="8">
+        <f t="shared" si="29"/>
+        <v>-38.900000000000091</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="29"/>
+        <v>-36.199999999999875</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="29"/>
+        <v>-49.300000000000068</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="29"/>
+        <v>-267.00000000000011</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="29"/>
+        <v>51.200000000000159</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" si="29"/>
+        <v>94.200000000000045</v>
+      </c>
+      <c r="L15" s="8">
+        <f t="shared" si="29"/>
+        <v>15.299999999999955</v>
+      </c>
+      <c r="M15" s="8">
+        <f t="shared" ref="M15:N15" si="30">M8-M14</f>
+        <v>63.899999999999977</v>
+      </c>
+      <c r="N15" s="8">
+        <f t="shared" si="30"/>
+        <v>59.799999999999955</v>
+      </c>
+      <c r="O15" s="8">
+        <f t="shared" ref="O15:R15" si="31">O8-O14</f>
+        <v>79.699999999999932</v>
+      </c>
+      <c r="P15" s="8">
+        <f t="shared" si="31"/>
+        <v>112.30000000000007</v>
+      </c>
+      <c r="Q15" s="8">
+        <f t="shared" si="31"/>
+        <v>136.43743999999992</v>
+      </c>
+      <c r="R15" s="8">
+        <f t="shared" si="31"/>
+        <v>134.74072000000001</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" ref="T15:Y15" si="32">T8-T14</f>
+        <v>-239.69999999999987</v>
+      </c>
+      <c r="U15" s="8">
         <f t="shared" si="32"/>
-        <v>-95.900000000000034</v>
-      </c>
-      <c r="E15" s="8">
+        <v>-328.6</v>
+      </c>
+      <c r="V15" s="8">
         <f t="shared" si="32"/>
-        <v>-74.499999999999943</v>
-      </c>
-      <c r="F15" s="8">
+        <v>-481.29999999999995</v>
+      </c>
+      <c r="W15" s="8">
         <f t="shared" si="32"/>
-        <v>-38.900000000000091</v>
-      </c>
-      <c r="G15" s="8">
+        <v>-318.89999999999986</v>
+      </c>
+      <c r="X15" s="8">
         <f t="shared" si="32"/>
-        <v>-36.199999999999875</v>
-      </c>
-      <c r="H15" s="8">
+        <v>-301.29999999999973</v>
+      </c>
+      <c r="Y15" s="8">
         <f t="shared" si="32"/>
-        <v>-49.300000000000068</v>
-      </c>
-      <c r="I15" s="8">
-        <f t="shared" si="32"/>
-        <v>-267.00000000000011</v>
-      </c>
-      <c r="J15" s="8">
-        <f t="shared" si="32"/>
-        <v>51.200000000000159</v>
-      </c>
-      <c r="K15" s="8">
-        <f t="shared" si="32"/>
-        <v>94.200000000000045</v>
-      </c>
-      <c r="L15" s="8">
-        <f t="shared" si="32"/>
-        <v>15.299999999999955</v>
-      </c>
-      <c r="M15" s="8">
-        <f t="shared" ref="M15:N15" si="33">M8-M14</f>
-        <v>63.899999999999977</v>
-      </c>
-      <c r="N15" s="8">
+        <v>233.20000000000027</v>
+      </c>
+      <c r="Z15" s="8">
+        <f t="shared" ref="Z15:AJ15" si="33">Z8-Z14</f>
+        <v>463.17815999999948</v>
+      </c>
+      <c r="AA15" s="8">
         <f t="shared" si="33"/>
-        <v>59.799999999999955</v>
-      </c>
-      <c r="O15" s="8">
-        <f t="shared" ref="O15:R15" si="34">O8-O14</f>
-        <v>79.699999999999932</v>
-      </c>
-      <c r="P15" s="8">
-        <f t="shared" si="34"/>
-        <v>71.165399999999977</v>
-      </c>
-      <c r="Q15" s="8">
-        <f t="shared" si="34"/>
-        <v>95.185440000000199</v>
-      </c>
-      <c r="R15" s="8">
-        <f t="shared" si="34"/>
-        <v>90.322119999999927</v>
-      </c>
-      <c r="T15" s="8">
-        <f t="shared" ref="T15:Y15" si="35">T8-T14</f>
-        <v>-239.69999999999987</v>
-      </c>
-      <c r="U15" s="8">
-        <f t="shared" si="35"/>
-        <v>-328.6</v>
-      </c>
-      <c r="V15" s="8">
-        <f t="shared" si="35"/>
-        <v>-481.29999999999995</v>
-      </c>
-      <c r="W15" s="8">
-        <f t="shared" si="35"/>
-        <v>-318.89999999999986</v>
-      </c>
-      <c r="X15" s="8">
-        <f t="shared" si="35"/>
-        <v>-301.29999999999973</v>
-      </c>
-      <c r="Y15" s="8">
-        <f t="shared" si="35"/>
-        <v>233.20000000000027</v>
-      </c>
-      <c r="Z15" s="8">
-        <f t="shared" ref="Z15:AJ15" si="36">Z8-Z14</f>
-        <v>336.3729600000006</v>
-      </c>
-      <c r="AA15" s="8">
-        <f t="shared" si="36"/>
-        <v>494.75853540000026</v>
+        <v>685.55335300000024</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" si="36"/>
-        <v>617.57830668999941</v>
+        <f t="shared" si="33"/>
+        <v>837.49031335600057</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" si="36"/>
-        <v>673.39338923752075</v>
+        <f t="shared" si="33"/>
+        <v>977.3827374712796</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="36"/>
-        <v>725.13611457456227</v>
+        <f t="shared" si="33"/>
+        <v>1039.2563431565477</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" si="36"/>
-        <v>757.01155000474</v>
+        <f t="shared" si="33"/>
+        <v>1077.2563127566491</v>
       </c>
       <c r="AF15" s="8">
-        <f t="shared" si="36"/>
-        <v>775.27745175825976</v>
+        <f t="shared" si="33"/>
+        <v>1097.368922138452</v>
       </c>
       <c r="AG15" s="8">
-        <f t="shared" si="36"/>
-        <v>793.92992825438341</v>
+        <f t="shared" si="33"/>
+        <v>1117.5018757367566</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" si="36"/>
-        <v>812.97692355503932</v>
+        <f t="shared" si="33"/>
+        <v>1137.6150030759427</v>
       </c>
       <c r="AI15" s="8">
-        <f t="shared" si="36"/>
-        <v>832.42654272906475</v>
+        <f t="shared" si="33"/>
+        <v>1157.663248669252</v>
       </c>
       <c r="AJ15" s="8">
-        <f t="shared" si="36"/>
-        <v>852.28705509359952</v>
+        <f t="shared" si="33"/>
+        <v>1177.5961659197528</v>
       </c>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.3">
@@ -2621,16 +2625,15 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="P16" s="5">
-        <f>P15*0.12</f>
-        <v>8.5398479999999974</v>
+        <v>14.9</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" ref="Q16:R16" si="37">Q15*0.12</f>
-        <v>11.422252800000024</v>
+        <f t="shared" ref="Q16:R16" si="34">Q15*0.12</f>
+        <v>16.372492799999989</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="37"/>
-        <v>10.83865439999999</v>
+        <f t="shared" si="34"/>
+        <v>16.168886400000002</v>
       </c>
       <c r="T16" s="5">
         <v>-0.1</v>
@@ -2655,47 +2658,47 @@
       </c>
       <c r="Z16" s="5">
         <f>SUM(O16:R16)</f>
-        <v>39.500755200000008</v>
+        <v>56.141379199999989</v>
       </c>
       <c r="AA16" s="5">
         <f>AA15*0.15</f>
-        <v>74.213780310000033</v>
+        <v>102.83300295000004</v>
       </c>
       <c r="AB16" s="5">
-        <f t="shared" ref="AB16:AJ16" si="38">AB15*0.15</f>
-        <v>92.636746003499908</v>
+        <f t="shared" ref="AB16:AJ16" si="35">AB15*0.15</f>
+        <v>125.62354700340008</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" si="38"/>
-        <v>101.00900838562811</v>
+        <f t="shared" si="35"/>
+        <v>146.60741062069192</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" si="38"/>
-        <v>108.77041718618433</v>
+        <f t="shared" si="35"/>
+        <v>155.88845147348215</v>
       </c>
       <c r="AE16" s="5">
-        <f t="shared" si="38"/>
-        <v>113.551732500711</v>
+        <f t="shared" si="35"/>
+        <v>161.58844691349736</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" si="38"/>
-        <v>116.29161776373896</v>
+        <f t="shared" si="35"/>
+        <v>164.6053383207678</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="38"/>
-        <v>119.08948923815751</v>
+        <f t="shared" si="35"/>
+        <v>167.62528136051347</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="38"/>
-        <v>121.94653853325589</v>
+        <f t="shared" si="35"/>
+        <v>170.6422504613914</v>
       </c>
       <c r="AI16" s="5">
-        <f t="shared" si="38"/>
-        <v>124.86398140935971</v>
+        <f t="shared" si="35"/>
+        <v>173.64948730038779</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="38"/>
-        <v>127.84305826403993</v>
+        <f t="shared" si="35"/>
+        <v>176.63942488796292</v>
       </c>
     </row>
     <row r="17" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2703,600 +2706,600 @@
         <v>35</v>
       </c>
       <c r="C17" s="8">
-        <f t="shared" ref="C17:L17" si="39">C15-C16</f>
+        <f t="shared" ref="C17:L17" si="36">C15-C16</f>
         <v>-110.39999999999996</v>
       </c>
       <c r="D17" s="8">
+        <f t="shared" si="36"/>
+        <v>-96.000000000000028</v>
+      </c>
+      <c r="E17" s="8">
+        <f t="shared" si="36"/>
+        <v>-74.29999999999994</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="36"/>
+        <v>-42.100000000000094</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="36"/>
+        <v>-34.599999999999874</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="36"/>
+        <v>-47.500000000000071</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="36"/>
+        <v>-266.80000000000013</v>
+      </c>
+      <c r="J17" s="8">
+        <f t="shared" si="36"/>
+        <v>48.000000000000156</v>
+      </c>
+      <c r="K17" s="8">
+        <f t="shared" si="36"/>
+        <v>88.000000000000043</v>
+      </c>
+      <c r="L17" s="8">
+        <f t="shared" si="36"/>
+        <v>17.399999999999956</v>
+      </c>
+      <c r="M17" s="8">
+        <f t="shared" ref="M17:N17" si="37">M15-M16</f>
+        <v>60.799999999999976</v>
+      </c>
+      <c r="N17" s="8">
+        <f t="shared" si="37"/>
+        <v>332.29999999999995</v>
+      </c>
+      <c r="O17" s="8">
+        <f t="shared" ref="O17:R17" si="38">O15-O16</f>
+        <v>70.999999999999929</v>
+      </c>
+      <c r="P17" s="8">
+        <f t="shared" si="38"/>
+        <v>97.400000000000063</v>
+      </c>
+      <c r="Q17" s="8">
+        <f t="shared" si="38"/>
+        <v>120.06494719999993</v>
+      </c>
+      <c r="R17" s="8">
+        <f t="shared" si="38"/>
+        <v>118.57183360000001</v>
+      </c>
+      <c r="T17" s="8">
+        <f t="shared" ref="T17:Y17" si="39">T15-T16</f>
+        <v>-239.59999999999988</v>
+      </c>
+      <c r="U17" s="8">
         <f t="shared" si="39"/>
-        <v>-96.000000000000028</v>
-      </c>
-      <c r="E17" s="8">
+        <v>-224.10000000000002</v>
+      </c>
+      <c r="V17" s="8">
         <f t="shared" si="39"/>
-        <v>-74.29999999999994</v>
-      </c>
-      <c r="F17" s="8">
+        <v>-484.09999999999997</v>
+      </c>
+      <c r="W17" s="8">
         <f t="shared" si="39"/>
-        <v>-42.100000000000094</v>
-      </c>
-      <c r="G17" s="8">
+        <v>-322.79999999999984</v>
+      </c>
+      <c r="X17" s="8">
         <f t="shared" si="39"/>
-        <v>-34.599999999999874</v>
-      </c>
-      <c r="H17" s="8">
+        <v>-300.89999999999975</v>
+      </c>
+      <c r="Y17" s="8">
         <f t="shared" si="39"/>
-        <v>-47.500000000000071</v>
-      </c>
-      <c r="I17" s="8">
-        <f t="shared" si="39"/>
-        <v>-266.80000000000013</v>
-      </c>
-      <c r="J17" s="8">
-        <f t="shared" si="39"/>
-        <v>48.000000000000156</v>
-      </c>
-      <c r="K17" s="8">
-        <f t="shared" si="39"/>
-        <v>88.000000000000043</v>
-      </c>
-      <c r="L17" s="8">
-        <f t="shared" si="39"/>
-        <v>17.399999999999956</v>
-      </c>
-      <c r="M17" s="8">
-        <f t="shared" ref="M17:N17" si="40">M15-M16</f>
-        <v>60.799999999999976</v>
-      </c>
-      <c r="N17" s="8">
+        <v>498.50000000000028</v>
+      </c>
+      <c r="Z17" s="8">
+        <f t="shared" ref="Z17:AJ17" si="40">Z15-Z16</f>
+        <v>407.03678079999952</v>
+      </c>
+      <c r="AA17" s="8">
         <f t="shared" si="40"/>
-        <v>332.29999999999995</v>
-      </c>
-      <c r="O17" s="8">
-        <f t="shared" ref="O17:R17" si="41">O15-O16</f>
-        <v>70.999999999999929</v>
-      </c>
-      <c r="P17" s="8">
-        <f t="shared" si="41"/>
-        <v>62.625551999999978</v>
-      </c>
-      <c r="Q17" s="8">
-        <f t="shared" si="41"/>
-        <v>83.763187200000175</v>
-      </c>
-      <c r="R17" s="8">
-        <f t="shared" si="41"/>
-        <v>79.483465599999931</v>
-      </c>
-      <c r="T17" s="8">
-        <f t="shared" ref="T17:Y17" si="42">T15-T16</f>
-        <v>-239.59999999999988</v>
-      </c>
-      <c r="U17" s="8">
-        <f t="shared" si="42"/>
-        <v>-224.10000000000002</v>
-      </c>
-      <c r="V17" s="8">
-        <f t="shared" si="42"/>
-        <v>-484.09999999999997</v>
-      </c>
-      <c r="W17" s="8">
-        <f t="shared" si="42"/>
-        <v>-322.79999999999984</v>
-      </c>
-      <c r="X17" s="8">
-        <f t="shared" si="42"/>
-        <v>-300.89999999999975</v>
-      </c>
-      <c r="Y17" s="8">
-        <f t="shared" si="42"/>
-        <v>498.50000000000028</v>
-      </c>
-      <c r="Z17" s="8">
-        <f t="shared" ref="Z17:AJ17" si="43">Z15-Z16</f>
-        <v>296.87220480000059</v>
-      </c>
-      <c r="AA17" s="8">
-        <f t="shared" si="43"/>
-        <v>420.54475509000019</v>
+        <v>582.72035005000021</v>
       </c>
       <c r="AB17" s="8">
-        <f t="shared" si="43"/>
-        <v>524.94156068649954</v>
+        <f t="shared" si="40"/>
+        <v>711.86676635260051</v>
       </c>
       <c r="AC17" s="8">
-        <f t="shared" si="43"/>
-        <v>572.38438085189262</v>
+        <f t="shared" si="40"/>
+        <v>830.7753268505877</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" si="43"/>
-        <v>616.36569738837795</v>
+        <f t="shared" si="40"/>
+        <v>883.36789168306552</v>
       </c>
       <c r="AE17" s="8">
-        <f t="shared" si="43"/>
-        <v>643.45981750402905</v>
+        <f t="shared" si="40"/>
+        <v>915.66786584315173</v>
       </c>
       <c r="AF17" s="8">
-        <f t="shared" si="43"/>
-        <v>658.98583399452082</v>
+        <f t="shared" si="40"/>
+        <v>932.76358381768421</v>
       </c>
       <c r="AG17" s="8">
-        <f t="shared" si="43"/>
-        <v>674.8404390162259</v>
+        <f t="shared" si="40"/>
+        <v>949.87659437624313</v>
       </c>
       <c r="AH17" s="8">
-        <f t="shared" si="43"/>
-        <v>691.03038502178345</v>
+        <f t="shared" si="40"/>
+        <v>966.97275261455127</v>
       </c>
       <c r="AI17" s="8">
-        <f t="shared" si="43"/>
-        <v>707.56256131970508</v>
+        <f t="shared" si="40"/>
+        <v>984.01376136886415</v>
       </c>
       <c r="AJ17" s="8">
-        <f t="shared" si="43"/>
-        <v>724.44399682955964</v>
+        <f t="shared" si="40"/>
+        <v>1000.9567410317899</v>
       </c>
       <c r="AK17" s="1">
         <f>AJ17*(1+$AN$22)</f>
-        <v>717.199556861264</v>
+        <v>990.94717362147196</v>
       </c>
       <c r="AL17" s="1">
-        <f t="shared" ref="AL17:CW17" si="44">AK17*(1+$AN$22)</f>
-        <v>710.0275612926514</v>
+        <f t="shared" ref="AL17:CW17" si="41">AK17*(1+$AN$22)</f>
+        <v>981.03770188525721</v>
       </c>
       <c r="AM17" s="1">
-        <f t="shared" si="44"/>
-        <v>702.92728567972483</v>
+        <f t="shared" si="41"/>
+        <v>971.22732486640462</v>
       </c>
       <c r="AN17" s="1">
-        <f t="shared" si="44"/>
-        <v>695.89801282292763</v>
+        <f t="shared" si="41"/>
+        <v>961.5150516177406</v>
       </c>
       <c r="AO17" s="1">
-        <f t="shared" si="44"/>
-        <v>688.93903269469831</v>
+        <f t="shared" si="41"/>
+        <v>951.89990110156316</v>
       </c>
       <c r="AP17" s="1">
-        <f t="shared" si="44"/>
-        <v>682.04964236775129</v>
+        <f t="shared" si="41"/>
+        <v>942.38090209054747</v>
       </c>
       <c r="AQ17" s="1">
-        <f t="shared" si="44"/>
-        <v>675.22914594407382</v>
+        <f t="shared" si="41"/>
+        <v>932.95709306964193</v>
       </c>
       <c r="AR17" s="1">
-        <f t="shared" si="44"/>
-        <v>668.47685448463312</v>
+        <f t="shared" si="41"/>
+        <v>923.62752213894555</v>
       </c>
       <c r="AS17" s="1">
-        <f t="shared" si="44"/>
-        <v>661.79208593978683</v>
+        <f t="shared" si="41"/>
+        <v>914.39124691755603</v>
       </c>
       <c r="AT17" s="1">
-        <f t="shared" si="44"/>
-        <v>655.174165080389</v>
+        <f t="shared" si="41"/>
+        <v>905.24733444838046</v>
       </c>
       <c r="AU17" s="1">
-        <f t="shared" si="44"/>
-        <v>648.62242342958507</v>
+        <f t="shared" si="41"/>
+        <v>896.19486110389664</v>
       </c>
       <c r="AV17" s="1">
-        <f t="shared" si="44"/>
-        <v>642.13619919528924</v>
+        <f t="shared" si="41"/>
+        <v>887.23291249285762</v>
       </c>
       <c r="AW17" s="1">
-        <f t="shared" si="44"/>
-        <v>635.71483720333629</v>
+        <f t="shared" si="41"/>
+        <v>878.36058336792905</v>
       </c>
       <c r="AX17" s="1">
-        <f t="shared" si="44"/>
-        <v>629.35768883130288</v>
+        <f t="shared" si="41"/>
+        <v>869.57697753424975</v>
       </c>
       <c r="AY17" s="1">
-        <f t="shared" si="44"/>
-        <v>623.06411194298983</v>
+        <f t="shared" si="41"/>
+        <v>860.88120775890729</v>
       </c>
       <c r="AZ17" s="1">
-        <f t="shared" si="44"/>
-        <v>616.83347082355988</v>
+        <f t="shared" si="41"/>
+        <v>852.27239568131824</v>
       </c>
       <c r="BA17" s="1">
-        <f t="shared" si="44"/>
-        <v>610.66513611532423</v>
+        <f t="shared" si="41"/>
+        <v>843.74967172450511</v>
       </c>
       <c r="BB17" s="1">
-        <f t="shared" si="44"/>
-        <v>604.55848475417099</v>
+        <f t="shared" si="41"/>
+        <v>835.31217500726007</v>
       </c>
       <c r="BC17" s="1">
-        <f t="shared" si="44"/>
-        <v>598.51289990662929</v>
+        <f t="shared" si="41"/>
+        <v>826.95905325718741</v>
       </c>
       <c r="BD17" s="1">
-        <f t="shared" si="44"/>
-        <v>592.52777090756297</v>
+        <f t="shared" si="41"/>
+        <v>818.68946272461551</v>
       </c>
       <c r="BE17" s="1">
-        <f t="shared" si="44"/>
-        <v>586.60249319848731</v>
+        <f t="shared" si="41"/>
+        <v>810.50256809736936</v>
       </c>
       <c r="BF17" s="1">
-        <f t="shared" si="44"/>
-        <v>580.73646826650247</v>
+        <f t="shared" si="41"/>
+        <v>802.39754241639571</v>
       </c>
       <c r="BG17" s="1">
-        <f t="shared" si="44"/>
-        <v>574.92910358383745</v>
+        <f t="shared" si="41"/>
+        <v>794.37356699223176</v>
       </c>
       <c r="BH17" s="1">
-        <f t="shared" si="44"/>
-        <v>569.17981254799906</v>
+        <f t="shared" si="41"/>
+        <v>786.42983132230938</v>
       </c>
       <c r="BI17" s="1">
-        <f t="shared" si="44"/>
-        <v>563.48801442251909</v>
+        <f t="shared" si="41"/>
+        <v>778.56553300908627</v>
       </c>
       <c r="BJ17" s="1">
-        <f t="shared" si="44"/>
-        <v>557.85313427829385</v>
+        <f t="shared" si="41"/>
+        <v>770.77987767899538</v>
       </c>
       <c r="BK17" s="1">
-        <f t="shared" si="44"/>
-        <v>552.27460293551087</v>
+        <f t="shared" si="41"/>
+        <v>763.07207890220536</v>
       </c>
       <c r="BL17" s="1">
-        <f t="shared" si="44"/>
-        <v>546.75185690615581</v>
+        <f t="shared" si="41"/>
+        <v>755.44135811318336</v>
       </c>
       <c r="BM17" s="1">
-        <f t="shared" si="44"/>
-        <v>541.28433833709425</v>
+        <f t="shared" si="41"/>
+        <v>747.88694453205153</v>
       </c>
       <c r="BN17" s="1">
-        <f t="shared" si="44"/>
-        <v>535.8714949537233</v>
+        <f t="shared" si="41"/>
+        <v>740.40807508673106</v>
       </c>
       <c r="BO17" s="1">
-        <f t="shared" si="44"/>
-        <v>530.51278000418608</v>
+        <f t="shared" si="41"/>
+        <v>733.00399433586369</v>
       </c>
       <c r="BP17" s="1">
-        <f t="shared" si="44"/>
-        <v>525.20765220414421</v>
+        <f t="shared" si="41"/>
+        <v>725.67395439250504</v>
       </c>
       <c r="BQ17" s="1">
-        <f t="shared" si="44"/>
-        <v>519.95557568210279</v>
+        <f t="shared" si="41"/>
+        <v>718.41721484857999</v>
       </c>
       <c r="BR17" s="1">
-        <f t="shared" si="44"/>
-        <v>514.75601992528175</v>
+        <f t="shared" si="41"/>
+        <v>711.23304270009419</v>
       </c>
       <c r="BS17" s="1">
-        <f t="shared" si="44"/>
-        <v>509.60845972602891</v>
+        <f t="shared" si="41"/>
+        <v>704.1207122730932</v>
       </c>
       <c r="BT17" s="1">
-        <f t="shared" si="44"/>
-        <v>504.51237512876861</v>
+        <f t="shared" si="41"/>
+        <v>697.07950515036225</v>
       </c>
       <c r="BU17" s="1">
-        <f t="shared" si="44"/>
-        <v>499.46725137748092</v>
+        <f t="shared" si="41"/>
+        <v>690.10871009885864</v>
       </c>
       <c r="BV17" s="1">
-        <f t="shared" si="44"/>
-        <v>494.47257886370613</v>
+        <f t="shared" si="41"/>
+        <v>683.20762299787009</v>
       </c>
       <c r="BW17" s="1">
-        <f t="shared" si="44"/>
-        <v>489.52785307506906</v>
+        <f t="shared" si="41"/>
+        <v>676.37554676789136</v>
       </c>
       <c r="BX17" s="1">
-        <f t="shared" si="44"/>
-        <v>484.63257454431835</v>
+        <f t="shared" si="41"/>
+        <v>669.61179130021242</v>
       </c>
       <c r="BY17" s="1">
-        <f t="shared" si="44"/>
-        <v>479.78624879887514</v>
+        <f t="shared" si="41"/>
+        <v>662.91567338721029</v>
       </c>
       <c r="BZ17" s="1">
-        <f t="shared" si="44"/>
-        <v>474.98838631088637</v>
+        <f t="shared" si="41"/>
+        <v>656.28651665333814</v>
       </c>
       <c r="CA17" s="1">
-        <f t="shared" si="44"/>
-        <v>470.23850244777748</v>
+        <f t="shared" si="41"/>
+        <v>649.72365148680478</v>
       </c>
       <c r="CB17" s="1">
-        <f t="shared" si="44"/>
-        <v>465.53611742329969</v>
+        <f t="shared" si="41"/>
+        <v>643.22641497193672</v>
       </c>
       <c r="CC17" s="1">
-        <f t="shared" si="44"/>
-        <v>460.88075624906668</v>
+        <f t="shared" si="41"/>
+        <v>636.79415082221738</v>
       </c>
       <c r="CD17" s="1">
-        <f t="shared" si="44"/>
-        <v>456.27194868657602</v>
+        <f t="shared" si="41"/>
+        <v>630.42620931399517</v>
       </c>
       <c r="CE17" s="1">
-        <f t="shared" si="44"/>
-        <v>451.70922919971025</v>
+        <f t="shared" si="41"/>
+        <v>624.12194722085519</v>
       </c>
       <c r="CF17" s="1">
-        <f t="shared" si="44"/>
-        <v>447.19213690771312</v>
+        <f t="shared" si="41"/>
+        <v>617.88072774864668</v>
       </c>
       <c r="CG17" s="1">
-        <f t="shared" si="44"/>
-        <v>442.72021553863601</v>
+        <f t="shared" si="41"/>
+        <v>611.70192047116018</v>
       </c>
       <c r="CH17" s="1">
-        <f t="shared" si="44"/>
-        <v>438.29301338324967</v>
+        <f t="shared" si="41"/>
+        <v>605.58490126644858</v>
       </c>
       <c r="CI17" s="1">
-        <f t="shared" si="44"/>
-        <v>433.9100832494172</v>
+        <f t="shared" si="41"/>
+        <v>599.52905225378413</v>
       </c>
       <c r="CJ17" s="1">
-        <f t="shared" si="44"/>
-        <v>429.57098241692302</v>
+        <f t="shared" si="41"/>
+        <v>593.53376173124627</v>
       </c>
       <c r="CK17" s="1">
-        <f t="shared" si="44"/>
-        <v>425.27527259275377</v>
+        <f t="shared" si="41"/>
+        <v>587.59842411393379</v>
       </c>
       <c r="CL17" s="1">
-        <f t="shared" si="44"/>
-        <v>421.0225198668262</v>
+        <f t="shared" si="41"/>
+        <v>581.72243987279444</v>
       </c>
       <c r="CM17" s="1">
-        <f t="shared" si="44"/>
-        <v>416.81229466815796</v>
+        <f t="shared" si="41"/>
+        <v>575.90521547406649</v>
       </c>
       <c r="CN17" s="1">
-        <f t="shared" si="44"/>
-        <v>412.64417172147637</v>
+        <f t="shared" si="41"/>
+        <v>570.14616331932586</v>
       </c>
       <c r="CO17" s="1">
-        <f t="shared" si="44"/>
-        <v>408.51773000426158</v>
+        <f t="shared" si="41"/>
+        <v>564.44470168613259</v>
       </c>
       <c r="CP17" s="1">
-        <f t="shared" si="44"/>
-        <v>404.43255270421895</v>
+        <f t="shared" si="41"/>
+        <v>558.80025466927123</v>
       </c>
       <c r="CQ17" s="1">
-        <f t="shared" si="44"/>
-        <v>400.38822717717676</v>
+        <f t="shared" si="41"/>
+        <v>553.21225212257855</v>
       </c>
       <c r="CR17" s="1">
-        <f t="shared" si="44"/>
-        <v>396.38434490540499</v>
+        <f t="shared" si="41"/>
+        <v>547.68012960135275</v>
       </c>
       <c r="CS17" s="1">
-        <f t="shared" si="44"/>
-        <v>392.42050145635091</v>
+        <f t="shared" si="41"/>
+        <v>542.20332830533926</v>
       </c>
       <c r="CT17" s="1">
-        <f t="shared" si="44"/>
-        <v>388.49629644178736</v>
+        <f t="shared" si="41"/>
+        <v>536.7812950222858</v>
       </c>
       <c r="CU17" s="1">
-        <f t="shared" si="44"/>
-        <v>384.6113334773695</v>
+        <f t="shared" si="41"/>
+        <v>531.41348207206295</v>
       </c>
       <c r="CV17" s="1">
-        <f t="shared" si="44"/>
-        <v>380.76522014259581</v>
+        <f t="shared" si="41"/>
+        <v>526.09934725134235</v>
       </c>
       <c r="CW17" s="1">
-        <f t="shared" si="44"/>
-        <v>376.95756794116983</v>
+        <f t="shared" si="41"/>
+        <v>520.83835377882895</v>
       </c>
       <c r="CX17" s="1">
-        <f t="shared" ref="CX17:EV17" si="45">CW17*(1+$AN$22)</f>
-        <v>373.18799226175815</v>
+        <f t="shared" ref="CX17:EV17" si="42">CW17*(1+$AN$22)</f>
+        <v>515.62997024104061</v>
       </c>
       <c r="CY17" s="1">
-        <f t="shared" si="45"/>
-        <v>369.45611233914059</v>
+        <f t="shared" si="42"/>
+        <v>510.47367053863019</v>
       </c>
       <c r="CZ17" s="1">
-        <f t="shared" si="45"/>
-        <v>365.76155121574919</v>
+        <f t="shared" si="42"/>
+        <v>505.36893383324389</v>
       </c>
       <c r="DA17" s="1">
-        <f t="shared" si="45"/>
-        <v>362.10393570359167</v>
+        <f t="shared" si="42"/>
+        <v>500.31524449491144</v>
       </c>
       <c r="DB17" s="1">
-        <f t="shared" si="45"/>
-        <v>358.48289634655578</v>
+        <f t="shared" si="42"/>
+        <v>495.3120920499623</v>
       </c>
       <c r="DC17" s="1">
-        <f t="shared" si="45"/>
-        <v>354.89806738309022</v>
+        <f t="shared" si="42"/>
+        <v>490.3589711294627</v>
       </c>
       <c r="DD17" s="1">
-        <f t="shared" si="45"/>
-        <v>351.34908670925932</v>
+        <f t="shared" si="42"/>
+        <v>485.45538141816809</v>
       </c>
       <c r="DE17" s="1">
-        <f t="shared" si="45"/>
-        <v>347.83559584216675</v>
+        <f t="shared" si="42"/>
+        <v>480.60082760398637</v>
       </c>
       <c r="DF17" s="1">
-        <f t="shared" si="45"/>
-        <v>344.35723988374508</v>
+        <f t="shared" si="42"/>
+        <v>475.79481932794653</v>
       </c>
       <c r="DG17" s="1">
-        <f t="shared" si="45"/>
-        <v>340.91366748490765</v>
+        <f t="shared" si="42"/>
+        <v>471.03687113466708</v>
       </c>
       <c r="DH17" s="1">
-        <f t="shared" si="45"/>
-        <v>337.50453081005855</v>
+        <f t="shared" si="42"/>
+        <v>466.32650242332039</v>
       </c>
       <c r="DI17" s="1">
-        <f t="shared" si="45"/>
-        <v>334.12948550195796</v>
+        <f t="shared" si="42"/>
+        <v>461.66323739908717</v>
       </c>
       <c r="DJ17" s="1">
-        <f t="shared" si="45"/>
-        <v>330.7881906469384</v>
+        <f t="shared" si="42"/>
+        <v>457.04660502509631</v>
       </c>
       <c r="DK17" s="1">
-        <f t="shared" si="45"/>
-        <v>327.48030874046901</v>
+        <f t="shared" si="42"/>
+        <v>452.47613897484536</v>
       </c>
       <c r="DL17" s="1">
-        <f t="shared" si="45"/>
-        <v>324.20550565306434</v>
+        <f t="shared" si="42"/>
+        <v>447.95137758509691</v>
       </c>
       <c r="DM17" s="1">
-        <f t="shared" si="45"/>
-        <v>320.96345059653368</v>
+        <f t="shared" si="42"/>
+        <v>443.47186380924592</v>
       </c>
       <c r="DN17" s="1">
-        <f t="shared" si="45"/>
-        <v>317.75381609056836</v>
+        <f t="shared" si="42"/>
+        <v>439.03714517115344</v>
       </c>
       <c r="DO17" s="1">
-        <f t="shared" si="45"/>
-        <v>314.57627792966269</v>
+        <f t="shared" si="42"/>
+        <v>434.64677371944191</v>
       </c>
       <c r="DP17" s="1">
-        <f t="shared" si="45"/>
-        <v>311.43051515036609</v>
+        <f t="shared" si="42"/>
+        <v>430.30030598224749</v>
       </c>
       <c r="DQ17" s="1">
-        <f t="shared" si="45"/>
-        <v>308.3162099988624</v>
+        <f t="shared" si="42"/>
+        <v>425.99730292242504</v>
       </c>
       <c r="DR17" s="1">
-        <f t="shared" si="45"/>
-        <v>305.23304789887379</v>
+        <f t="shared" si="42"/>
+        <v>421.73732989320081</v>
       </c>
       <c r="DS17" s="1">
-        <f t="shared" si="45"/>
-        <v>302.18071741988507</v>
+        <f t="shared" si="42"/>
+        <v>417.51995659426882</v>
       </c>
       <c r="DT17" s="1">
-        <f t="shared" si="45"/>
-        <v>299.15891024568623</v>
+        <f t="shared" si="42"/>
+        <v>413.34475702832611</v>
       </c>
       <c r="DU17" s="1">
-        <f t="shared" si="45"/>
-        <v>296.16732114322934</v>
+        <f t="shared" si="42"/>
+        <v>409.21130945804288</v>
       </c>
       <c r="DV17" s="1">
-        <f t="shared" si="45"/>
-        <v>293.20564793179705</v>
+        <f t="shared" si="42"/>
+        <v>405.11919636346244</v>
       </c>
       <c r="DW17" s="1">
-        <f t="shared" si="45"/>
-        <v>290.27359145247908</v>
+        <f t="shared" si="42"/>
+        <v>401.06800439982783</v>
       </c>
       <c r="DX17" s="1">
-        <f t="shared" si="45"/>
-        <v>287.3708555379543</v>
+        <f t="shared" si="42"/>
+        <v>397.05732435582956</v>
       </c>
       <c r="DY17" s="1">
-        <f t="shared" si="45"/>
-        <v>284.49714698257475</v>
+        <f t="shared" si="42"/>
+        <v>393.08675111227126</v>
       </c>
       <c r="DZ17" s="1">
-        <f t="shared" si="45"/>
-        <v>281.65217551274901</v>
+        <f t="shared" si="42"/>
+        <v>389.15588360114856</v>
       </c>
       <c r="EA17" s="1">
-        <f t="shared" si="45"/>
-        <v>278.83565375762151</v>
+        <f t="shared" si="42"/>
+        <v>385.26432476513708</v>
       </c>
       <c r="EB17" s="1">
-        <f t="shared" si="45"/>
-        <v>276.04729722004532</v>
+        <f t="shared" si="42"/>
+        <v>381.4116815174857</v>
       </c>
       <c r="EC17" s="1">
-        <f t="shared" si="45"/>
-        <v>273.28682424784489</v>
+        <f t="shared" si="42"/>
+        <v>377.59756470231082</v>
       </c>
       <c r="ED17" s="1">
-        <f t="shared" si="45"/>
-        <v>270.55395600536644</v>
+        <f t="shared" si="42"/>
+        <v>373.82158905528769</v>
       </c>
       <c r="EE17" s="1">
-        <f t="shared" si="45"/>
-        <v>267.84841644531275</v>
+        <f t="shared" si="42"/>
+        <v>370.08337316473478</v>
       </c>
       <c r="EF17" s="1">
-        <f t="shared" si="45"/>
-        <v>265.1699322808596</v>
+        <f t="shared" si="42"/>
+        <v>366.3825394330874</v>
       </c>
       <c r="EG17" s="1">
-        <f t="shared" si="45"/>
-        <v>262.51823295805099</v>
+        <f t="shared" si="42"/>
+        <v>362.7187140387565</v>
       </c>
       <c r="EH17" s="1">
-        <f t="shared" si="45"/>
-        <v>259.89305062847046</v>
+        <f t="shared" si="42"/>
+        <v>359.09152689836895</v>
       </c>
       <c r="EI17" s="1">
-        <f t="shared" si="45"/>
-        <v>257.29412012218575</v>
+        <f t="shared" si="42"/>
+        <v>355.50061162938528</v>
       </c>
       <c r="EJ17" s="1">
-        <f t="shared" si="45"/>
-        <v>254.72117892096389</v>
+        <f t="shared" si="42"/>
+        <v>351.94560551309144</v>
       </c>
       <c r="EK17" s="1">
-        <f t="shared" si="45"/>
-        <v>252.17396713175424</v>
+        <f t="shared" si="42"/>
+        <v>348.42614945796049</v>
       </c>
       <c r="EL17" s="1">
-        <f t="shared" si="45"/>
-        <v>249.65222746043671</v>
+        <f t="shared" si="42"/>
+        <v>344.94188796338091</v>
       </c>
       <c r="EM17" s="1">
-        <f t="shared" si="45"/>
-        <v>247.15570518583235</v>
+        <f t="shared" si="42"/>
+        <v>341.4924690837471</v>
       </c>
       <c r="EN17" s="1">
-        <f t="shared" si="45"/>
-        <v>244.68414813397402</v>
+        <f t="shared" si="42"/>
+        <v>338.0775443929096</v>
       </c>
       <c r="EO17" s="1">
-        <f t="shared" si="45"/>
-        <v>242.23730665263429</v>
+        <f t="shared" si="42"/>
+        <v>334.69676894898049</v>
       </c>
       <c r="EP17" s="1">
-        <f t="shared" si="45"/>
-        <v>239.81493358610794</v>
+        <f t="shared" si="42"/>
+        <v>331.34980125949068</v>
       </c>
       <c r="EQ17" s="1">
-        <f t="shared" si="45"/>
-        <v>237.41678425024685</v>
+        <f t="shared" si="42"/>
+        <v>328.03630324689578</v>
       </c>
       <c r="ER17" s="1">
-        <f t="shared" si="45"/>
-        <v>235.04261640774439</v>
+        <f t="shared" si="42"/>
+        <v>324.7559402144268</v>
       </c>
       <c r="ES17" s="1">
-        <f t="shared" si="45"/>
-        <v>232.69219024366694</v>
+        <f t="shared" si="42"/>
+        <v>321.50838081228255</v>
       </c>
       <c r="ET17" s="1">
-        <f t="shared" si="45"/>
-        <v>230.36526834123026</v>
+        <f t="shared" si="42"/>
+        <v>318.29329700415974</v>
       </c>
       <c r="EU17" s="1">
-        <f t="shared" si="45"/>
-        <v>228.06161565781795</v>
+        <f t="shared" si="42"/>
+        <v>315.11036403411816</v>
       </c>
       <c r="EV17" s="1">
-        <f t="shared" si="45"/>
-        <v>225.78099950123976</v>
+        <f t="shared" si="42"/>
+        <v>311.95926039377696</v>
       </c>
     </row>
     <row r="18" spans="2:152" x14ac:dyDescent="0.3">
@@ -3343,13 +3346,16 @@
         <v>1098</v>
       </c>
       <c r="P18" s="5">
-        <v>1098</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="Q18" s="5">
-        <v>1098</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="R18" s="5">
-        <v>1098</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="T18" s="5">
         <v>937</v>
@@ -3370,37 +3376,48 @@
         <v>1087.9000000000001</v>
       </c>
       <c r="Z18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AA18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AB18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AC18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AD18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AE18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AF18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AG18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AH18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AI18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1087.9000000000001</v>
+        <f>1107</f>
+        <v>1107</v>
       </c>
     </row>
     <row r="19" spans="2:152" x14ac:dyDescent="0.3">
@@ -3408,136 +3425,136 @@
         <v>36</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="C19:L19" si="46">C17/C18</f>
+        <f t="shared" ref="C19:L19" si="43">C17/C18</f>
         <v>-0.11787315823190259</v>
       </c>
       <c r="D19" s="7">
+        <f t="shared" si="43"/>
+        <v>-0.10249839846252405</v>
+      </c>
+      <c r="E19" s="7">
+        <f t="shared" si="43"/>
+        <v>-7.9329489643390927E-2</v>
+      </c>
+      <c r="F19" s="7">
+        <f t="shared" si="43"/>
+        <v>-4.494981849241949E-2</v>
+      </c>
+      <c r="G19" s="7">
+        <f t="shared" si="43"/>
+        <v>-3.6942131112534561E-2</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="43"/>
+        <v>-5.0715353405936442E-2</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="43"/>
+        <v>-0.28486013239376479</v>
+      </c>
+      <c r="J19" s="7">
+        <f t="shared" si="43"/>
+        <v>5.1249199231262178E-2</v>
+      </c>
+      <c r="K19" s="7">
+        <f t="shared" si="43"/>
+        <v>8.955831467535115E-2</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="43"/>
+        <v>1.6324233042499255E-2</v>
+      </c>
+      <c r="M19" s="7">
+        <f t="shared" ref="M19:N19" si="44">M17/M18</f>
+        <v>5.6031702147267513E-2</v>
+      </c>
+      <c r="N19" s="7">
+        <f t="shared" si="44"/>
+        <v>0.30545086864601517</v>
+      </c>
+      <c r="O19" s="7">
+        <f t="shared" ref="O19:R19" si="45">O17/O18</f>
+        <v>6.466302367941705E-2</v>
+      </c>
+      <c r="P19" s="7">
+        <f t="shared" si="45"/>
+        <v>8.7985546522131947E-2</v>
+      </c>
+      <c r="Q19" s="7">
+        <f t="shared" si="45"/>
+        <v>0.1084597535682023</v>
+      </c>
+      <c r="R19" s="7">
+        <f t="shared" si="45"/>
+        <v>0.10711096079494128</v>
+      </c>
+      <c r="T19" s="7">
+        <f t="shared" ref="T19:Y19" si="46">T17/T18</f>
+        <v>-0.25570971184631791</v>
+      </c>
+      <c r="U19" s="7">
         <f t="shared" si="46"/>
-        <v>-0.10249839846252405</v>
-      </c>
-      <c r="E19" s="7">
+        <v>-0.23916755602988263</v>
+      </c>
+      <c r="V19" s="7">
         <f t="shared" si="46"/>
-        <v>-7.9329489643390927E-2</v>
-      </c>
-      <c r="F19" s="7">
+        <v>-0.51664887940234783</v>
+      </c>
+      <c r="W19" s="7">
         <f t="shared" si="46"/>
-        <v>-4.494981849241949E-2</v>
-      </c>
-      <c r="G19" s="7">
+        <v>-0.34450373532550677</v>
+      </c>
+      <c r="X19" s="7">
         <f t="shared" si="46"/>
-        <v>-3.6942131112534561E-2</v>
-      </c>
-      <c r="H19" s="7">
+        <v>-0.3211312700106721</v>
+      </c>
+      <c r="Y19" s="7">
         <f t="shared" si="46"/>
-        <v>-5.0715353405936442E-2</v>
-      </c>
-      <c r="I19" s="7">
-        <f t="shared" si="46"/>
-        <v>-0.28486013239376479</v>
-      </c>
-      <c r="J19" s="7">
-        <f t="shared" si="46"/>
-        <v>5.1249199231262178E-2</v>
-      </c>
-      <c r="K19" s="7">
-        <f t="shared" si="46"/>
-        <v>8.955831467535115E-2</v>
-      </c>
-      <c r="L19" s="7">
-        <f t="shared" si="46"/>
-        <v>1.6324233042499255E-2</v>
-      </c>
-      <c r="M19" s="7">
-        <f t="shared" ref="M19:N19" si="47">M17/M18</f>
-        <v>5.6031702147267513E-2</v>
-      </c>
-      <c r="N19" s="7">
+        <v>0.45822226307565056</v>
+      </c>
+      <c r="Z19" s="7">
+        <f t="shared" ref="Z19:AJ19" si="47">Z17/Z18</f>
+        <v>0.36769356892502214</v>
+      </c>
+      <c r="AA19" s="7">
         <f t="shared" si="47"/>
-        <v>0.30545086864601517</v>
-      </c>
-      <c r="O19" s="7">
-        <f t="shared" ref="O19:R19" si="48">O17/O18</f>
-        <v>6.466302367941705E-2</v>
-      </c>
-      <c r="P19" s="7">
-        <f t="shared" si="48"/>
-        <v>5.7036021857923475E-2</v>
-      </c>
-      <c r="Q19" s="7">
-        <f t="shared" si="48"/>
-        <v>7.6287055737705084E-2</v>
-      </c>
-      <c r="R19" s="7">
-        <f t="shared" si="48"/>
-        <v>7.2389312932604671E-2</v>
-      </c>
-      <c r="T19" s="7">
-        <f t="shared" ref="T19:Y19" si="49">T17/T18</f>
-        <v>-0.25570971184631791</v>
-      </c>
-      <c r="U19" s="7">
-        <f t="shared" si="49"/>
-        <v>-0.23916755602988263</v>
-      </c>
-      <c r="V19" s="7">
-        <f t="shared" si="49"/>
-        <v>-0.51664887940234783</v>
-      </c>
-      <c r="W19" s="7">
-        <f t="shared" si="49"/>
-        <v>-0.34450373532550677</v>
-      </c>
-      <c r="X19" s="7">
-        <f t="shared" si="49"/>
-        <v>-0.3211312700106721</v>
-      </c>
-      <c r="Y19" s="7">
-        <f t="shared" si="49"/>
-        <v>0.45822226307565056</v>
-      </c>
-      <c r="Z19" s="7">
-        <f t="shared" ref="Z19:AJ19" si="50">Z17/Z18</f>
-        <v>0.27288556374666839</v>
-      </c>
-      <c r="AA19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.386565635711003</v>
+        <v>0.52639598017163525</v>
       </c>
       <c r="AB19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.4825274020466031</v>
+        <f t="shared" si="47"/>
+        <v>0.64305940953261109</v>
       </c>
       <c r="AC19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.52613694351676865</v>
+        <f t="shared" si="47"/>
+        <v>0.75047455000053087</v>
       </c>
       <c r="AD19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.56656466346941625</v>
+        <f t="shared" si="47"/>
+        <v>0.79798364199012239</v>
       </c>
       <c r="AE19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.59146963645925998</v>
+        <f t="shared" si="47"/>
+        <v>0.82716157709408467</v>
       </c>
       <c r="AF19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.60574118392731024</v>
+        <f t="shared" si="47"/>
+        <v>0.84260486343060903</v>
       </c>
       <c r="AG19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.62031477067398277</v>
+        <f t="shared" si="47"/>
+        <v>0.85806377089091523</v>
       </c>
       <c r="AH19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.63519660356814356</v>
+        <f t="shared" si="47"/>
+        <v>0.87350745493636073</v>
       </c>
       <c r="AI19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.65039301527686832</v>
+        <f t="shared" si="47"/>
+        <v>0.88890132011640843</v>
       </c>
       <c r="AJ19" s="7">
-        <f t="shared" si="50"/>
-        <v>0.66591046679801413</v>
+        <f t="shared" si="47"/>
+        <v>0.90420663146503155</v>
       </c>
     </row>
     <row r="21" spans="2:152" x14ac:dyDescent="0.3">
@@ -3549,116 +3566,116 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9">
-        <f t="shared" ref="G21:L21" si="51">G3/C3-1</f>
+        <f t="shared" ref="G21:L21" si="48">G3/C3-1</f>
         <v>2.1385135135135136</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>2.1438127090301005</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>1.8499999999999996</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>1.0988939492517895</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>0.79198062432723337</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>0.4353191489361703</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" ref="M21:N21" si="52">M3/I3-1</f>
+        <f t="shared" ref="M21:N21" si="49">M3/I3-1</f>
         <v>0.28194222931065038</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>0.15297582145071287</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" ref="O21" si="53">O3/K3-1</f>
+        <f t="shared" ref="O21" si="50">O3/K3-1</f>
         <v>0.14701907193272268</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" ref="P21" si="54">P3/L3-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="P21" si="51">P3/L3-1</f>
+        <v>0.17462199822116808</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" ref="Q21" si="55">Q3/M3-1</f>
+        <f t="shared" ref="Q21" si="52">Q3/M3-1</f>
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" ref="R21" si="53">R3/N3-1</f>
         <v>0.12000000000000011</v>
-      </c>
-      <c r="R21" s="9">
-        <f t="shared" ref="R21" si="56">R3/N3-1</f>
-        <v>0.1100000000000001</v>
       </c>
       <c r="T21" s="9"/>
       <c r="U21" s="9">
-        <f t="shared" ref="U21:AJ21" si="57">U3/T3-1</f>
+        <f t="shared" ref="U21:AJ21" si="54">U3/T3-1</f>
         <v>-0.40233475830318977</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>-2.3383768913342484E-2</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>1.1783098591549295</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>1.6523988102935476</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>0.36892399200429016</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="57"/>
-        <v>0.13096623691146081</v>
+        <f t="shared" si="54"/>
+        <v>0.14468409430871132</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="54"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3667,19 +3684,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:F22" si="58">C5/C3</f>
+        <f t="shared" ref="C22:F22" si="55">C5/C3</f>
         <v>0.80152027027027029</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>0.82073578595317731</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>0.79696969696969699</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>0.67859466493168508</v>
       </c>
       <c r="G22" s="9">
@@ -3687,116 +3704,116 @@
         <v>0.63509149623250816</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:L22" si="59">H5/H3</f>
+        <f t="shared" ref="H22:L22" si="56">H5/H3</f>
         <v>0.61936170212765962</v>
       </c>
       <c r="I22" s="9">
+        <f t="shared" si="56"/>
+        <v>0.6113769271664008</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="56"/>
+        <v>0.60384376937383755</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="56"/>
+        <v>0.60474545727586726</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="56"/>
+        <v>0.61162170174918473</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" ref="M22:N22" si="57">M5/M3</f>
+        <v>0.59579762233895495</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="57"/>
+        <v>0.63193977685172731</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" ref="O22:R22" si="58">O5/O3</f>
+        <v>0.65291961246399577</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="58"/>
+        <v>0.65345784957092379</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="58"/>
+        <v>0.65</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="58"/>
+        <v>0.65</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" ref="T22:AJ22" si="59">T5/T3</f>
+        <v>0.54225583689575807</v>
+      </c>
+      <c r="U22" s="9">
         <f t="shared" si="59"/>
-        <v>0.6113769271664008</v>
-      </c>
-      <c r="J22" s="9">
+        <v>0.48940852819807429</v>
+      </c>
+      <c r="V22" s="9">
         <f t="shared" si="59"/>
-        <v>0.60384376937383755</v>
-      </c>
-      <c r="K22" s="9">
+        <v>0.71042253521126753</v>
+      </c>
+      <c r="W22" s="9">
         <f t="shared" si="59"/>
-        <v>0.60474545727586726</v>
-      </c>
-      <c r="L22" s="9">
+        <v>0.7552049657312816</v>
+      </c>
+      <c r="X22" s="9">
         <f t="shared" si="59"/>
-        <v>0.61162170174918473</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" ref="M22:N22" si="60">M5/M3</f>
-        <v>0.59579762233895495</v>
-      </c>
-      <c r="N22" s="9">
-        <f t="shared" si="60"/>
-        <v>0.63193977685172731</v>
-      </c>
-      <c r="O22" s="9">
-        <f t="shared" ref="O22:R22" si="61">O5/O3</f>
-        <v>0.65291961246399577</v>
-      </c>
-      <c r="P22" s="9">
-        <f t="shared" si="61"/>
-        <v>0.63</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" si="61"/>
-        <v>0.63</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" si="61"/>
-        <v>0.63</v>
-      </c>
-      <c r="T22" s="9">
-        <f t="shared" ref="T22:AJ22" si="62">T5/T3</f>
-        <v>0.54225583689575807</v>
-      </c>
-      <c r="U22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.48940852819807429</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.71042253521126753</v>
-      </c>
-      <c r="W22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.7552049657312816</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" si="62"/>
         <v>0.61513334308419876</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>0.61129710093311485</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63551278575178238</v>
+        <f t="shared" si="59"/>
+        <v>0.65154633850687793</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.65000000000000013</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.62999999999999989</v>
+        <f t="shared" si="59"/>
+        <v>0.65</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.64999999999999991</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.65</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.65</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.65</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.65</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.65</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.65</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="62"/>
-        <v>0.63</v>
+        <f t="shared" si="59"/>
+        <v>0.65</v>
       </c>
       <c r="AM22" t="s">
         <v>50</v>
@@ -3818,48 +3835,48 @@
         <v>2.9736618521665203E-3</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:N23" si="63">H6/D6-1</f>
+        <f t="shared" ref="H23:N23" si="60">H6/D6-1</f>
         <v>-0.13683771380892773</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>-0.27771514468245029</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>-8.9883111648528802E-2</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>2.6260059296908222E-2</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>-0.10101498308361534</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>0.38449531737773168</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>0.16917626217891923</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" ref="O23:O24" si="64">O6/K6-1</f>
+        <f t="shared" ref="O23:O24" si="61">O6/K6-1</f>
         <v>0.12670243499793643</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" ref="P23:P24" si="65">P6/L6-1</f>
-        <v>0.5</v>
+        <f t="shared" ref="P23:P24" si="62">P6/L6-1</f>
+        <v>0.81236559139784958</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" ref="Q23:Q24" si="66">Q6/M6-1</f>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" ref="Q23:Q24" si="63">Q6/M6-1</f>
+        <v>0.35000000000000009</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" ref="R23:R24" si="67">R6/N6-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="R23:R24" si="64">R6/N6-1</f>
+        <v>0.44999999999999996</v>
       </c>
       <c r="T23" s="9"/>
       <c r="U23" s="9">
@@ -3867,63 +3884,63 @@
         <v>2.4361702127659579</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" ref="V23:AJ23" si="68">V6/U6-1</f>
+        <f t="shared" ref="V23:AJ23" si="65">V6/U6-1</f>
         <v>0.89009287925696579</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.35039585039585042</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>-0.12968765793995762</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.1131242740998839</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="68"/>
-        <v>0.19260016694490822</v>
+        <f t="shared" si="65"/>
+        <v>0.41082533388981624</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="68"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="65"/>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="65"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="68"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
       <c r="AD23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM23" t="s">
@@ -3946,120 +3963,120 @@
         <v>0.71763708309779539</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:L24" si="69">H7/D7-1</f>
+        <f t="shared" ref="H24:L24" si="66">H7/D7-1</f>
         <v>0.73920863309352525</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.63003663003663002</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.56795679567956792</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.49448741155175258</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.27138425173585468</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" ref="M24" si="70">M7/I7-1</f>
+        <f t="shared" ref="M24" si="67">M7/I7-1</f>
         <v>0.3079973562458691</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" ref="N24" si="71">N7/J7-1</f>
+        <f t="shared" ref="N24" si="68">N7/J7-1</f>
         <v>0.15717566016073481</v>
       </c>
       <c r="O24" s="9">
+        <f t="shared" si="61"/>
+        <v>0.14159876679145555</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="62"/>
+        <v>0.31245642574947707</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="63"/>
+        <v>0.19647397675593736</v>
+      </c>
+      <c r="R24" s="9">
         <f t="shared" si="64"/>
-        <v>0.14159876679145555</v>
-      </c>
-      <c r="P24" s="9">
-        <f t="shared" si="65"/>
-        <v>0.22564489890773864</v>
-      </c>
-      <c r="Q24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.10924305204648821</v>
-      </c>
-      <c r="R24" s="9">
-        <f t="shared" si="67"/>
-        <v>0.12047722988391696</v>
+        <v>0.20643714654231582</v>
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9">
-        <f t="shared" ref="U24:AJ24" si="72">U7/T7-1</f>
+        <f t="shared" ref="U24:AJ24" si="69">U7/T7-1</f>
         <v>4.1747572815534095E-2</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.44800958594062035</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.62063258550937861</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.65216157948485232</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.29329349953641692</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="72"/>
-        <v>0.14665046996973086</v>
+        <f t="shared" si="69"/>
+        <v>0.21241012160798678</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="72"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="69"/>
+        <v>0.12849554518121176</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="72"/>
-        <v>6.2646715363962047E-2</v>
+        <f t="shared" si="69"/>
+        <v>7.2805221503599249E-2</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="72"/>
-        <v>4.26650300598439E-2</v>
+        <f t="shared" si="69"/>
+        <v>4.9847367936616482E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="72"/>
-        <v>3.2683778089954263E-2</v>
+        <f t="shared" si="69"/>
+        <v>3.3345465259674967E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="72"/>
-        <v>2.2702791767209574E-2</v>
+        <f t="shared" si="69"/>
+        <v>2.3367009375889314E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="72"/>
-        <v>1.2722076777961444E-2</v>
+        <f t="shared" si="69"/>
+        <v>1.338883277005487E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="72"/>
-        <v>1.2741638972021185E-2</v>
+        <f t="shared" si="69"/>
+        <v>1.3410940908049396E-2</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="72"/>
-        <v>1.2761288411425431E-2</v>
+        <f t="shared" si="69"/>
+        <v>1.3433118378506137E-2</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="72"/>
-        <v>1.2781024721108647E-2</v>
+        <f t="shared" si="69"/>
+        <v>1.3455364426691485E-2</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="72"/>
-        <v>1.2800847514211622E-2</v>
+        <f t="shared" si="69"/>
+        <v>1.3477678286521355E-2</v>
       </c>
       <c r="AM24" t="s">
         <v>51</v>
       </c>
       <c r="AN24" s="5">
         <f>NPV(AN23,Z17:EV17)</f>
-        <v>7448.6539452837505</v>
+        <v>10378.739793848174</v>
       </c>
     </row>
     <row r="25" spans="2:152" x14ac:dyDescent="0.3">
@@ -4067,43 +4084,43 @@
         <v>40</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:L25" si="73">(C8-C11)/C7</f>
+        <f t="shared" ref="C25:L25" si="70">(C8-C11)/C7</f>
         <v>0.73459581684567543</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.7279033915724562</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.73432449903038144</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.67704770477047693</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.63880204048050027</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.59698626089525786</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.58017184401850619</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.5872560275545351</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.59997797841885037</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.56809202881710441</v>
       </c>
       <c r="M25" s="9">
@@ -4115,88 +4132,88 @@
         <v>0.60115090782815739</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="74">(O8-O11)/O7</f>
+        <f t="shared" ref="O25:R25" si="71">(O8-O11)/O7</f>
         <v>0.61361882716049376</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="74"/>
-        <v>0.59786782203092559</v>
+        <f t="shared" si="71"/>
+        <v>0.6237273129703409</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="74"/>
-        <v>0.59687859649634289</v>
+        <f t="shared" si="71"/>
+        <v>0.62620076171266259</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="74"/>
-        <v>0.59946791413308254</v>
+        <f t="shared" si="71"/>
+        <v>0.63018382062685863</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" ref="T25:AJ25" si="75">(T8-T11)/T7</f>
+        <f t="shared" ref="T25:AJ25" si="72">(T8-T11)/T7</f>
         <v>0.45256588072122061</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.51471175609106645</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.66917984553144538</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.71490979235220709</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.59843411970742766</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.58762147522701935</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.60181637900991436</v>
+        <f t="shared" si="72"/>
+        <v>0.62379274443686927</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.60792846846659088</v>
+        <f t="shared" si="72"/>
+        <v>0.63204568815649209</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.60860611221422101</v>
+        <f t="shared" si="72"/>
+        <v>0.63488595926052527</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.60929978932830398</v>
+        <f t="shared" si="72"/>
+        <v>0.63709128408862536</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.61000329538675135</v>
+        <f t="shared" si="72"/>
+        <v>0.63784532815612538</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.61071684078457056</v>
+        <f t="shared" si="72"/>
+        <v>0.63860914695191739</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.61144064196478043</v>
+        <f t="shared" si="72"/>
+        <v>0.63938293178173145</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.61216767122274374</v>
+        <f t="shared" si="72"/>
+        <v>0.64015914324770917</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.61289791468101984</v>
+        <f t="shared" si="72"/>
+        <v>0.64093775493420146</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.61363135802583013</v>
+        <f t="shared" si="72"/>
+        <v>0.64171874002824747</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.61436798650572155</v>
+        <f t="shared" si="72"/>
+        <v>0.64250207132210069</v>
       </c>
       <c r="AM25" t="s">
         <v>52</v>
@@ -4219,112 +4236,112 @@
         <v>0.4297924297924296</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:L26" si="76">H9/D9-1</f>
+        <f t="shared" ref="H26:L26" si="73">H9/D9-1</f>
         <v>0.2756539235412474</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0.13550135501355021</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0.25154457193292168</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0.11784799316823236</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>4.258675078864349E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" ref="M26" si="77">M9/I9-1</f>
+        <f t="shared" ref="M26" si="74">M9/I9-1</f>
         <v>0.11137629276054084</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" ref="N26" si="78">N9/J9-1</f>
+        <f t="shared" ref="N26" si="75">N9/J9-1</f>
         <v>5.0775740479548581E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" ref="O26" si="79">O9/K9-1</f>
+        <f t="shared" ref="O26" si="76">O9/K9-1</f>
         <v>0.19327731092436951</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" ref="P26" si="80">P9/L9-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="P26" si="77">P9/L9-1</f>
+        <v>0.15052950075642979</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" ref="Q26" si="81">Q9/M9-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="Q26" si="78">Q9/M9-1</f>
+        <v>0.12999999999999989</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" ref="R26" si="82">R9/N9-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="R26" si="79">R9/N9-1</f>
+        <v>0.12000000000000011</v>
       </c>
       <c r="T26" s="9"/>
       <c r="U26" s="9">
-        <f t="shared" ref="U26:AJ26" si="83">U9/T9-1</f>
+        <f t="shared" ref="U26:AJ26" si="80">U9/T9-1</f>
         <v>0.36406779661016953</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.37226640159045754</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.46794639623324885</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.2617813964964224</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>7.8998826750097839E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="83"/>
-        <v>8.3988764044943931E-2</v>
+        <f t="shared" si="80"/>
+        <v>0.14722906850308082</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AB26" s="9">
+        <f t="shared" si="80"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AC26" s="9">
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AC26" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AD26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM26" t="s">
@@ -4332,7 +4349,7 @@
       </c>
       <c r="AN26" s="5">
         <f>AN24+AN25</f>
-        <v>9271.5539452837511</v>
+        <v>12201.639793848175</v>
       </c>
     </row>
     <row r="27" spans="2:152" x14ac:dyDescent="0.3">
@@ -4340,19 +4357,19 @@
         <v>43</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:F27" si="84">C10/C7</f>
+        <f t="shared" ref="C27:F27" si="81">C10/C7</f>
         <v>0.39033352176370828</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.36973278520041114</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.34927817280758455</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.3126912691269127</v>
       </c>
       <c r="G27" s="9">
@@ -4360,115 +4377,115 @@
         <v>0.28830014809939108</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:L27" si="85">H10/H7</f>
+        <f t="shared" ref="H27:L27" si="82">H10/H7</f>
         <v>0.27005466095435077</v>
       </c>
       <c r="I27" s="9">
+        <f t="shared" si="82"/>
+        <v>0.24679444811632517</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="82"/>
+        <v>0.20057405281285878</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" si="82"/>
+        <v>0.18432063422153711</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="82"/>
+        <v>0.21473390657680688</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" ref="M27:N27" si="83">M10/M7</f>
+        <v>0.21718039413845378</v>
+      </c>
+      <c r="N27" s="9">
+        <f t="shared" si="83"/>
+        <v>0.2275027284452823</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" ref="O27:R27" si="84">O10/O7</f>
+        <v>0.22974537037037038</v>
+      </c>
+      <c r="P27" s="9">
+        <f t="shared" si="84"/>
+        <v>0.23435148295706063</v>
+      </c>
+      <c r="Q27" s="9">
+        <f t="shared" si="84"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="84"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="T27" s="9">
+        <f t="shared" ref="T27:AJ27" si="85">T10/T7</f>
+        <v>0.36920943134535367</v>
+      </c>
+      <c r="U27" s="9">
         <f t="shared" si="85"/>
-        <v>0.24679444811632517</v>
-      </c>
-      <c r="J27" s="9">
+        <v>0.36825988550126482</v>
+      </c>
+      <c r="V27" s="9">
         <f t="shared" si="85"/>
-        <v>0.20057405281285878</v>
-      </c>
-      <c r="K27" s="9">
+        <v>0.39251563074659801</v>
+      </c>
+      <c r="W27" s="9">
         <f t="shared" si="85"/>
-        <v>0.18432063422153711</v>
-      </c>
-      <c r="L27" s="9">
+        <v>0.35050493589016224</v>
+      </c>
+      <c r="X27" s="9">
         <f t="shared" si="85"/>
-        <v>0.21473390657680688</v>
-      </c>
-      <c r="M27" s="9">
-        <f t="shared" ref="M27:N27" si="86">M10/M7</f>
-        <v>0.21718039413845378</v>
-      </c>
-      <c r="N27" s="9">
-        <f t="shared" si="86"/>
-        <v>0.2275027284452823</v>
-      </c>
-      <c r="O27" s="9">
-        <f t="shared" ref="O27:R27" si="87">O10/O7</f>
-        <v>0.22974537037037038</v>
-      </c>
-      <c r="P27" s="9">
-        <f t="shared" si="87"/>
-        <v>0.24</v>
-      </c>
-      <c r="Q27" s="9">
-        <f t="shared" si="87"/>
+        <v>0.2470382198413516</v>
+      </c>
+      <c r="Y27" s="9">
+        <f t="shared" si="85"/>
+        <v>0.21145982688120654</v>
+      </c>
+      <c r="Z27" s="9">
+        <f t="shared" si="85"/>
+        <v>0.23101857592529773</v>
+      </c>
+      <c r="AA27" s="9">
+        <f t="shared" si="85"/>
         <v>0.22</v>
       </c>
-      <c r="R27" s="9">
-        <f t="shared" si="87"/>
-        <v>0.22</v>
-      </c>
-      <c r="T27" s="9">
-        <f t="shared" ref="T27:AJ27" si="88">T10/T7</f>
-        <v>0.36920943134535367</v>
-      </c>
-      <c r="U27" s="9">
-        <f t="shared" si="88"/>
-        <v>0.36825988550126482</v>
-      </c>
-      <c r="V27" s="9">
-        <f t="shared" si="88"/>
-        <v>0.39251563074659801</v>
-      </c>
-      <c r="W27" s="9">
-        <f t="shared" si="88"/>
-        <v>0.35050493589016224</v>
-      </c>
-      <c r="X27" s="9">
-        <f t="shared" si="88"/>
-        <v>0.2470382198413516</v>
-      </c>
-      <c r="Y27" s="9">
-        <f t="shared" si="88"/>
-        <v>0.21145982688120654</v>
-      </c>
-      <c r="Z27" s="9">
-        <f t="shared" si="88"/>
-        <v>0.22722465940259556</v>
-      </c>
-      <c r="AA27" s="9">
-        <f t="shared" si="88"/>
+      <c r="AB27" s="9">
+        <f t="shared" si="85"/>
         <v>0.21</v>
       </c>
-      <c r="AB27" s="9">
-        <f t="shared" si="88"/>
+      <c r="AC27" s="9">
+        <f t="shared" si="85"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AD27" s="9">
+        <f t="shared" si="85"/>
         <v>0.2</v>
       </c>
-      <c r="AC27" s="9">
-        <f t="shared" si="88"/>
+      <c r="AE27" s="9">
+        <f t="shared" si="85"/>
         <v>0.2</v>
       </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="88"/>
+      <c r="AF27" s="9">
+        <f t="shared" si="85"/>
         <v>0.2</v>
       </c>
-      <c r="AE27" s="9">
-        <f t="shared" si="88"/>
+      <c r="AG27" s="9">
+        <f t="shared" si="85"/>
         <v>0.2</v>
       </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="88"/>
+      <c r="AH27" s="9">
+        <f t="shared" si="85"/>
         <v>0.2</v>
       </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="88"/>
+      <c r="AI27" s="9">
+        <f t="shared" si="85"/>
         <v>0.2</v>
       </c>
-      <c r="AH27" s="9">
-        <f t="shared" si="88"/>
-        <v>0.2</v>
-      </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="88"/>
-        <v>0.19999999999999998</v>
-      </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>0.2</v>
       </c>
       <c r="AM27" t="s">
@@ -4476,7 +4493,7 @@
       </c>
       <c r="AN27" s="4">
         <f>AN26/AJ18</f>
-        <v>8.5224321585474314</v>
+        <v>11.022258169691215</v>
       </c>
     </row>
     <row r="28" spans="2:152" x14ac:dyDescent="0.3">
@@ -4488,139 +4505,139 @@
         <v>0.19898247597512719</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" ref="D28:N28" si="89">D11/D7</f>
+        <f t="shared" ref="D28:N28" si="86">D11/D7</f>
         <v>0.20323741007194243</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.17905623787976727</v>
       </c>
       <c r="F28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.1450945094509451</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.13806154352476552</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.13872063820357514</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.12994051553205552</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.11928817451205512</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.1102180136533803</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.12746920752963048</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.12501263264274887</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="86"/>
         <v>0.12719515824982636</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28:R28" si="90">O11/O7</f>
+        <f t="shared" ref="O28:R28" si="87">O11/O7</f>
         <v>0.13069058641975309</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="87"/>
+        <v>0.13315626383355467</v>
+      </c>
+      <c r="Q28" s="9">
+        <f t="shared" si="87"/>
         <v>0.13</v>
       </c>
-      <c r="Q28" s="9">
-        <f t="shared" si="90"/>
+      <c r="R28" s="9">
+        <f t="shared" si="87"/>
         <v>0.13</v>
       </c>
-      <c r="R28" s="9">
-        <f t="shared" si="90"/>
+      <c r="T28" s="9">
+        <f t="shared" ref="T28:AJ28" si="88">T11/T7</f>
+        <v>0.16130374479889042</v>
+      </c>
+      <c r="U28" s="9">
+        <f t="shared" si="88"/>
+        <v>0.23818399680468647</v>
+      </c>
+      <c r="V28" s="9">
+        <f t="shared" si="88"/>
+        <v>0.2363001103346819</v>
+      </c>
+      <c r="W28" s="9">
+        <f t="shared" si="88"/>
+        <v>0.17769204584137072</v>
+      </c>
+      <c r="X28" s="9">
+        <f t="shared" si="88"/>
+        <v>0.13049002438103086</v>
+      </c>
+      <c r="Y28" s="9">
+        <f t="shared" si="88"/>
+        <v>0.12259040943125696</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" si="88"/>
+        <v>0.13093754537437099</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" si="88"/>
         <v>0.13</v>
       </c>
-      <c r="T28" s="9">
-        <f t="shared" ref="T28:AJ28" si="91">T11/T7</f>
-        <v>0.16130374479889042</v>
-      </c>
-      <c r="U28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.23818399680468647</v>
-      </c>
-      <c r="V28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.2363001103346819</v>
-      </c>
-      <c r="W28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.17769204584137072</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.13049002438103086</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12259040943125696</v>
-      </c>
-      <c r="Z28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.13016579773371167</v>
-      </c>
-      <c r="AA28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12000000000000001</v>
-      </c>
       <c r="AB28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.11999999999999998</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.12</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="91"/>
-        <v>0.11999999999999998</v>
+        <f t="shared" si="88"/>
+        <v>0.13</v>
       </c>
       <c r="AM28" t="s">
         <v>55</v>
       </c>
       <c r="AN28" s="4">
         <f>Main!D3</f>
-        <v>13.43</v>
+        <v>24.38</v>
       </c>
     </row>
     <row r="29" spans="2:152" x14ac:dyDescent="0.3">
@@ -4636,112 +4653,112 @@
         <v>-9.3772893772893773E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:L29" si="92">H12/D12-1</f>
+        <f t="shared" ref="H29:L29" si="89">H12/D12-1</f>
         <v>4.2925278219395846E-2</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>-1.3470681458003231E-2</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.16445623342175053</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.17380759902991105</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>0.10518292682926833</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" ref="M29" si="93">M12/I12-1</f>
+        <f t="shared" ref="M29" si="90">M12/I12-1</f>
         <v>0.19598393574297202</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" ref="N29" si="94">N12/J12-1</f>
+        <f t="shared" ref="N29" si="91">N12/J12-1</f>
         <v>0.22171602126044054</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29" si="95">O12/K12-1</f>
+        <f t="shared" ref="O29" si="92">O12/K12-1</f>
         <v>7.713498622589543E-2</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29" si="96">P12/L12-1</f>
+        <f t="shared" ref="P29" si="93">P12/L12-1</f>
+        <v>0.14068965517241394</v>
+      </c>
+      <c r="Q29" s="9">
+        <f t="shared" ref="Q29" si="94">Q12/M12-1</f>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="R29" s="9">
+        <f t="shared" ref="R29" si="95">R12/N12-1</f>
         <v>0.10000000000000009</v>
-      </c>
-      <c r="Q29" s="9">
-        <f t="shared" ref="Q29" si="97">Q12/M12-1</f>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="R29" s="9">
-        <f t="shared" ref="R29" si="98">R12/N12-1</f>
-        <v>8.0000000000000071E-2</v>
       </c>
       <c r="T29" s="9"/>
       <c r="U29" s="9">
-        <f t="shared" ref="U29:AJ29" si="99">U12/T12-1</f>
+        <f t="shared" ref="U29:AJ29" si="96">U12/T12-1</f>
         <v>0.55876559422193028</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>1.0998315080033696</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>6.21865596790383E-3</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>1.8939393939393812E-2</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>0.1739385638818236</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" si="99"/>
-        <v>8.9103333333333312E-2</v>
+        <f t="shared" si="96"/>
+        <v>0.10926333333333327</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM29" s="1" t="s">
@@ -4749,7 +4766,7 @@
       </c>
       <c r="AN29" s="10">
         <f>AN27/AN28-1</f>
-        <v>-0.36541830539483011</v>
+        <v>-0.54789753200610281</v>
       </c>
     </row>
     <row r="30" spans="2:152" x14ac:dyDescent="0.3">
@@ -4757,19 +4774,19 @@
         <v>47</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:F30" si="100">C15/C7</f>
+        <f t="shared" ref="C30:F30" si="97">C15/C7</f>
         <v>-0.30977953646127743</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>-0.24640287769784183</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>-0.16052574876104275</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>-7.0027002700270194E-2</v>
       </c>
       <c r="G30" s="9">
@@ -4777,116 +4794,116 @@
         <v>-5.9568866216883121E-2</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30:L30" si="101">H15/H7</f>
+        <f t="shared" ref="H30:L30" si="98">H15/H7</f>
         <v>-7.2832028364603438E-2</v>
       </c>
       <c r="I30" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.35294117647058837</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="98"/>
+        <v>5.878300803673956E-2</v>
+      </c>
+      <c r="K30" s="9">
+        <f t="shared" si="98"/>
+        <v>0.10372164721427003</v>
+      </c>
+      <c r="L30" s="9">
+        <f t="shared" si="98"/>
+        <v>1.7778294213339478E-2</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" ref="M30:N30" si="99">M15/M7</f>
+        <v>6.4578069732187951E-2</v>
+      </c>
+      <c r="N30" s="9">
+        <f t="shared" si="99"/>
+        <v>5.9331282865363585E-2</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" ref="O30:R30" si="100">O15/O7</f>
+        <v>7.6871141975308574E-2</v>
+      </c>
+      <c r="P30" s="9">
+        <f t="shared" si="100"/>
+        <v>9.9424524125719407E-2</v>
+      </c>
+      <c r="Q30" s="9">
+        <f t="shared" si="100"/>
+        <v>0.11524298701507116</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="100"/>
+        <v>0.11080942919550514</v>
+      </c>
+      <c r="T30" s="9">
+        <f t="shared" ref="T30:AJ30" si="101">T15/T7</f>
+        <v>-0.33245492371705948</v>
+      </c>
+      <c r="U30" s="9">
         <f t="shared" si="101"/>
-        <v>-0.35294117647058837</v>
-      </c>
-      <c r="J30" s="9">
+        <v>-0.43749167887098922</v>
+      </c>
+      <c r="V30" s="9">
         <f t="shared" si="101"/>
-        <v>5.878300803673956E-2</v>
-      </c>
-      <c r="K30" s="9">
+        <v>-0.44253401986024271</v>
+      </c>
+      <c r="W30" s="9">
         <f t="shared" si="101"/>
-        <v>0.10372164721427003</v>
-      </c>
-      <c r="L30" s="9">
+        <v>-0.18092590491319635</v>
+      </c>
+      <c r="X30" s="9">
         <f t="shared" si="101"/>
-        <v>1.7778294213339478E-2</v>
-      </c>
-      <c r="M30" s="9">
-        <f t="shared" ref="M30:N30" si="102">M15/M7</f>
-        <v>6.4578069732187951E-2</v>
-      </c>
-      <c r="N30" s="9">
-        <f t="shared" si="102"/>
-        <v>5.9331282865363585E-2</v>
-      </c>
-      <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="103">O15/O7</f>
-        <v>7.6871141975308574E-2</v>
-      </c>
-      <c r="P30" s="9">
-        <f t="shared" si="103"/>
-        <v>6.74687852558329E-2</v>
-      </c>
-      <c r="Q30" s="9">
-        <f t="shared" si="103"/>
-        <v>8.6721744612772086E-2</v>
-      </c>
-      <c r="R30" s="9">
-        <f t="shared" si="103"/>
-        <v>7.9978571346348074E-2</v>
-      </c>
-      <c r="T30" s="9">
-        <f t="shared" ref="T30:AJ30" si="104">T15/T7</f>
-        <v>-0.33245492371705948</v>
-      </c>
-      <c r="U30" s="9">
-        <f t="shared" si="104"/>
-        <v>-0.43749167887098922</v>
-      </c>
-      <c r="V30" s="9">
-        <f t="shared" si="104"/>
-        <v>-0.44253401986024271</v>
-      </c>
-      <c r="W30" s="9">
-        <f t="shared" si="104"/>
-        <v>-0.18092590491319635</v>
-      </c>
-      <c r="X30" s="9">
-        <f t="shared" si="104"/>
         <v>-0.10346485354211726</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="101"/>
         <v>6.1919175827093692E-2</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" si="104"/>
-        <v>7.7890886103209225E-2</v>
+        <f t="shared" si="101"/>
+        <v>0.10143670670816879</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.10510717531628565</v>
+        <f t="shared" si="101"/>
+        <v>0.13304191206687369</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.12346452726444943</v>
+        <f t="shared" si="101"/>
+        <v>0.15149773244699249</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.12911425868463827</v>
+        <f t="shared" si="101"/>
+        <v>0.16840882295239626</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.13463486454570017</v>
+        <f t="shared" si="101"/>
+        <v>0.17329152443745305</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.13743301267678215</v>
+        <f t="shared" si="101"/>
+        <v>0.17552633048576699</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.13898100143385733</v>
+        <f t="shared" si="101"/>
+        <v>0.17644110476177166</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.1405341239518976</v>
+        <f t="shared" si="101"/>
+        <v>0.17730042793387538</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.14209236502987943</v>
+        <f t="shared" si="101"/>
+        <v>0.17809910678304636</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.1436557084878996</v>
+        <f t="shared" si="101"/>
+        <v>0.17883151299236333</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="104"/>
-        <v>0.14522413716572943</v>
+        <f t="shared" si="101"/>
+        <v>0.17949154659318861</v>
       </c>
       <c r="AM30" t="s">
         <v>57</v>
@@ -4900,19 +4917,19 @@
         <v>34</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="105">C16/C15</f>
+        <f t="shared" ref="C31:F31" si="102">C16/C15</f>
         <v>-7.2992700729927031E-3</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="102"/>
         <v>-1.0427528675703854E-3</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="102"/>
         <v>2.6845637583892638E-3</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="102"/>
         <v>-8.2262210796914981E-2</v>
       </c>
       <c r="G31" s="9">
@@ -4920,115 +4937,115 @@
         <v>4.4198895027624467E-2</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:L31" si="106">H16/H15</f>
+        <f t="shared" ref="H31:L31" si="103">H16/H15</f>
         <v>3.6511156186612527E-2</v>
       </c>
       <c r="I31" s="9">
+        <f t="shared" si="103"/>
+        <v>7.4906367041198472E-4</v>
+      </c>
+      <c r="J31" s="9">
+        <f t="shared" si="103"/>
+        <v>6.2499999999999813E-2</v>
+      </c>
+      <c r="K31" s="9">
+        <f t="shared" si="103"/>
+        <v>6.5817409766454324E-2</v>
+      </c>
+      <c r="L31" s="9">
+        <f t="shared" si="103"/>
+        <v>-0.13725490196078471</v>
+      </c>
+      <c r="M31" s="9">
+        <f t="shared" ref="M31:N31" si="104">M16/M15</f>
+        <v>4.8513302034428815E-2</v>
+      </c>
+      <c r="N31" s="9">
+        <f t="shared" si="104"/>
+        <v>-4.5568561872909736</v>
+      </c>
+      <c r="O31" s="9">
+        <f t="shared" ref="O31:R31" si="105">O16/O15</f>
+        <v>0.10915934755332506</v>
+      </c>
+      <c r="P31" s="9">
+        <f t="shared" si="105"/>
+        <v>0.13268032056990198</v>
+      </c>
+      <c r="Q31" s="9">
+        <f t="shared" si="105"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="105"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="T31" s="9">
+        <f t="shared" ref="T31:AJ31" si="106">T16/T15</f>
+        <v>4.1718815185648754E-4</v>
+      </c>
+      <c r="U31" s="9">
         <f t="shared" si="106"/>
-        <v>7.4906367041198472E-4</v>
-      </c>
-      <c r="J31" s="9">
+        <v>0.31801582471089468</v>
+      </c>
+      <c r="V31" s="9">
         <f t="shared" si="106"/>
-        <v>6.2499999999999813E-2</v>
-      </c>
-      <c r="K31" s="9">
+        <v>-5.8175773945564101E-3</v>
+      </c>
+      <c r="W31" s="9">
         <f t="shared" si="106"/>
-        <v>6.5817409766454324E-2</v>
-      </c>
-      <c r="L31" s="9">
+        <v>-1.2229539040451558E-2</v>
+      </c>
+      <c r="X31" s="9">
         <f t="shared" si="106"/>
-        <v>-0.13725490196078471</v>
-      </c>
-      <c r="M31" s="9">
-        <f t="shared" ref="M31:N31" si="107">M16/M15</f>
-        <v>4.8513302034428815E-2</v>
-      </c>
-      <c r="N31" s="9">
-        <f t="shared" si="107"/>
-        <v>-4.5568561872909736</v>
-      </c>
-      <c r="O31" s="9">
-        <f t="shared" ref="O31:R31" si="108">O16/O15</f>
-        <v>0.10915934755332506</v>
-      </c>
-      <c r="P31" s="9">
-        <f t="shared" si="108"/>
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="Q31" s="9">
-        <f t="shared" si="108"/>
-        <v>0.12</v>
-      </c>
-      <c r="R31" s="9">
-        <f t="shared" si="108"/>
-        <v>0.12</v>
-      </c>
-      <c r="T31" s="9">
-        <f t="shared" ref="T31:AJ31" si="109">T16/T15</f>
-        <v>4.1718815185648754E-4</v>
-      </c>
-      <c r="U31" s="9">
-        <f t="shared" si="109"/>
-        <v>0.31801582471089468</v>
-      </c>
-      <c r="V31" s="9">
-        <f t="shared" si="109"/>
-        <v>-5.8175773945564101E-3</v>
-      </c>
-      <c r="W31" s="9">
-        <f t="shared" si="109"/>
-        <v>-1.2229539040451558E-2</v>
-      </c>
-      <c r="X31" s="9">
-        <f t="shared" si="109"/>
         <v>1.3275804845668793E-3</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>-1.1376500857632921</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" si="109"/>
-        <v>0.11743142254954125</v>
+        <f t="shared" si="106"/>
+        <v>0.12120903800818253</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>0.15</v>
       </c>
     </row>
@@ -5041,132 +5058,132 @@
         <v>-0.31204070096099479</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" ref="D32:AJ32" si="110">D17/D7</f>
+        <f t="shared" ref="D32:AJ32" si="107">D17/D7</f>
         <v>-0.24665981500513884</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-0.16009480715363056</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-7.5787578757875951E-2</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-5.6935988152048499E-2</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-7.017284680159562E-2</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-0.35267680105750182</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>5.5109070034443347E-2</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>9.68949570579168E-2</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>2.0218452242621376E-2</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>6.1445174330469907E-2</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>0.32969540629030653</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>6.8479938271604868E-2</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="110"/>
-        <v>5.9372531025132944E-2</v>
+        <f t="shared" si="107"/>
+        <v>8.6232846392209003E-2</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="110"/>
-        <v>7.6315135259239442E-2</v>
+        <f t="shared" si="107"/>
+        <v>0.10141382857326263</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="110"/>
-        <v>7.0381142784786313E-2</v>
+        <f t="shared" si="107"/>
+        <v>9.7512297692044531E-2</v>
       </c>
       <c r="T32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-0.33231622746185835</v>
       </c>
       <c r="U32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-0.29836240181067769</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-0.44510849577050388</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-0.18313854533076129</v>
       </c>
       <c r="X32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-0.10332749562171618</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>0.13236153151717919</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" si="110"/>
-        <v>6.8744048544465072E-2</v>
+        <f t="shared" si="107"/>
+        <v>8.9141661069353506E-2</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="110"/>
-        <v>8.9341099018842796E-2</v>
+        <f t="shared" si="107"/>
+        <v>0.11308562525684264</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.10494484817478203</v>
+        <f t="shared" si="107"/>
+        <v>0.12877307257994361</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.10974711988194252</v>
+        <f t="shared" si="107"/>
+        <v>0.14314749950953681</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.11443963486384516</v>
+        <f t="shared" si="107"/>
+        <v>0.1472977957718351</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.11681806077526483</v>
+        <f t="shared" si="107"/>
+        <v>0.14919738091290194</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.11813385121877873</v>
+        <f t="shared" si="107"/>
+        <v>0.14997493904750592</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.11945400535911295</v>
+        <f t="shared" si="107"/>
+        <v>0.15070536374379409</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.12077851027539752</v>
+        <f t="shared" si="107"/>
+        <v>0.1513842407655894</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.12210735221471467</v>
+        <f t="shared" si="107"/>
+        <v>0.15200678604350884</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="110"/>
-        <v>0.12344051659087002</v>
+        <f t="shared" si="107"/>
+        <v>0.15256781460421032</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SOFI.xlsx
+++ b/Financial Analysis/SOFI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B5EE6F-17AC-493A-B50D-0FF5EE8F0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839387FA-D1CC-4510-8BF2-CDFC79C68BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{42D26EF4-2D58-4793-8C51-B0C7F6F93649}"/>
   </bookViews>
@@ -744,14 +744,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>24.38</v>
+        <v>27.35</v>
       </c>
       <c r="E3" s="3">
-        <v>45867</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45867</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45965</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>26988.66</v>
+        <v>30276.45</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -817,7 +817,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>25165.759999999998</v>
+        <v>28453.55</v>
       </c>
     </row>
   </sheetData>
@@ -1104,7 +1104,7 @@
         <v>274.60000000000002</v>
       </c>
       <c r="Q4" s="5">
-        <f t="shared" ref="P4:R4" si="1">Q3-Q5</f>
+        <f t="shared" ref="Q4:R4" si="1">Q3-Q5</f>
         <v>288.63659999999993</v>
       </c>
       <c r="R4" s="5">
@@ -1995,7 +1995,7 @@
         <v>150.4</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" ref="P11:R11" si="19">Q7*0.13</f>
+        <f t="shared" ref="Q11:R11" si="19">Q7*0.13</f>
         <v>153.90843000000001</v>
       </c>
       <c r="R11" s="5">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AN28" s="4">
         <f>Main!D3</f>
-        <v>24.38</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="29" spans="2:152" x14ac:dyDescent="0.3">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="AN29" s="10">
         <f>AN27/AN28-1</f>
-        <v>-0.54789753200610281</v>
+        <v>-0.59699238867673809</v>
       </c>
     </row>
     <row r="30" spans="2:152" x14ac:dyDescent="0.3">

--- a/Financial Analysis/SOFI.xlsx
+++ b/Financial Analysis/SOFI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839387FA-D1CC-4510-8BF2-CDFC79C68BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE3D914-9752-4E3A-A4A0-44535737F0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{42D26EF4-2D58-4793-8C51-B0C7F6F93649}"/>
   </bookViews>
@@ -217,10 +217,10 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Q225 8K</t>
-  </si>
-  <si>
-    <t>Heavily overvalued</t>
+    <t>Q325 8K</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -320,13 +320,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -344,7 +344,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10683240" y="7620"/>
+          <a:off x="11292840" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -744,17 +744,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>27.35</v>
+        <v>31.37</v>
       </c>
       <c r="E3" s="3">
-        <v>45937</v>
+        <v>45959</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45959</v>
       </c>
       <c r="G3" s="3">
-        <v>45965</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -762,8 +762,8 @@
         <v>1</v>
       </c>
       <c r="D4" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f>1171.2</f>
+        <v>1171.2</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>63</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>30276.45</v>
+        <v>36740.544000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -783,11 +783,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="5">
-        <f>2085.7+630.4+2153.5</f>
-        <v>4869.6000000000004</v>
+        <f>3246.4+500.1+2512.4</f>
+        <v>6258.9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -795,11 +795,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="5">
-        <f>3046.1+0.6</f>
-        <v>3046.7</v>
+        <f>2713.9+0.5</f>
+        <v>2714.4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -808,7 +808,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>1822.9000000000005</v>
+        <v>3544.4999999999995</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -817,7 +817,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>28453.55</v>
+        <v>33196.044000000002</v>
       </c>
     </row>
   </sheetData>
@@ -984,12 +984,11 @@
         <v>792.4</v>
       </c>
       <c r="Q3" s="5">
-        <f>M3*1.14</f>
-        <v>824.67599999999993</v>
+        <v>891.6</v>
       </c>
       <c r="R3" s="5">
-        <f>N3*1.12</f>
-        <v>833.16800000000001</v>
+        <f>N3*1.25</f>
+        <v>929.875</v>
       </c>
       <c r="T3" s="5">
         <v>608.20000000000005</v>
@@ -1014,47 +1013,47 @@
       </c>
       <c r="Z3" s="5">
         <f>SUM(O3:R3)</f>
-        <v>3214.0439999999999</v>
+        <v>3377.6749999999997</v>
       </c>
       <c r="AA3" s="5">
-        <f>Z3*1.09</f>
-        <v>3503.3079600000001</v>
+        <f>Z3*1.15</f>
+        <v>3884.3262499999992</v>
       </c>
       <c r="AB3" s="5">
-        <f>AA3*1.06</f>
-        <v>3713.5064376000005</v>
+        <f>AA3*1.1</f>
+        <v>4272.7588749999995</v>
       </c>
       <c r="AC3" s="5">
-        <f>AB3*1.04</f>
-        <v>3862.0466951040007</v>
+        <f>AB3*1.07</f>
+        <v>4571.8519962499995</v>
       </c>
       <c r="AD3" s="5">
-        <f>AC3*1.03</f>
-        <v>3977.9080959571206</v>
+        <f>AC3*1.04</f>
+        <v>4754.7260760999998</v>
       </c>
       <c r="AE3" s="5">
-        <f>AD3*1.02</f>
-        <v>4057.4662578762632</v>
+        <f>AD3*1.03</f>
+        <v>4897.3678583829997</v>
       </c>
       <c r="AF3" s="5">
-        <f>AE3*1.01</f>
-        <v>4098.040920455026</v>
+        <f>AE3*1.02</f>
+        <v>4995.3152155506596</v>
       </c>
       <c r="AG3" s="5">
-        <f t="shared" ref="AG3:AJ3" si="0">AF3*1.01</f>
-        <v>4139.0213296595766</v>
+        <f t="shared" ref="AG3:AJ3" si="0">AF3*1.02</f>
+        <v>5095.2215198616732</v>
       </c>
       <c r="AH3" s="5">
         <f t="shared" si="0"/>
-        <v>4180.4115429561725</v>
+        <v>5197.1259502589064</v>
       </c>
       <c r="AI3" s="5">
         <f t="shared" si="0"/>
-        <v>4222.2156583857341</v>
+        <v>5301.0684692640843</v>
       </c>
       <c r="AJ3" s="5">
         <f t="shared" si="0"/>
-        <v>4264.4378149695913</v>
+        <v>5407.0898386493664</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
@@ -1104,12 +1103,11 @@
         <v>274.60000000000002</v>
       </c>
       <c r="Q4" s="5">
-        <f t="shared" ref="Q4:R4" si="1">Q3-Q5</f>
-        <v>288.63659999999993</v>
+        <v>306.39999999999998</v>
       </c>
       <c r="R4" s="5">
-        <f t="shared" si="1"/>
-        <v>291.60879999999997</v>
+        <f t="shared" ref="R4" si="1">R3-R5</f>
+        <v>316.15750000000003</v>
       </c>
       <c r="T4" s="5">
         <v>278.39999999999998</v>
@@ -1134,47 +1132,47 @@
       </c>
       <c r="Z4" s="5">
         <f>SUM(O4:R4)</f>
-        <v>1119.9454000000001</v>
+        <v>1162.2575000000002</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" ref="AA4:AJ4" si="2">AA3-AA5</f>
-        <v>1226.1577859999998</v>
+        <v>1320.6709249999994</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="2"/>
-        <v>1299.7272531600001</v>
+        <v>1410.0104287499998</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" si="2"/>
-        <v>1351.7163432864004</v>
+        <v>1508.7111587624995</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="2"/>
-        <v>1392.2678335849923</v>
+        <v>1569.0596051129996</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="2"/>
-        <v>1420.1131902566922</v>
+        <v>1616.1313932663898</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" si="2"/>
-        <v>1434.3143221592591</v>
+        <v>1648.4540211317176</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="2"/>
-        <v>1448.6574653808516</v>
+        <v>1681.4231015543519</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="2"/>
-        <v>1463.1440400346601</v>
+        <v>1715.051563585439</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="2"/>
-        <v>1477.775480435007</v>
+        <v>1749.3525948571478</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="2"/>
-        <v>1492.553235239357</v>
+        <v>1784.3396467542907</v>
       </c>
     </row>
     <row r="5" spans="2:36" x14ac:dyDescent="0.3">
@@ -1182,7 +1180,7 @@
         <v>37</v>
       </c>
       <c r="C5" s="5">
-        <f t="shared" ref="C5:P5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:Q5" si="3">C3-C4</f>
         <v>94.9</v>
       </c>
       <c r="D5" s="5">
@@ -1238,12 +1236,12 @@
         <v>517.79999999999995</v>
       </c>
       <c r="Q5" s="5">
-        <f>Q3*0.65</f>
-        <v>536.0394</v>
+        <f t="shared" si="3"/>
+        <v>585.20000000000005</v>
       </c>
       <c r="R5" s="5">
-        <f>R3*0.65</f>
-        <v>541.55920000000003</v>
+        <f>R3*0.66</f>
+        <v>613.71749999999997</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" ref="T5:Y5" si="4">T3-T4</f>
@@ -1271,47 +1269,47 @@
       </c>
       <c r="Z5" s="5">
         <f>SUM(O5:R5)</f>
-        <v>2094.0985999999998</v>
+        <v>2215.4174999999996</v>
       </c>
       <c r="AA5" s="5">
-        <f>AA3*0.65</f>
-        <v>2277.1501740000003</v>
+        <f>AA3*0.66</f>
+        <v>2563.6553249999997</v>
       </c>
       <c r="AB5" s="5">
-        <f t="shared" ref="AB5:AJ5" si="5">AB3*0.65</f>
-        <v>2413.7791844400003</v>
+        <f>AB3*0.67</f>
+        <v>2862.7484462499997</v>
       </c>
       <c r="AC5" s="5">
-        <f t="shared" si="5"/>
-        <v>2510.3303518176003</v>
+        <f t="shared" ref="AC5:AJ5" si="5">AC3*0.67</f>
+        <v>3063.1408374875</v>
       </c>
       <c r="AD5" s="5">
         <f t="shared" si="5"/>
-        <v>2585.6402623721283</v>
+        <v>3185.6664709870001</v>
       </c>
       <c r="AE5" s="5">
         <f t="shared" si="5"/>
-        <v>2637.353067619571</v>
+        <v>3281.2364651166099</v>
       </c>
       <c r="AF5" s="5">
         <f t="shared" si="5"/>
-        <v>2663.726598295767</v>
+        <v>3346.861194418942</v>
       </c>
       <c r="AG5" s="5">
         <f t="shared" si="5"/>
-        <v>2690.363864278725</v>
+        <v>3413.7984183073213</v>
       </c>
       <c r="AH5" s="5">
         <f t="shared" si="5"/>
-        <v>2717.2675029215125</v>
+        <v>3482.0743866734674</v>
       </c>
       <c r="AI5" s="5">
         <f t="shared" si="5"/>
-        <v>2744.440177950727</v>
+        <v>3551.7158744069366</v>
       </c>
       <c r="AJ5" s="5">
         <f t="shared" si="5"/>
-        <v>2771.8845797302342</v>
+        <v>3622.7501918950757</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
@@ -1361,12 +1359,11 @@
         <v>337.1</v>
       </c>
       <c r="Q6" s="5">
-        <f>M6*1.35</f>
-        <v>359.23500000000007</v>
+        <v>376.5</v>
       </c>
       <c r="R6" s="5">
-        <f>N6*1.45</f>
-        <v>382.8</v>
+        <f>N6*1.5</f>
+        <v>396</v>
       </c>
       <c r="T6" s="5">
         <v>112.8</v>
@@ -1391,47 +1388,47 @@
       </c>
       <c r="Z6" s="5">
         <f>SUM(O6:R6)</f>
-        <v>1352.135</v>
+        <v>1382.6</v>
       </c>
       <c r="AA6" s="5">
-        <f>Z6*1.22</f>
-        <v>1649.6046999999999</v>
+        <f>Z6*1.3</f>
+        <v>1797.3799999999999</v>
       </c>
       <c r="AB6" s="5">
-        <f>AA6*1.1</f>
-        <v>1814.5651700000001</v>
+        <f>AA6*1.2</f>
+        <v>2156.8559999999998</v>
       </c>
       <c r="AC6" s="5">
-        <f>AB6*1.07</f>
-        <v>1941.5847319000002</v>
+        <f>AB6*1.15</f>
+        <v>2480.3843999999995</v>
       </c>
       <c r="AD6" s="5">
-        <f>AC6*1.04</f>
-        <v>2019.2481211760003</v>
+        <f>AC6*1.1</f>
+        <v>2728.4228399999997</v>
       </c>
       <c r="AE6" s="5">
-        <f>AD6*1.03</f>
-        <v>2079.8255648112804</v>
+        <f>AD6*1.07</f>
+        <v>2919.4124388</v>
       </c>
       <c r="AF6" s="5">
-        <f>AE6*1.02</f>
-        <v>2121.4220761075062</v>
+        <f>AE6*1.05</f>
+        <v>3065.38306074</v>
       </c>
       <c r="AG6" s="5">
-        <f t="shared" ref="AG6:AJ6" si="6">AF6*1.02</f>
-        <v>2163.8505176296562</v>
+        <f>AF6*1.03</f>
+        <v>3157.3445525622001</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" si="6"/>
-        <v>2207.1275279822494</v>
+        <f t="shared" ref="AH6:AJ6" si="6">AG6*1.03</f>
+        <v>3252.0648891390661</v>
       </c>
       <c r="AI6" s="5">
         <f t="shared" si="6"/>
-        <v>2251.2700785418942</v>
+        <v>3349.6268358132379</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="6"/>
-        <v>2296.2954801127321</v>
+        <v>3450.115640887635</v>
       </c>
     </row>
     <row r="7" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1496,11 +1493,11 @@
       </c>
       <c r="Q7" s="8">
         <f t="shared" si="9"/>
-        <v>1183.9110000000001</v>
+        <v>1268.0999999999999</v>
       </c>
       <c r="R7" s="8">
         <f t="shared" si="9"/>
-        <v>1215.9680000000001</v>
+        <v>1325.875</v>
       </c>
       <c r="T7" s="8">
         <f t="shared" ref="T7:Y7" si="10">T3+T6</f>
@@ -1528,47 +1525,47 @@
       </c>
       <c r="Z7" s="8">
         <f t="shared" ref="Z7:AJ7" si="11">Z3+Z6</f>
-        <v>4566.1790000000001</v>
+        <v>4760.2749999999996</v>
       </c>
       <c r="AA7" s="8">
         <f t="shared" si="11"/>
-        <v>5152.91266</v>
+        <v>5681.7062499999993</v>
       </c>
       <c r="AB7" s="8">
         <f t="shared" si="11"/>
-        <v>5528.0716076000008</v>
+        <v>6429.6148749999993</v>
       </c>
       <c r="AC7" s="8">
         <f t="shared" si="11"/>
-        <v>5803.6314270040011</v>
+        <v>7052.2363962499985</v>
       </c>
       <c r="AD7" s="8">
         <f t="shared" si="11"/>
-        <v>5997.1562171331207</v>
+        <v>7483.148916099999</v>
       </c>
       <c r="AE7" s="8">
         <f t="shared" si="11"/>
-        <v>6137.2918226875436</v>
+        <v>7816.7802971829997</v>
       </c>
       <c r="AF7" s="8">
         <f t="shared" si="11"/>
-        <v>6219.4629965625318</v>
+        <v>8060.6982762906591</v>
       </c>
       <c r="AG7" s="8">
         <f t="shared" si="11"/>
-        <v>6302.8718472892324</v>
+        <v>8252.5660724238733</v>
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="11"/>
-        <v>6387.5390709384219</v>
+        <v>8449.190839397972</v>
       </c>
       <c r="AI7" s="8">
         <f t="shared" si="11"/>
-        <v>6473.4857369276287</v>
+        <v>8650.6953050773227</v>
       </c>
       <c r="AJ7" s="8">
         <f t="shared" si="11"/>
-        <v>6560.7332950823238</v>
+        <v>8857.2054795370022</v>
       </c>
     </row>
     <row r="8" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1633,11 +1630,11 @@
       </c>
       <c r="Q8" s="8">
         <f t="shared" si="14"/>
-        <v>895.27440000000001</v>
+        <v>961.7</v>
       </c>
       <c r="R8" s="8">
         <f t="shared" si="14"/>
-        <v>924.3592000000001</v>
+        <v>1009.7175</v>
       </c>
       <c r="T8" s="8">
         <f t="shared" ref="T8:Y8" si="15">T5+T6</f>
@@ -1665,47 +1662,47 @@
       </c>
       <c r="Z8" s="8">
         <f t="shared" ref="Z8:AJ8" si="16">Z5+Z6</f>
-        <v>3446.2335999999996</v>
+        <v>3598.0174999999995</v>
       </c>
       <c r="AA8" s="8">
         <f t="shared" si="16"/>
-        <v>3926.7548740000002</v>
+        <v>4361.0353249999998</v>
       </c>
       <c r="AB8" s="8">
         <f t="shared" si="16"/>
-        <v>4228.3443544400006</v>
+        <v>5019.6044462499995</v>
       </c>
       <c r="AC8" s="8">
         <f t="shared" si="16"/>
-        <v>4451.9150837176003</v>
+        <v>5543.5252374874999</v>
       </c>
       <c r="AD8" s="8">
         <f t="shared" si="16"/>
-        <v>4604.8883835481283</v>
+        <v>5914.0893109869994</v>
       </c>
       <c r="AE8" s="8">
         <f t="shared" si="16"/>
-        <v>4717.1786324308514</v>
+        <v>6200.6489039166099</v>
       </c>
       <c r="AF8" s="8">
         <f t="shared" si="16"/>
-        <v>4785.1486744032736</v>
+        <v>6412.244255158942</v>
       </c>
       <c r="AG8" s="8">
         <f t="shared" si="16"/>
-        <v>4854.2143819083813</v>
+        <v>6571.1429708695214</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="16"/>
-        <v>4924.3950309037618</v>
+        <v>6734.139275812533</v>
       </c>
       <c r="AI8" s="8">
         <f t="shared" si="16"/>
-        <v>4995.7102564926208</v>
+        <v>6901.3427102201749</v>
       </c>
       <c r="AJ8" s="8">
         <f t="shared" si="16"/>
-        <v>5068.1800598429663</v>
+        <v>7072.8658327827106</v>
       </c>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.3">
@@ -1755,12 +1752,11 @@
         <v>152.1</v>
       </c>
       <c r="Q9" s="5">
-        <f>M9*1.13</f>
-        <v>157.86099999999996</v>
+        <v>167.1</v>
       </c>
       <c r="R9" s="5">
-        <f>N9*1.12</f>
-        <v>166.88000000000002</v>
+        <f>N9*1.18</f>
+        <v>175.82</v>
       </c>
       <c r="T9" s="5">
         <v>147.5</v>
@@ -1785,47 +1781,47 @@
       </c>
       <c r="Z9" s="5">
         <f>SUM(O9:R9)</f>
-        <v>633.04099999999994</v>
+        <v>651.22</v>
       </c>
       <c r="AA9" s="5">
-        <f>Z9*1.07</f>
-        <v>677.35387000000003</v>
+        <f>Z9*1.11</f>
+        <v>722.85420000000011</v>
       </c>
       <c r="AB9" s="5">
-        <f>AA9*1.05</f>
-        <v>711.22156350000012</v>
+        <f>AA9*1.07</f>
+        <v>773.45399400000019</v>
       </c>
       <c r="AC9" s="5">
-        <f>AB9*1.03</f>
-        <v>732.55821040500018</v>
+        <f>AB9*1.04</f>
+        <v>804.39215376000027</v>
       </c>
       <c r="AD9" s="5">
-        <f>AC9*1.01</f>
-        <v>739.88379250905018</v>
+        <f>AC9*1.03</f>
+        <v>828.52391837280027</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" ref="AE9:AJ9" si="17">AD9*1.01</f>
-        <v>747.28263043414074</v>
+        <f>AD9*1.02</f>
+        <v>845.09439674025634</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" si="17"/>
-        <v>754.75545673848217</v>
+        <f t="shared" ref="AF9:AJ9" si="17">AE9*1.02</f>
+        <v>861.99628467506147</v>
       </c>
       <c r="AG9" s="5">
         <f t="shared" si="17"/>
-        <v>762.30301130586702</v>
+        <v>879.23621036856275</v>
       </c>
       <c r="AH9" s="5">
         <f t="shared" si="17"/>
-        <v>769.92604141892571</v>
+        <v>896.82093457593407</v>
       </c>
       <c r="AI9" s="5">
         <f t="shared" si="17"/>
-        <v>777.62530183311492</v>
+        <v>914.7573532674528</v>
       </c>
       <c r="AJ9" s="5">
         <f t="shared" si="17"/>
-        <v>785.40155485144612</v>
+        <v>933.05250033280186</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
@@ -1875,12 +1871,11 @@
         <v>264.7</v>
       </c>
       <c r="Q10" s="5">
-        <f>Q7*0.23</f>
-        <v>272.29953</v>
+        <v>286.89999999999998</v>
       </c>
       <c r="R10" s="5">
         <f>R7*0.23</f>
-        <v>279.67264</v>
+        <v>304.95125000000002</v>
       </c>
       <c r="T10" s="5">
         <v>266.2</v>
@@ -1905,47 +1900,47 @@
       </c>
       <c r="Z10" s="5">
         <f>SUM(O10:R10)</f>
-        <v>1054.8721700000001</v>
+        <v>1094.75125</v>
       </c>
       <c r="AA10" s="5">
         <f>AA7*0.22</f>
-        <v>1133.6407852</v>
+        <v>1249.9753749999998</v>
       </c>
       <c r="AB10" s="5">
         <f>AB7*0.21</f>
-        <v>1160.8950375960001</v>
+        <v>1350.2191237499999</v>
       </c>
       <c r="AC10" s="5">
         <f>AC7*0.2</f>
-        <v>1160.7262854008002</v>
+        <v>1410.4472792499998</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" ref="AD10:AJ10" si="18">AD7*0.2</f>
-        <v>1199.4312434266242</v>
+        <v>1496.6297832199998</v>
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="18"/>
-        <v>1227.4583645375087</v>
+        <v>1563.3560594365999</v>
       </c>
       <c r="AF10" s="5">
         <f t="shared" si="18"/>
-        <v>1243.8925993125065</v>
+        <v>1612.1396552581318</v>
       </c>
       <c r="AG10" s="5">
         <f t="shared" si="18"/>
-        <v>1260.5743694578466</v>
+        <v>1650.5132144847748</v>
       </c>
       <c r="AH10" s="5">
         <f t="shared" si="18"/>
-        <v>1277.5078141876845</v>
+        <v>1689.8381678795945</v>
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="18"/>
-        <v>1294.6971473855258</v>
+        <v>1730.1390610154647</v>
       </c>
       <c r="AJ10" s="5">
         <f t="shared" si="18"/>
-        <v>1312.1466590164648</v>
+        <v>1771.4410959074005</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
@@ -1995,12 +1990,11 @@
         <v>150.4</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" ref="Q11:R11" si="19">Q7*0.13</f>
-        <v>153.90843000000001</v>
+        <v>161.4</v>
       </c>
       <c r="R11" s="5">
-        <f t="shared" si="19"/>
-        <v>158.07584000000003</v>
+        <f t="shared" ref="R11" si="19">R7*0.13</f>
+        <v>172.36375000000001</v>
       </c>
       <c r="T11" s="5">
         <v>116.3</v>
@@ -2025,47 +2019,47 @@
       </c>
       <c r="Z11" s="5">
         <f>SUM(O11:R11)</f>
-        <v>597.88427000000001</v>
+        <v>619.66374999999994</v>
       </c>
       <c r="AA11" s="5">
         <f>AA7*0.13</f>
-        <v>669.87864580000007</v>
+        <v>738.62181249999992</v>
       </c>
       <c r="AB11" s="5">
         <f t="shared" ref="AB11:AJ11" si="20">AB7*0.13</f>
-        <v>718.64930898800014</v>
+        <v>835.84993374999999</v>
       </c>
       <c r="AC11" s="5">
         <f t="shared" si="20"/>
-        <v>754.47208551052017</v>
+        <v>916.79073151249986</v>
       </c>
       <c r="AD11" s="5">
         <f t="shared" si="20"/>
-        <v>779.6303082273057</v>
+        <v>972.8093590929999</v>
       </c>
       <c r="AE11" s="5">
         <f t="shared" si="20"/>
-        <v>797.84793694938071</v>
+        <v>1016.18143863379</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" si="20"/>
-        <v>808.53018955312916</v>
+        <v>1047.8907759177857</v>
       </c>
       <c r="AG11" s="5">
         <f t="shared" si="20"/>
-        <v>819.37334014760029</v>
+        <v>1072.8335894151035</v>
       </c>
       <c r="AH11" s="5">
         <f t="shared" si="20"/>
-        <v>830.38007922199483</v>
+        <v>1098.3948091217364</v>
       </c>
       <c r="AI11" s="5">
         <f t="shared" si="20"/>
-        <v>841.55314580059178</v>
+        <v>1124.5903896600521</v>
       </c>
       <c r="AJ11" s="5">
         <f t="shared" si="20"/>
-        <v>852.89532836070214</v>
+        <v>1151.4367123398104</v>
       </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.3">
@@ -2115,12 +2109,11 @@
         <v>165.4</v>
       </c>
       <c r="Q12" s="5">
-        <f>M12*1.12</f>
-        <v>166.76800000000003</v>
+        <v>188.4</v>
       </c>
       <c r="R12" s="5">
-        <f>N12*1.1</f>
-        <v>176.99</v>
+        <f>N12*1.3</f>
+        <v>209.17000000000002</v>
       </c>
       <c r="T12" s="5">
         <v>152.30000000000001</v>
@@ -2145,47 +2138,47 @@
       </c>
       <c r="Z12" s="5">
         <f>SUM(O12:R12)</f>
-        <v>665.55799999999999</v>
+        <v>719.37000000000012</v>
       </c>
       <c r="AA12" s="5">
         <f>Z12*1.09</f>
-        <v>725.4582200000001</v>
+        <v>784.11330000000021</v>
       </c>
       <c r="AB12" s="5">
         <f>AA12*1.05</f>
-        <v>761.73113100000012</v>
+        <v>823.31896500000028</v>
       </c>
       <c r="AC12" s="5">
         <f>AB12*1.03</f>
-        <v>784.58306493000009</v>
+        <v>848.01853395000035</v>
       </c>
       <c r="AD12" s="5">
         <f>AC12*1.02</f>
-        <v>800.27472622860012</v>
+        <v>864.97890462900034</v>
       </c>
       <c r="AE12" s="5">
         <f t="shared" ref="AE12" si="21">AD12*1.02</f>
-        <v>816.2802207531721</v>
+        <v>882.27848272158042</v>
       </c>
       <c r="AF12" s="5">
         <f>AE12*1.01</f>
-        <v>824.44302296070384</v>
+        <v>891.10126754879627</v>
       </c>
       <c r="AG12" s="5">
         <f t="shared" ref="AG12:AJ12" si="22">AF12*1.01</f>
-        <v>832.68745319031086</v>
+        <v>900.01228022428427</v>
       </c>
       <c r="AH12" s="5">
         <f t="shared" si="22"/>
-        <v>841.01432772221403</v>
+        <v>909.01240302652707</v>
       </c>
       <c r="AI12" s="5">
         <f t="shared" si="22"/>
-        <v>849.42447099943615</v>
+        <v>918.10252705679238</v>
       </c>
       <c r="AJ12" s="5">
         <f t="shared" si="22"/>
-        <v>857.91871570943056</v>
+        <v>927.28355232736033</v>
       </c>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.3">
@@ -2236,10 +2229,10 @@
         <v>10</v>
       </c>
       <c r="Q13" s="5">
-        <v>8</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="R13" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" s="5">
         <v>0</v>
@@ -2264,47 +2257,47 @@
       </c>
       <c r="Z13" s="5">
         <f>SUM(O13:R13)</f>
-        <v>31.7</v>
+        <v>33.9</v>
       </c>
       <c r="AA13" s="5">
         <f>Z13*1.1</f>
-        <v>34.870000000000005</v>
+        <v>37.29</v>
       </c>
       <c r="AB13" s="5">
         <f t="shared" ref="AB13:AJ13" si="23">AA13*1.1</f>
-        <v>38.357000000000006</v>
+        <v>41.019000000000005</v>
       </c>
       <c r="AC13" s="5">
         <f t="shared" si="23"/>
-        <v>42.192700000000009</v>
+        <v>45.120900000000013</v>
       </c>
       <c r="AD13" s="5">
         <f t="shared" si="23"/>
-        <v>46.411970000000011</v>
+        <v>49.632990000000021</v>
       </c>
       <c r="AE13" s="5">
         <f t="shared" si="23"/>
-        <v>51.053167000000016</v>
+        <v>54.596289000000027</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="23"/>
-        <v>56.158483700000019</v>
+        <v>60.055917900000033</v>
       </c>
       <c r="AG13" s="5">
         <f t="shared" si="23"/>
-        <v>61.774332070000028</v>
+        <v>66.061509690000037</v>
       </c>
       <c r="AH13" s="5">
         <f t="shared" si="23"/>
-        <v>67.951765277000035</v>
+        <v>72.667660659000049</v>
       </c>
       <c r="AI13" s="5">
         <f t="shared" si="23"/>
-        <v>74.746941804700043</v>
+        <v>79.934426724900064</v>
       </c>
       <c r="AJ13" s="5">
         <f t="shared" si="23"/>
-        <v>82.221635985170053</v>
+        <v>87.927869397390083</v>
       </c>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.3">
@@ -2369,11 +2362,11 @@
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="26"/>
-        <v>758.83696000000009</v>
+        <v>813</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="26"/>
-        <v>789.61848000000009</v>
+        <v>871.30500000000006</v>
       </c>
       <c r="T14" s="5">
         <f t="shared" ref="T14:Y14" si="27">SUM(T9:T13)</f>
@@ -2401,47 +2394,47 @@
       </c>
       <c r="Z14" s="5">
         <f t="shared" ref="Z14:AJ14" si="28">SUM(Z9:Z13)</f>
-        <v>2983.0554400000001</v>
+        <v>3118.9050000000002</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="28"/>
-        <v>3241.201521</v>
+        <v>3532.8546875000002</v>
       </c>
       <c r="AB14" s="5">
         <f t="shared" si="28"/>
-        <v>3390.8540410840001</v>
+        <v>3823.8610165000009</v>
       </c>
       <c r="AC14" s="5">
         <f t="shared" si="28"/>
-        <v>3474.5323462463207</v>
+        <v>4024.7695984725001</v>
       </c>
       <c r="AD14" s="5">
         <f t="shared" si="28"/>
-        <v>3565.6320403915806</v>
+        <v>4212.5749553148007</v>
       </c>
       <c r="AE14" s="5">
         <f t="shared" si="28"/>
-        <v>3639.9223196742023</v>
+        <v>4361.5066665322265</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="28"/>
-        <v>3687.7797522648216</v>
+        <v>4473.1839012997752</v>
       </c>
       <c r="AG14" s="5">
         <f t="shared" si="28"/>
-        <v>3736.7125061716247</v>
+        <v>4568.656804182725</v>
       </c>
       <c r="AH14" s="5">
         <f t="shared" si="28"/>
-        <v>3786.7800278278191</v>
+        <v>4666.7339752627922</v>
       </c>
       <c r="AI14" s="5">
         <f t="shared" si="28"/>
-        <v>3838.0470078233689</v>
+        <v>4767.5237577246617</v>
       </c>
       <c r="AJ14" s="5">
         <f t="shared" si="28"/>
-        <v>3890.5838939232135</v>
+        <v>4871.1417303047638</v>
       </c>
     </row>
     <row r="15" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2506,11 +2499,11 @@
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="31"/>
-        <v>136.43743999999992</v>
+        <v>148.70000000000005</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="31"/>
-        <v>134.74072000000001</v>
+        <v>138.41249999999991</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" ref="T15:Y15" si="32">T8-T14</f>
@@ -2538,47 +2531,47 @@
       </c>
       <c r="Z15" s="8">
         <f t="shared" ref="Z15:AJ15" si="33">Z8-Z14</f>
-        <v>463.17815999999948</v>
+        <v>479.11249999999927</v>
       </c>
       <c r="AA15" s="8">
         <f t="shared" si="33"/>
-        <v>685.55335300000024</v>
+        <v>828.18063749999965</v>
       </c>
       <c r="AB15" s="8">
         <f t="shared" si="33"/>
-        <v>837.49031335600057</v>
+        <v>1195.7434297499985</v>
       </c>
       <c r="AC15" s="8">
         <f t="shared" si="33"/>
-        <v>977.3827374712796</v>
+        <v>1518.7556390149998</v>
       </c>
       <c r="AD15" s="8">
         <f t="shared" si="33"/>
-        <v>1039.2563431565477</v>
+        <v>1701.5143556721987</v>
       </c>
       <c r="AE15" s="8">
         <f t="shared" si="33"/>
-        <v>1077.2563127566491</v>
+        <v>1839.1422373843834</v>
       </c>
       <c r="AF15" s="8">
         <f t="shared" si="33"/>
-        <v>1097.368922138452</v>
+        <v>1939.0603538591668</v>
       </c>
       <c r="AG15" s="8">
         <f t="shared" si="33"/>
-        <v>1117.5018757367566</v>
+        <v>2002.4861666867964</v>
       </c>
       <c r="AH15" s="8">
         <f t="shared" si="33"/>
-        <v>1137.6150030759427</v>
+        <v>2067.4053005497408</v>
       </c>
       <c r="AI15" s="8">
         <f t="shared" si="33"/>
-        <v>1157.663248669252</v>
+        <v>2133.8189524955133</v>
       </c>
       <c r="AJ15" s="8">
         <f t="shared" si="33"/>
-        <v>1177.5961659197528</v>
+        <v>2201.7241024779469</v>
       </c>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.3">
@@ -2628,12 +2621,11 @@
         <v>14.9</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" ref="Q16:R16" si="34">Q15*0.12</f>
-        <v>16.372492799999989</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="34"/>
-        <v>16.168886400000002</v>
+        <f t="shared" ref="R16" si="34">R15*0.12</f>
+        <v>16.60949999999999</v>
       </c>
       <c r="T16" s="5">
         <v>-0.1</v>
@@ -2658,47 +2650,47 @@
       </c>
       <c r="Z16" s="5">
         <f>SUM(O16:R16)</f>
-        <v>56.141379199999989</v>
+        <v>49.409499999999987</v>
       </c>
       <c r="AA16" s="5">
         <f>AA15*0.15</f>
-        <v>102.83300295000004</v>
+        <v>124.22709562499995</v>
       </c>
       <c r="AB16" s="5">
         <f t="shared" ref="AB16:AJ16" si="35">AB15*0.15</f>
-        <v>125.62354700340008</v>
+        <v>179.36151446249977</v>
       </c>
       <c r="AC16" s="5">
         <f t="shared" si="35"/>
-        <v>146.60741062069192</v>
+        <v>227.81334585224997</v>
       </c>
       <c r="AD16" s="5">
         <f t="shared" si="35"/>
-        <v>155.88845147348215</v>
+        <v>255.22715335082978</v>
       </c>
       <c r="AE16" s="5">
         <f t="shared" si="35"/>
-        <v>161.58844691349736</v>
+        <v>275.8713356076575</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="35"/>
-        <v>164.6053383207678</v>
+        <v>290.85905307887498</v>
       </c>
       <c r="AG16" s="5">
         <f t="shared" si="35"/>
-        <v>167.62528136051347</v>
+        <v>300.37292500301947</v>
       </c>
       <c r="AH16" s="5">
         <f t="shared" si="35"/>
-        <v>170.6422504613914</v>
+        <v>310.1107950824611</v>
       </c>
       <c r="AI16" s="5">
         <f t="shared" si="35"/>
-        <v>173.64948730038779</v>
+        <v>320.07284287432697</v>
       </c>
       <c r="AJ16" s="5">
         <f t="shared" si="35"/>
-        <v>176.63942488796292</v>
+        <v>330.25861537169203</v>
       </c>
     </row>
     <row r="17" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2763,11 +2755,11 @@
       </c>
       <c r="Q17" s="8">
         <f t="shared" si="38"/>
-        <v>120.06494719999993</v>
+        <v>139.50000000000006</v>
       </c>
       <c r="R17" s="8">
         <f t="shared" si="38"/>
-        <v>118.57183360000001</v>
+        <v>121.80299999999991</v>
       </c>
       <c r="T17" s="8">
         <f t="shared" ref="T17:Y17" si="39">T15-T16</f>
@@ -2795,511 +2787,511 @@
       </c>
       <c r="Z17" s="8">
         <f t="shared" ref="Z17:AJ17" si="40">Z15-Z16</f>
-        <v>407.03678079999952</v>
+        <v>429.70299999999929</v>
       </c>
       <c r="AA17" s="8">
         <f t="shared" si="40"/>
-        <v>582.72035005000021</v>
+        <v>703.9535418749997</v>
       </c>
       <c r="AB17" s="8">
         <f t="shared" si="40"/>
-        <v>711.86676635260051</v>
+        <v>1016.3819152874987</v>
       </c>
       <c r="AC17" s="8">
         <f t="shared" si="40"/>
-        <v>830.7753268505877</v>
+        <v>1290.9422931627498</v>
       </c>
       <c r="AD17" s="8">
         <f t="shared" si="40"/>
-        <v>883.36789168306552</v>
+        <v>1446.287202321369</v>
       </c>
       <c r="AE17" s="8">
         <f t="shared" si="40"/>
-        <v>915.66786584315173</v>
+        <v>1563.2709017767259</v>
       </c>
       <c r="AF17" s="8">
         <f t="shared" si="40"/>
-        <v>932.76358381768421</v>
+        <v>1648.2013007802918</v>
       </c>
       <c r="AG17" s="8">
         <f t="shared" si="40"/>
-        <v>949.87659437624313</v>
+        <v>1702.113241683777</v>
       </c>
       <c r="AH17" s="8">
         <f t="shared" si="40"/>
-        <v>966.97275261455127</v>
+        <v>1757.2945054672796</v>
       </c>
       <c r="AI17" s="8">
         <f t="shared" si="40"/>
-        <v>984.01376136886415</v>
+        <v>1813.7461096211864</v>
       </c>
       <c r="AJ17" s="8">
         <f t="shared" si="40"/>
-        <v>1000.9567410317899</v>
+        <v>1871.4654871062548</v>
       </c>
       <c r="AK17" s="1">
         <f>AJ17*(1+$AN$22)</f>
-        <v>990.94717362147196</v>
+        <v>1852.7508322351923</v>
       </c>
       <c r="AL17" s="1">
         <f t="shared" ref="AL17:CW17" si="41">AK17*(1+$AN$22)</f>
-        <v>981.03770188525721</v>
+        <v>1834.2233239128404</v>
       </c>
       <c r="AM17" s="1">
         <f t="shared" si="41"/>
-        <v>971.22732486640462</v>
+        <v>1815.8810906737119</v>
       </c>
       <c r="AN17" s="1">
         <f t="shared" si="41"/>
-        <v>961.5150516177406</v>
+        <v>1797.7222797669747</v>
       </c>
       <c r="AO17" s="1">
         <f t="shared" si="41"/>
-        <v>951.89990110156316</v>
+        <v>1779.7450569693049</v>
       </c>
       <c r="AP17" s="1">
         <f t="shared" si="41"/>
-        <v>942.38090209054747</v>
+        <v>1761.9476063996119</v>
       </c>
       <c r="AQ17" s="1">
         <f t="shared" si="41"/>
-        <v>932.95709306964193</v>
+        <v>1744.3281303356157</v>
       </c>
       <c r="AR17" s="1">
         <f t="shared" si="41"/>
-        <v>923.62752213894555</v>
+        <v>1726.8848490322596</v>
       </c>
       <c r="AS17" s="1">
         <f t="shared" si="41"/>
-        <v>914.39124691755603</v>
+        <v>1709.616000541937</v>
       </c>
       <c r="AT17" s="1">
         <f t="shared" si="41"/>
-        <v>905.24733444838046</v>
+        <v>1692.5198405365177</v>
       </c>
       <c r="AU17" s="1">
         <f t="shared" si="41"/>
-        <v>896.19486110389664</v>
+        <v>1675.5946421311526</v>
       </c>
       <c r="AV17" s="1">
         <f t="shared" si="41"/>
-        <v>887.23291249285762</v>
+        <v>1658.838695709841</v>
       </c>
       <c r="AW17" s="1">
         <f t="shared" si="41"/>
-        <v>878.36058336792905</v>
+        <v>1642.2503087527425</v>
       </c>
       <c r="AX17" s="1">
         <f t="shared" si="41"/>
-        <v>869.57697753424975</v>
+        <v>1625.827805665215</v>
       </c>
       <c r="AY17" s="1">
         <f t="shared" si="41"/>
-        <v>860.88120775890729</v>
+        <v>1609.5695276085628</v>
       </c>
       <c r="AZ17" s="1">
         <f t="shared" si="41"/>
-        <v>852.27239568131824</v>
+        <v>1593.4738323324771</v>
       </c>
       <c r="BA17" s="1">
         <f t="shared" si="41"/>
-        <v>843.74967172450511</v>
+        <v>1577.5390940091522</v>
       </c>
       <c r="BB17" s="1">
         <f t="shared" si="41"/>
-        <v>835.31217500726007</v>
+        <v>1561.7637030690607</v>
       </c>
       <c r="BC17" s="1">
         <f t="shared" si="41"/>
-        <v>826.95905325718741</v>
+        <v>1546.14606603837</v>
       </c>
       <c r="BD17" s="1">
         <f t="shared" si="41"/>
-        <v>818.68946272461551</v>
+        <v>1530.6846053779864</v>
       </c>
       <c r="BE17" s="1">
         <f t="shared" si="41"/>
-        <v>810.50256809736936</v>
+        <v>1515.3777593242064</v>
       </c>
       <c r="BF17" s="1">
         <f t="shared" si="41"/>
-        <v>802.39754241639571</v>
+        <v>1500.2239817309644</v>
       </c>
       <c r="BG17" s="1">
         <f t="shared" si="41"/>
-        <v>794.37356699223176</v>
+        <v>1485.2217419136548</v>
       </c>
       <c r="BH17" s="1">
         <f t="shared" si="41"/>
-        <v>786.42983132230938</v>
+        <v>1470.3695244945181</v>
       </c>
       <c r="BI17" s="1">
         <f t="shared" si="41"/>
-        <v>778.56553300908627</v>
+        <v>1455.6658292495729</v>
       </c>
       <c r="BJ17" s="1">
         <f t="shared" si="41"/>
-        <v>770.77987767899538</v>
+        <v>1441.1091709570771</v>
       </c>
       <c r="BK17" s="1">
         <f t="shared" si="41"/>
-        <v>763.07207890220536</v>
+        <v>1426.6980792475063</v>
       </c>
       <c r="BL17" s="1">
         <f t="shared" si="41"/>
-        <v>755.44135811318336</v>
+        <v>1412.4310984550311</v>
       </c>
       <c r="BM17" s="1">
         <f t="shared" si="41"/>
-        <v>747.88694453205153</v>
+        <v>1398.3067874704809</v>
       </c>
       <c r="BN17" s="1">
         <f t="shared" si="41"/>
-        <v>740.40807508673106</v>
+        <v>1384.3237195957761</v>
       </c>
       <c r="BO17" s="1">
         <f t="shared" si="41"/>
-        <v>733.00399433586369</v>
+        <v>1370.4804823998184</v>
       </c>
       <c r="BP17" s="1">
         <f t="shared" si="41"/>
-        <v>725.67395439250504</v>
+        <v>1356.7756775758201</v>
       </c>
       <c r="BQ17" s="1">
         <f t="shared" si="41"/>
-        <v>718.41721484857999</v>
+        <v>1343.2079208000619</v>
       </c>
       <c r="BR17" s="1">
         <f t="shared" si="41"/>
-        <v>711.23304270009419</v>
+        <v>1329.7758415920612</v>
       </c>
       <c r="BS17" s="1">
         <f t="shared" si="41"/>
-        <v>704.1207122730932</v>
+        <v>1316.4780831761404</v>
       </c>
       <c r="BT17" s="1">
         <f t="shared" si="41"/>
-        <v>697.07950515036225</v>
+        <v>1303.3133023443791</v>
       </c>
       <c r="BU17" s="1">
         <f t="shared" si="41"/>
-        <v>690.10871009885864</v>
+        <v>1290.2801693209353</v>
       </c>
       <c r="BV17" s="1">
         <f t="shared" si="41"/>
-        <v>683.20762299787009</v>
+        <v>1277.377367627726</v>
       </c>
       <c r="BW17" s="1">
         <f t="shared" si="41"/>
-        <v>676.37554676789136</v>
+        <v>1264.6035939514488</v>
       </c>
       <c r="BX17" s="1">
         <f t="shared" si="41"/>
-        <v>669.61179130021242</v>
+        <v>1251.9575580119342</v>
       </c>
       <c r="BY17" s="1">
         <f t="shared" si="41"/>
-        <v>662.91567338721029</v>
+        <v>1239.4379824318148</v>
       </c>
       <c r="BZ17" s="1">
         <f t="shared" si="41"/>
-        <v>656.28651665333814</v>
+        <v>1227.0436026074967</v>
       </c>
       <c r="CA17" s="1">
         <f t="shared" si="41"/>
-        <v>649.72365148680478</v>
+        <v>1214.7731665814217</v>
       </c>
       <c r="CB17" s="1">
         <f t="shared" si="41"/>
-        <v>643.22641497193672</v>
+        <v>1202.6254349156075</v>
       </c>
       <c r="CC17" s="1">
         <f t="shared" si="41"/>
-        <v>636.79415082221738</v>
+        <v>1190.5991805664514</v>
       </c>
       <c r="CD17" s="1">
         <f t="shared" si="41"/>
-        <v>630.42620931399517</v>
+        <v>1178.6931887607868</v>
       </c>
       <c r="CE17" s="1">
         <f t="shared" si="41"/>
-        <v>624.12194722085519</v>
+        <v>1166.906256873179</v>
       </c>
       <c r="CF17" s="1">
         <f t="shared" si="41"/>
-        <v>617.88072774864668</v>
+        <v>1155.2371943044473</v>
       </c>
       <c r="CG17" s="1">
         <f t="shared" si="41"/>
-        <v>611.70192047116018</v>
+        <v>1143.6848223614027</v>
       </c>
       <c r="CH17" s="1">
         <f t="shared" si="41"/>
-        <v>605.58490126644858</v>
+        <v>1132.2479741377886</v>
       </c>
       <c r="CI17" s="1">
         <f t="shared" si="41"/>
-        <v>599.52905225378413</v>
+        <v>1120.9254943964106</v>
       </c>
       <c r="CJ17" s="1">
         <f t="shared" si="41"/>
-        <v>593.53376173124627</v>
+        <v>1109.7162394524464</v>
       </c>
       <c r="CK17" s="1">
         <f t="shared" si="41"/>
-        <v>587.59842411393379</v>
+        <v>1098.6190770579219</v>
       </c>
       <c r="CL17" s="1">
         <f t="shared" si="41"/>
-        <v>581.72243987279444</v>
+        <v>1087.6328862873427</v>
       </c>
       <c r="CM17" s="1">
         <f t="shared" si="41"/>
-        <v>575.90521547406649</v>
+        <v>1076.7565574244693</v>
       </c>
       <c r="CN17" s="1">
         <f t="shared" si="41"/>
-        <v>570.14616331932586</v>
+        <v>1065.9889918502247</v>
       </c>
       <c r="CO17" s="1">
         <f t="shared" si="41"/>
-        <v>564.44470168613259</v>
+        <v>1055.3291019317223</v>
       </c>
       <c r="CP17" s="1">
         <f t="shared" si="41"/>
-        <v>558.80025466927123</v>
+        <v>1044.7758109124052</v>
       </c>
       <c r="CQ17" s="1">
         <f t="shared" si="41"/>
-        <v>553.21225212257855</v>
+        <v>1034.328052803281</v>
       </c>
       <c r="CR17" s="1">
         <f t="shared" si="41"/>
-        <v>547.68012960135275</v>
+        <v>1023.9847722752482</v>
       </c>
       <c r="CS17" s="1">
         <f t="shared" si="41"/>
-        <v>542.20332830533926</v>
+        <v>1013.7449245524957</v>
       </c>
       <c r="CT17" s="1">
         <f t="shared" si="41"/>
-        <v>536.7812950222858</v>
+        <v>1003.6074753069707</v>
       </c>
       <c r="CU17" s="1">
         <f t="shared" si="41"/>
-        <v>531.41348207206295</v>
+        <v>993.57140055390107</v>
       </c>
       <c r="CV17" s="1">
         <f t="shared" si="41"/>
-        <v>526.09934725134235</v>
+        <v>983.63568654836206</v>
       </c>
       <c r="CW17" s="1">
         <f t="shared" si="41"/>
-        <v>520.83835377882895</v>
+        <v>973.79932968287847</v>
       </c>
       <c r="CX17" s="1">
         <f t="shared" ref="CX17:EV17" si="42">CW17*(1+$AN$22)</f>
-        <v>515.62997024104061</v>
+        <v>964.06133638604967</v>
       </c>
       <c r="CY17" s="1">
         <f t="shared" si="42"/>
-        <v>510.47367053863019</v>
+        <v>954.42072302218912</v>
       </c>
       <c r="CZ17" s="1">
         <f t="shared" si="42"/>
-        <v>505.36893383324389</v>
+        <v>944.87651579196722</v>
       </c>
       <c r="DA17" s="1">
         <f t="shared" si="42"/>
-        <v>500.31524449491144</v>
+        <v>935.42775063404758</v>
       </c>
       <c r="DB17" s="1">
         <f t="shared" si="42"/>
-        <v>495.3120920499623</v>
+        <v>926.07347312770708</v>
       </c>
       <c r="DC17" s="1">
         <f t="shared" si="42"/>
-        <v>490.3589711294627</v>
+        <v>916.81273839642995</v>
       </c>
       <c r="DD17" s="1">
         <f t="shared" si="42"/>
-        <v>485.45538141816809</v>
+        <v>907.64461101246559</v>
       </c>
       <c r="DE17" s="1">
         <f t="shared" si="42"/>
-        <v>480.60082760398637</v>
+        <v>898.56816490234087</v>
       </c>
       <c r="DF17" s="1">
         <f t="shared" si="42"/>
-        <v>475.79481932794653</v>
+        <v>889.58248325331749</v>
       </c>
       <c r="DG17" s="1">
         <f t="shared" si="42"/>
-        <v>471.03687113466708</v>
+        <v>880.68665842078428</v>
       </c>
       <c r="DH17" s="1">
         <f t="shared" si="42"/>
-        <v>466.32650242332039</v>
+        <v>871.87979183657649</v>
       </c>
       <c r="DI17" s="1">
         <f t="shared" si="42"/>
-        <v>461.66323739908717</v>
+        <v>863.16099391821069</v>
       </c>
       <c r="DJ17" s="1">
         <f t="shared" si="42"/>
-        <v>457.04660502509631</v>
+        <v>854.52938397902858</v>
       </c>
       <c r="DK17" s="1">
         <f t="shared" si="42"/>
-        <v>452.47613897484536</v>
+        <v>845.98409013923833</v>
       </c>
       <c r="DL17" s="1">
         <f t="shared" si="42"/>
-        <v>447.95137758509691</v>
+        <v>837.52424923784599</v>
       </c>
       <c r="DM17" s="1">
         <f t="shared" si="42"/>
-        <v>443.47186380924592</v>
+        <v>829.14900674546755</v>
       </c>
       <c r="DN17" s="1">
         <f t="shared" si="42"/>
-        <v>439.03714517115344</v>
+        <v>820.85751667801287</v>
       </c>
       <c r="DO17" s="1">
         <f t="shared" si="42"/>
-        <v>434.64677371944191</v>
+        <v>812.64894151123269</v>
       </c>
       <c r="DP17" s="1">
         <f t="shared" si="42"/>
-        <v>430.30030598224749</v>
+        <v>804.52245209612033</v>
       </c>
       <c r="DQ17" s="1">
         <f t="shared" si="42"/>
-        <v>425.99730292242504</v>
+        <v>796.47722757515908</v>
       </c>
       <c r="DR17" s="1">
         <f t="shared" si="42"/>
-        <v>421.73732989320081</v>
+        <v>788.51245529940752</v>
       </c>
       <c r="DS17" s="1">
         <f t="shared" si="42"/>
-        <v>417.51995659426882</v>
+        <v>780.62733074641346</v>
       </c>
       <c r="DT17" s="1">
         <f t="shared" si="42"/>
-        <v>413.34475702832611</v>
+        <v>772.82105743894931</v>
       </c>
       <c r="DU17" s="1">
         <f t="shared" si="42"/>
-        <v>409.21130945804288</v>
+        <v>765.09284686455976</v>
       </c>
       <c r="DV17" s="1">
         <f t="shared" si="42"/>
-        <v>405.11919636346244</v>
+        <v>757.44191839591417</v>
       </c>
       <c r="DW17" s="1">
         <f t="shared" si="42"/>
-        <v>401.06800439982783</v>
+        <v>749.86749921195508</v>
       </c>
       <c r="DX17" s="1">
         <f t="shared" si="42"/>
-        <v>397.05732435582956</v>
+        <v>742.36882421983557</v>
       </c>
       <c r="DY17" s="1">
         <f t="shared" si="42"/>
-        <v>393.08675111227126</v>
+        <v>734.94513597763716</v>
       </c>
       <c r="DZ17" s="1">
         <f t="shared" si="42"/>
-        <v>389.15588360114856</v>
+        <v>727.5956846178608</v>
       </c>
       <c r="EA17" s="1">
         <f t="shared" si="42"/>
-        <v>385.26432476513708</v>
+        <v>720.31972777168221</v>
       </c>
       <c r="EB17" s="1">
         <f t="shared" si="42"/>
-        <v>381.4116815174857</v>
+        <v>713.11653049396534</v>
       </c>
       <c r="EC17" s="1">
         <f t="shared" si="42"/>
-        <v>377.59756470231082</v>
+        <v>705.98536518902563</v>
       </c>
       <c r="ED17" s="1">
         <f t="shared" si="42"/>
-        <v>373.82158905528769</v>
+        <v>698.92551153713532</v>
       </c>
       <c r="EE17" s="1">
         <f t="shared" si="42"/>
-        <v>370.08337316473478</v>
+        <v>691.93625642176391</v>
       </c>
       <c r="EF17" s="1">
         <f t="shared" si="42"/>
-        <v>366.3825394330874</v>
+        <v>685.01689385754628</v>
       </c>
       <c r="EG17" s="1">
         <f t="shared" si="42"/>
-        <v>362.7187140387565</v>
+        <v>678.16672491897077</v>
       </c>
       <c r="EH17" s="1">
         <f t="shared" si="42"/>
-        <v>359.09152689836895</v>
+        <v>671.38505766978108</v>
       </c>
       <c r="EI17" s="1">
         <f t="shared" si="42"/>
-        <v>355.50061162938528</v>
+        <v>664.67120709308324</v>
       </c>
       <c r="EJ17" s="1">
         <f t="shared" si="42"/>
-        <v>351.94560551309144</v>
+        <v>658.02449502215245</v>
       </c>
       <c r="EK17" s="1">
         <f t="shared" si="42"/>
-        <v>348.42614945796049</v>
+        <v>651.44425007193092</v>
       </c>
       <c r="EL17" s="1">
         <f t="shared" si="42"/>
-        <v>344.94188796338091</v>
+        <v>644.92980757121165</v>
       </c>
       <c r="EM17" s="1">
         <f t="shared" si="42"/>
-        <v>341.4924690837471</v>
+        <v>638.48050949549952</v>
       </c>
       <c r="EN17" s="1">
         <f t="shared" si="42"/>
-        <v>338.0775443929096</v>
+        <v>632.09570440054449</v>
       </c>
       <c r="EO17" s="1">
         <f t="shared" si="42"/>
-        <v>334.69676894898049</v>
+        <v>625.77474735653902</v>
       </c>
       <c r="EP17" s="1">
         <f t="shared" si="42"/>
-        <v>331.34980125949068</v>
+        <v>619.51699988297366</v>
       </c>
       <c r="EQ17" s="1">
         <f t="shared" si="42"/>
-        <v>328.03630324689578</v>
+        <v>613.32182988414388</v>
       </c>
       <c r="ER17" s="1">
         <f t="shared" si="42"/>
-        <v>324.7559402144268</v>
+        <v>607.1886115853024</v>
       </c>
       <c r="ES17" s="1">
         <f t="shared" si="42"/>
-        <v>321.50838081228255</v>
+        <v>601.11672546944942</v>
       </c>
       <c r="ET17" s="1">
         <f t="shared" si="42"/>
-        <v>318.29329700415974</v>
+        <v>595.10555821475486</v>
       </c>
       <c r="EU17" s="1">
         <f t="shared" si="42"/>
-        <v>315.11036403411816</v>
+        <v>589.15450263260732</v>
       </c>
       <c r="EV17" s="1">
         <f t="shared" si="42"/>
-        <v>311.95926039377696</v>
+        <v>583.26295760628125</v>
       </c>
     </row>
     <row r="18" spans="2:152" x14ac:dyDescent="0.3">
@@ -3350,12 +3342,12 @@
         <v>1107</v>
       </c>
       <c r="Q18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f>1171.2</f>
+        <v>1171.2</v>
       </c>
       <c r="R18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f>1171.2</f>
+        <v>1171.2</v>
       </c>
       <c r="T18" s="5">
         <v>937</v>
@@ -3376,48 +3368,48 @@
         <v>1087.9000000000001</v>
       </c>
       <c r="Z18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" ref="Z18:AJ18" si="43">1171.2</f>
+        <v>1171.2</v>
       </c>
       <c r="AA18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AB18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AC18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AD18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AE18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AF18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AG18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AH18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AI18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
       <c r="AJ18" s="5">
-        <f>1107</f>
-        <v>1107</v>
+        <f t="shared" si="43"/>
+        <v>1171.2</v>
       </c>
     </row>
     <row r="19" spans="2:152" x14ac:dyDescent="0.3">
@@ -3425,136 +3417,136 @@
         <v>36</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="C19:L19" si="43">C17/C18</f>
+        <f t="shared" ref="C19:L19" si="44">C17/C18</f>
         <v>-0.11787315823190259</v>
       </c>
       <c r="D19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-0.10249839846252405</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-7.9329489643390927E-2</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-4.494981849241949E-2</v>
       </c>
       <c r="G19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-3.6942131112534561E-2</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-5.0715353405936442E-2</v>
       </c>
       <c r="I19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-0.28486013239376479</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>5.1249199231262178E-2</v>
       </c>
       <c r="K19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>8.955831467535115E-2</v>
       </c>
       <c r="L19" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1.6324233042499255E-2</v>
       </c>
       <c r="M19" s="7">
-        <f t="shared" ref="M19:N19" si="44">M17/M18</f>
+        <f t="shared" ref="M19:N19" si="45">M17/M18</f>
         <v>5.6031702147267513E-2</v>
       </c>
       <c r="N19" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.30545086864601517</v>
       </c>
       <c r="O19" s="7">
-        <f t="shared" ref="O19:R19" si="45">O17/O18</f>
+        <f t="shared" ref="O19:R19" si="46">O17/O18</f>
         <v>6.466302367941705E-2</v>
       </c>
       <c r="P19" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>8.7985546522131947E-2</v>
       </c>
       <c r="Q19" s="7">
-        <f t="shared" si="45"/>
-        <v>0.1084597535682023</v>
+        <f t="shared" si="46"/>
+        <v>0.11910860655737709</v>
       </c>
       <c r="R19" s="7">
-        <f t="shared" si="45"/>
-        <v>0.10711096079494128</v>
+        <f t="shared" si="46"/>
+        <v>0.10399846311475403</v>
       </c>
       <c r="T19" s="7">
-        <f t="shared" ref="T19:Y19" si="46">T17/T18</f>
+        <f t="shared" ref="T19:Y19" si="47">T17/T18</f>
         <v>-0.25570971184631791</v>
       </c>
       <c r="U19" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-0.23916755602988263</v>
       </c>
       <c r="V19" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-0.51664887940234783</v>
       </c>
       <c r="W19" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-0.34450373532550677</v>
       </c>
       <c r="X19" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-0.3211312700106721</v>
       </c>
       <c r="Y19" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.45822226307565056</v>
       </c>
       <c r="Z19" s="7">
-        <f t="shared" ref="Z19:AJ19" si="47">Z17/Z18</f>
-        <v>0.36769356892502214</v>
+        <f t="shared" ref="Z19:AJ19" si="48">Z17/Z18</f>
+        <v>0.366891222677595</v>
       </c>
       <c r="AA19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.52639598017163525</v>
+        <f t="shared" si="48"/>
+        <v>0.6010532290599383</v>
       </c>
       <c r="AB19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.64305940953261109</v>
+        <f t="shared" si="48"/>
+        <v>0.86781242767033695</v>
       </c>
       <c r="AC19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.75047455000053087</v>
+        <f t="shared" si="48"/>
+        <v>1.1022389798179215</v>
       </c>
       <c r="AD19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.79798364199012239</v>
+        <f t="shared" si="48"/>
+        <v>1.2348763681022616</v>
       </c>
       <c r="AE19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.82716157709408467</v>
+        <f t="shared" si="48"/>
+        <v>1.3347599912711114</v>
       </c>
       <c r="AF19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.84260486343060903</v>
+        <f t="shared" si="48"/>
+        <v>1.4072757008028447</v>
       </c>
       <c r="AG19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.85806377089091523</v>
+        <f t="shared" si="48"/>
+        <v>1.4533070711097822</v>
       </c>
       <c r="AH19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.87350745493636073</v>
+        <f t="shared" si="48"/>
+        <v>1.5004222211981553</v>
       </c>
       <c r="AI19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.88890132011640843</v>
+        <f t="shared" si="48"/>
+        <v>1.5486220198268326</v>
       </c>
       <c r="AJ19" s="7">
-        <f t="shared" si="47"/>
-        <v>0.90420663146503155</v>
+        <f t="shared" si="48"/>
+        <v>1.597904275193182</v>
       </c>
     </row>
     <row r="21" spans="2:152" x14ac:dyDescent="0.3">
@@ -3566,117 +3558,117 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9">
-        <f t="shared" ref="G21:L21" si="48">G3/C3-1</f>
+        <f t="shared" ref="G21:L21" si="49">G3/C3-1</f>
         <v>2.1385135135135136</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>2.1438127090301005</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.8499999999999996</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.0988939492517895</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.79198062432723337</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.4353191489361703</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" ref="M21:N21" si="49">M3/I3-1</f>
+        <f t="shared" ref="M21:N21" si="50">M3/I3-1</f>
         <v>0.28194222931065038</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.15297582145071287</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" ref="O21" si="50">O3/K3-1</f>
+        <f t="shared" ref="O21" si="51">O3/K3-1</f>
         <v>0.14701907193272268</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" ref="P21" si="51">P3/L3-1</f>
+        <f t="shared" ref="P21" si="52">P3/L3-1</f>
         <v>0.17462199822116808</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" ref="Q21" si="52">Q3/M3-1</f>
-        <v>0.1399999999999999</v>
+        <f t="shared" ref="Q21" si="53">Q3/M3-1</f>
+        <v>0.23251313243019078</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" ref="R21" si="53">R3/N3-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="R21" si="54">R3/N3-1</f>
+        <v>0.25</v>
       </c>
       <c r="T21" s="9"/>
       <c r="U21" s="9">
-        <f t="shared" ref="U21:AJ21" si="54">U3/T3-1</f>
+        <f t="shared" ref="U21:AJ21" si="55">U3/T3-1</f>
         <v>-0.40233475830318977</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>-2.3383768913342484E-2</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.1783098591549295</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.6523988102935476</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.36892399200429016</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="54"/>
-        <v>0.14468409430871132</v>
+        <f t="shared" si="55"/>
+        <v>0.2029613932616281</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="54"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="55"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="54"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="55"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="55"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="54"/>
+      <c r="AE21" s="9">
+        <f t="shared" si="55"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AE21" s="9">
-        <f t="shared" si="54"/>
+      <c r="AF21" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF21" s="9">
-        <f t="shared" si="54"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AG21" s="9">
-        <f t="shared" si="54"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="55"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="54"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="55"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="54"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="55"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="54"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="55"/>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="22" spans="2:152" x14ac:dyDescent="0.3">
@@ -3684,19 +3676,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:F22" si="55">C5/C3</f>
+        <f t="shared" ref="C22:F22" si="56">C5/C3</f>
         <v>0.80152027027027029</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.82073578595317731</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.79696969696969699</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.67859466493168508</v>
       </c>
       <c r="G22" s="9">
@@ -3704,116 +3696,116 @@
         <v>0.63509149623250816</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:L22" si="56">H5/H3</f>
+        <f t="shared" ref="H22:L22" si="57">H5/H3</f>
         <v>0.61936170212765962</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.6113769271664008</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.60384376937383755</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.60474545727586726</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.61162170174918473</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22:N22" si="57">M5/M3</f>
+        <f t="shared" ref="M22:N22" si="58">M5/M3</f>
         <v>0.59579762233895495</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.63193977685172731</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22:R22" si="58">O5/O3</f>
+        <f t="shared" ref="O22:R22" si="59">O5/O3</f>
         <v>0.65291961246399577</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.65345784957092379</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="58"/>
-        <v>0.65</v>
+        <f t="shared" si="59"/>
+        <v>0.65634813817855542</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="58"/>
-        <v>0.65</v>
+        <f t="shared" si="59"/>
+        <v>0.65999999999999992</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22:AJ22" si="59">T5/T3</f>
+        <f t="shared" ref="T22:AJ22" si="60">T5/T3</f>
         <v>0.54225583689575807</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.48940852819807429</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.71042253521126753</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.7552049657312816</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.61513334308419876</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.61129710093311485</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65154633850687793</v>
+        <f t="shared" si="60"/>
+        <v>0.65590013840881667</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65000000000000013</v>
+        <f t="shared" si="60"/>
+        <v>0.66</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.64999999999999991</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.65</v>
+        <f t="shared" si="60"/>
+        <v>0.67</v>
       </c>
       <c r="AM22" t="s">
         <v>50</v>
@@ -3835,48 +3827,48 @@
         <v>2.9736618521665203E-3</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:N23" si="60">H6/D6-1</f>
+        <f t="shared" ref="H23:N23" si="61">H6/D6-1</f>
         <v>-0.13683771380892773</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-0.27771514468245029</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-8.9883111648528802E-2</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>2.6260059296908222E-2</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-0.10101498308361534</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.38449531737773168</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.16917626217891923</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" ref="O23:O24" si="61">O6/K6-1</f>
+        <f t="shared" ref="O23:O24" si="62">O6/K6-1</f>
         <v>0.12670243499793643</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" ref="P23:P24" si="62">P6/L6-1</f>
+        <f t="shared" ref="P23:P24" si="63">P6/L6-1</f>
         <v>0.81236559139784958</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" ref="Q23:Q24" si="63">Q6/M6-1</f>
-        <v>0.35000000000000009</v>
+        <f t="shared" ref="Q23:Q24" si="64">Q6/M6-1</f>
+        <v>0.41488162344983071</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" ref="R23:R24" si="64">R6/N6-1</f>
-        <v>0.44999999999999996</v>
+        <f t="shared" ref="R23:R24" si="65">R6/N6-1</f>
+        <v>0.5</v>
       </c>
       <c r="T23" s="9"/>
       <c r="U23" s="9">
@@ -3884,64 +3876,64 @@
         <v>2.4361702127659579</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" ref="V23:AJ23" si="65">V6/U6-1</f>
+        <f t="shared" ref="V23:AJ23" si="66">V6/U6-1</f>
         <v>0.89009287925696579</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.35039585039585042</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-0.12968765793995762</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.1131242740998839</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.41082533388981624</v>
+        <f t="shared" si="66"/>
+        <v>0.44261268781302143</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="65"/>
-        <v>0.21999999999999997</v>
+        <f t="shared" si="66"/>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="66"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="66"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="65"/>
+      <c r="AE23" s="9">
+        <f t="shared" si="66"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="65"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AE23" s="9">
-        <f t="shared" si="65"/>
+      <c r="AF23" s="9">
+        <f t="shared" si="66"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AG23" s="9">
+        <f t="shared" si="66"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="65"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="65"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AH23" s="9">
-        <f t="shared" si="65"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="66"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="65"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="66"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="65"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="66"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM23" t="s">
         <v>49</v>
@@ -3963,120 +3955,120 @@
         <v>0.71763708309779539</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:L24" si="66">H7/D7-1</f>
+        <f t="shared" ref="H24:L24" si="67">H7/D7-1</f>
         <v>0.73920863309352525</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.63003663003663002</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.56795679567956792</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.49448741155175258</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.27138425173585468</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" ref="M24" si="67">M7/I7-1</f>
+        <f t="shared" ref="M24" si="68">M7/I7-1</f>
         <v>0.3079973562458691</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" ref="N24" si="68">N7/J7-1</f>
+        <f t="shared" ref="N24" si="69">N7/J7-1</f>
         <v>0.15717566016073481</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.14159876679145555</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.31245642574947707</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="63"/>
-        <v>0.19647397675593736</v>
+        <f t="shared" si="64"/>
+        <v>0.28155634158665976</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="64"/>
-        <v>0.20643714654231582</v>
+        <f t="shared" si="65"/>
+        <v>0.31548268677448155</v>
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9">
-        <f t="shared" ref="U24:AJ24" si="69">U7/T7-1</f>
+        <f t="shared" ref="U24:AJ24" si="70">U7/T7-1</f>
         <v>4.1747572815534095E-2</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.44800958594062035</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.62063258550937861</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.65216157948485232</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.29329349953641692</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="69"/>
-        <v>0.21241012160798678</v>
+        <f t="shared" si="70"/>
+        <v>0.2639464181403004</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="69"/>
-        <v>0.12849554518121176</v>
+        <f t="shared" si="70"/>
+        <v>0.19356681074097604</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="69"/>
-        <v>7.2805221503599249E-2</v>
+        <f t="shared" si="70"/>
+        <v>0.13163451119987069</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="69"/>
-        <v>4.9847367936616482E-2</v>
+        <f t="shared" si="70"/>
+        <v>9.6836518726947762E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="69"/>
-        <v>3.3345465259674967E-2</v>
+        <f t="shared" si="70"/>
+        <v>6.1102960201268486E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="69"/>
-        <v>2.3367009375889314E-2</v>
+        <f t="shared" si="70"/>
+        <v>4.4584356775954737E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="69"/>
-        <v>1.338883277005487E-2</v>
+        <f t="shared" si="70"/>
+        <v>3.1204405117483347E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="69"/>
-        <v>1.3410940908049396E-2</v>
+        <f t="shared" si="70"/>
+        <v>2.3802875328749806E-2</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="69"/>
-        <v>1.3433118378506137E-2</v>
+        <f t="shared" si="70"/>
+        <v>2.3825894303485251E-2</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="69"/>
-        <v>1.3455364426691485E-2</v>
+        <f t="shared" si="70"/>
+        <v>2.3848966073739319E-2</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="69"/>
-        <v>1.3477678286521355E-2</v>
+        <f t="shared" si="70"/>
+        <v>2.3872089719594314E-2</v>
       </c>
       <c r="AM24" t="s">
         <v>51</v>
       </c>
       <c r="AN24" s="5">
         <f>NPV(AN23,Z17:EV17)</f>
-        <v>10378.739793848174</v>
+        <v>17958.379419934059</v>
       </c>
     </row>
     <row r="25" spans="2:152" x14ac:dyDescent="0.3">
@@ -4084,43 +4076,43 @@
         <v>40</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:L25" si="70">(C8-C11)/C7</f>
+        <f t="shared" ref="C25:L25" si="71">(C8-C11)/C7</f>
         <v>0.73459581684567543</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.7279033915724562</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.73432449903038144</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.67704770477047693</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.63880204048050027</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59698626089525786</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.58017184401850619</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.5872560275545351</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59997797841885037</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.56809202881710441</v>
       </c>
       <c r="M25" s="9">
@@ -4132,95 +4124,95 @@
         <v>0.60115090782815739</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="71">(O8-O11)/O7</f>
+        <f t="shared" ref="O25:R25" si="72">(O8-O11)/O7</f>
         <v>0.61361882716049376</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.6237273129703409</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="71"/>
-        <v>0.62620076171266259</v>
+        <f t="shared" si="72"/>
+        <v>0.63110164813500524</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="71"/>
-        <v>0.63018382062685863</v>
+        <f t="shared" si="72"/>
+        <v>0.63154803431696049</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" ref="T25:AJ25" si="72">(T8-T11)/T7</f>
+        <f t="shared" ref="T25:AJ25" si="73">(T8-T11)/T7</f>
         <v>0.45256588072122061</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.51471175609106645</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.66917984553144538</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.71490979235220709</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.59843411970742766</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.58762147522701935</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.62379274443686927</v>
+        <f t="shared" si="73"/>
+        <v>0.62566842251760657</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.63204568815649209</v>
+        <f t="shared" si="73"/>
+        <v>0.63755733807956017</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.63488595926052527</v>
+        <f t="shared" si="73"/>
+        <v>0.65070063974865988</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.63709128408862536</v>
+        <f t="shared" si="73"/>
+        <v>0.65606628110697618</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.63784532815612538</v>
+        <f t="shared" si="73"/>
+        <v>0.66032094340162506</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.63860914695191739</v>
+        <f t="shared" si="73"/>
+        <v>0.66324845629231655</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.63938293178173145</v>
+        <f t="shared" si="73"/>
+        <v>0.66549488584873617</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.64015914324770917</v>
+        <f t="shared" si="73"/>
+        <v>0.66625451201501273</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.64093775493420146</v>
+        <f t="shared" si="73"/>
+        <v>0.66701588043339299</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.64171874002824747</v>
+        <f t="shared" si="73"/>
+        <v>0.66777896074661114</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.64250207132210069</v>
+        <f t="shared" si="73"/>
+        <v>0.66854372229743442</v>
       </c>
       <c r="AM25" t="s">
         <v>52</v>
       </c>
       <c r="AN25" s="5">
         <f>Main!D8</f>
-        <v>1822.9000000000005</v>
+        <v>3544.4999999999995</v>
       </c>
     </row>
     <row r="26" spans="2:152" x14ac:dyDescent="0.3">
@@ -4236,120 +4228,120 @@
         <v>0.4297924297924296</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:L26" si="73">H9/D9-1</f>
+        <f t="shared" ref="H26:L26" si="74">H9/D9-1</f>
         <v>0.2756539235412474</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.13550135501355021</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.25154457193292168</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.11784799316823236</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>4.258675078864349E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" ref="M26" si="74">M9/I9-1</f>
+        <f t="shared" ref="M26" si="75">M9/I9-1</f>
         <v>0.11137629276054084</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" ref="N26" si="75">N9/J9-1</f>
+        <f t="shared" ref="N26" si="76">N9/J9-1</f>
         <v>5.0775740479548581E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" ref="O26" si="76">O9/K9-1</f>
+        <f t="shared" ref="O26" si="77">O9/K9-1</f>
         <v>0.19327731092436951</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" ref="P26" si="77">P9/L9-1</f>
+        <f t="shared" ref="P26" si="78">P9/L9-1</f>
         <v>0.15052950075642979</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" ref="Q26" si="78">Q9/M9-1</f>
-        <v>0.12999999999999989</v>
+        <f t="shared" ref="Q26" si="79">Q9/M9-1</f>
+        <v>0.19613457408733015</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" ref="R26" si="79">R9/N9-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="R26" si="80">R9/N9-1</f>
+        <v>0.17999999999999994</v>
       </c>
       <c r="T26" s="9"/>
       <c r="U26" s="9">
-        <f t="shared" ref="U26:AJ26" si="80">U9/T9-1</f>
+        <f t="shared" ref="U26:AJ26" si="81">U9/T9-1</f>
         <v>0.36406779661016953</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.37226640159045754</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.46794639623324885</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.2617813964964224</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>7.8998826750097839E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="80"/>
-        <v>0.14722906850308082</v>
+        <f t="shared" si="81"/>
+        <v>0.18017397607828944</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
+        <v>0.1100000000000001</v>
+      </c>
+      <c r="AB26" s="9">
+        <f t="shared" si="81"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="80"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
       <c r="AC26" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AD26" s="9">
+        <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD26" s="9">
-        <f t="shared" si="80"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AE26" s="9">
-        <f t="shared" si="80"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="81"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="80"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="81"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="80"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="81"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="80"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="81"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="80"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="81"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="80"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="81"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM26" t="s">
         <v>53</v>
       </c>
       <c r="AN26" s="5">
         <f>AN24+AN25</f>
-        <v>12201.639793848175</v>
+        <v>21502.879419934059</v>
       </c>
     </row>
     <row r="27" spans="2:152" x14ac:dyDescent="0.3">
@@ -4357,19 +4349,19 @@
         <v>43</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:F27" si="81">C10/C7</f>
+        <f t="shared" ref="C27:F27" si="82">C10/C7</f>
         <v>0.39033352176370828</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.36973278520041114</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.34927817280758455</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.3126912691269127</v>
       </c>
       <c r="G27" s="9">
@@ -4377,115 +4369,115 @@
         <v>0.28830014809939108</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:L27" si="82">H10/H7</f>
+        <f t="shared" ref="H27:L27" si="83">H10/H7</f>
         <v>0.27005466095435077</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.24679444811632517</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.20057405281285878</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.18432063422153711</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.21473390657680688</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" ref="M27:N27" si="83">M10/M7</f>
+        <f t="shared" ref="M27:N27" si="84">M10/M7</f>
         <v>0.21718039413845378</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0.2275027284452823</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" ref="O27:R27" si="84">O10/O7</f>
+        <f t="shared" ref="O27:R27" si="85">O10/O7</f>
         <v>0.22974537037037038</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.23435148295706063</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="84"/>
-        <v>0.22999999999999998</v>
+        <f t="shared" si="85"/>
+        <v>0.22624398706726598</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="84"/>
-        <v>0.22999999999999998</v>
+        <f t="shared" si="85"/>
+        <v>0.23</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" ref="T27:AJ27" si="85">T10/T7</f>
+        <f t="shared" ref="T27:AJ27" si="86">T10/T7</f>
         <v>0.36920943134535367</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.36825988550126482</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.39251563074659801</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.35050493589016224</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.2470382198413516</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.21145982688120654</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="85"/>
-        <v>0.23101857592529773</v>
+        <f t="shared" si="86"/>
+        <v>0.22997647194752407</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="85"/>
-        <v>0.22</v>
+        <f t="shared" si="86"/>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.21</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="85"/>
-        <v>0.19999999999999998</v>
+        <f t="shared" si="86"/>
+        <v>0.2</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.2</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.2</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.2</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.2</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.2</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.2</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.2</v>
       </c>
       <c r="AM27" t="s">
@@ -4493,7 +4485,7 @@
       </c>
       <c r="AN27" s="4">
         <f>AN26/AJ18</f>
-        <v>11.022258169691215</v>
+        <v>18.359698958277029</v>
       </c>
     </row>
     <row r="28" spans="2:152" x14ac:dyDescent="0.3">
@@ -4505,131 +4497,131 @@
         <v>0.19898247597512719</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" ref="D28:N28" si="86">D11/D7</f>
+        <f t="shared" ref="D28:N28" si="87">D11/D7</f>
         <v>0.20323741007194243</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.17905623787976727</v>
       </c>
       <c r="F28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.1450945094509451</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.13806154352476552</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.13872063820357514</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.12994051553205552</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.11928817451205512</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.1102180136533803</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.12746920752963048</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.12501263264274887</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.12719515824982636</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28:R28" si="87">O11/O7</f>
+        <f t="shared" ref="O28:R28" si="88">O11/O7</f>
         <v>0.13069058641975309</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.13315626383355467</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="87"/>
-        <v>0.13</v>
+        <f t="shared" si="88"/>
+        <v>0.12727702862550275</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="87"/>
-        <v>0.13</v>
-      </c>
-      <c r="T28" s="9">
-        <f t="shared" ref="T28:AJ28" si="88">T11/T7</f>
-        <v>0.16130374479889042</v>
-      </c>
-      <c r="U28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.23818399680468647</v>
-      </c>
-      <c r="V28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.2363001103346819</v>
-      </c>
-      <c r="W28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.17769204584137072</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.13049002438103086</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.12259040943125696</v>
-      </c>
-      <c r="Z28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.13093754537437099</v>
-      </c>
-      <c r="AA28" s="9">
         <f t="shared" si="88"/>
         <v>0.13</v>
       </c>
+      <c r="T28" s="9">
+        <f t="shared" ref="T28:AJ28" si="89">T11/T7</f>
+        <v>0.16130374479889042</v>
+      </c>
+      <c r="U28" s="9">
+        <f t="shared" si="89"/>
+        <v>0.23818399680468647</v>
+      </c>
+      <c r="V28" s="9">
+        <f t="shared" si="89"/>
+        <v>0.2363001103346819</v>
+      </c>
+      <c r="W28" s="9">
+        <f t="shared" si="89"/>
+        <v>0.17769204584137072</v>
+      </c>
+      <c r="X28" s="9">
+        <f t="shared" si="89"/>
+        <v>0.13049002438103086</v>
+      </c>
+      <c r="Y28" s="9">
+        <f t="shared" si="89"/>
+        <v>0.12259040943125696</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" si="89"/>
+        <v>0.13017393953080442</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" si="89"/>
+        <v>0.13</v>
+      </c>
       <c r="AB28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.13</v>
       </c>
       <c r="AM28" t="s">
@@ -4637,7 +4629,7 @@
       </c>
       <c r="AN28" s="4">
         <f>Main!D3</f>
-        <v>27.35</v>
+        <v>31.37</v>
       </c>
     </row>
     <row r="29" spans="2:152" x14ac:dyDescent="0.3">
@@ -4653,112 +4645,112 @@
         <v>-9.3772893772893773E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:L29" si="89">H12/D12-1</f>
+        <f t="shared" ref="H29:L29" si="90">H12/D12-1</f>
         <v>4.2925278219395846E-2</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-1.3470681458003231E-2</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.16445623342175053</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.17380759902991105</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.10518292682926833</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" ref="M29" si="90">M12/I12-1</f>
+        <f t="shared" ref="M29" si="91">M12/I12-1</f>
         <v>0.19598393574297202</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" ref="N29" si="91">N12/J12-1</f>
+        <f t="shared" ref="N29" si="92">N12/J12-1</f>
         <v>0.22171602126044054</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29" si="92">O12/K12-1</f>
+        <f t="shared" ref="O29" si="93">O12/K12-1</f>
         <v>7.713498622589543E-2</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29" si="93">P12/L12-1</f>
+        <f t="shared" ref="P29" si="94">P12/L12-1</f>
         <v>0.14068965517241394</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" ref="Q29" si="94">Q12/M12-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="Q29" si="95">Q12/M12-1</f>
+        <v>0.26527871054398933</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" ref="R29" si="95">R12/N12-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="R29" si="96">R12/N12-1</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T29" s="9"/>
       <c r="U29" s="9">
-        <f t="shared" ref="U29:AJ29" si="96">U12/T12-1</f>
+        <f t="shared" ref="U29:AJ29" si="97">U12/T12-1</f>
         <v>0.55876559422193028</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.0998315080033696</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>6.21865596790383E-3</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.8939393939393812E-2</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.1739385638818236</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" si="96"/>
-        <v>0.10926333333333327</v>
+        <f t="shared" si="97"/>
+        <v>0.19895000000000018</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM29" s="1" t="s">
@@ -4766,7 +4758,7 @@
       </c>
       <c r="AN29" s="10">
         <f>AN27/AN28-1</f>
-        <v>-0.59699238867673809</v>
+        <v>-0.41473704308967074</v>
       </c>
     </row>
     <row r="30" spans="2:152" x14ac:dyDescent="0.3">
@@ -4774,19 +4766,19 @@
         <v>47</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:F30" si="97">C15/C7</f>
+        <f t="shared" ref="C30:F30" si="98">C15/C7</f>
         <v>-0.30977953646127743</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-0.24640287769784183</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-0.16052574876104275</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-7.0027002700270194E-2</v>
       </c>
       <c r="G30" s="9">
@@ -4794,116 +4786,116 @@
         <v>-5.9568866216883121E-2</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30:L30" si="98">H15/H7</f>
+        <f t="shared" ref="H30:L30" si="99">H15/H7</f>
         <v>-7.2832028364603438E-2</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>-0.35294117647058837</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>5.878300803673956E-2</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.10372164721427003</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1.7778294213339478E-2</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" ref="M30:N30" si="99">M15/M7</f>
+        <f t="shared" ref="M30:N30" si="100">M15/M7</f>
         <v>6.4578069732187951E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>5.9331282865363585E-2</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="100">O15/O7</f>
+        <f t="shared" ref="O30:R30" si="101">O15/O7</f>
         <v>7.6871141975308574E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>9.9424524125719407E-2</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="100"/>
-        <v>0.11524298701507116</v>
+        <f t="shared" si="101"/>
+        <v>0.11726204558000163</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="100"/>
-        <v>0.11080942919550514</v>
+        <f t="shared" si="101"/>
+        <v>0.10439332516262838</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" ref="T30:AJ30" si="101">T15/T7</f>
+        <f t="shared" ref="T30:AJ30" si="102">T15/T7</f>
         <v>-0.33245492371705948</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-0.43749167887098922</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-0.44253401986024271</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-0.18092590491319635</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-0.10346485354211726</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>6.1919175827093692E-2</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.10143670670816879</v>
+        <f t="shared" si="102"/>
+        <v>0.10064807180257429</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.13304191206687369</v>
+        <f t="shared" si="102"/>
+        <v>0.14576266372447533</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.15149773244699249</v>
+        <f t="shared" si="102"/>
+        <v>0.18597434729712309</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.16840882295239626</v>
+        <f t="shared" si="102"/>
+        <v>0.21535801605042518</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.17329152443745305</v>
+        <f t="shared" si="102"/>
+        <v>0.22737945946944735</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.17552633048576699</v>
+        <f t="shared" si="102"/>
+        <v>0.2352813009273359</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.17644110476177166</v>
+        <f t="shared" si="102"/>
+        <v>0.24055736704134223</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.17730042793387538</v>
+        <f t="shared" si="102"/>
+        <v>0.24265012229082866</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.17809910678304636</v>
+        <f t="shared" si="102"/>
+        <v>0.24468678005349079</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.17883151299236333</v>
+        <f t="shared" si="102"/>
+        <v>0.24666444456125028</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.17949154659318861</v>
+        <f t="shared" si="102"/>
+        <v>0.24857999597781025</v>
       </c>
       <c r="AM30" t="s">
         <v>57</v>
@@ -4917,19 +4909,19 @@
         <v>34</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="102">C16/C15</f>
+        <f t="shared" ref="C31:F31" si="103">C16/C15</f>
         <v>-7.2992700729927031E-3</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-1.0427528675703854E-3</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>2.6845637583892638E-3</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-8.2262210796914981E-2</v>
       </c>
       <c r="G31" s="9">
@@ -4937,115 +4929,115 @@
         <v>4.4198895027624467E-2</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:L31" si="103">H16/H15</f>
+        <f t="shared" ref="H31:L31" si="104">H16/H15</f>
         <v>3.6511156186612527E-2</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>7.4906367041198472E-4</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>6.2499999999999813E-2</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>6.5817409766454324E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-0.13725490196078471</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" ref="M31:N31" si="104">M16/M15</f>
+        <f t="shared" ref="M31:N31" si="105">M16/M15</f>
         <v>4.8513302034428815E-2</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>-4.5568561872909736</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" ref="O31:R31" si="105">O16/O15</f>
+        <f t="shared" ref="O31:R31" si="106">O16/O15</f>
         <v>0.10915934755332506</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.13268032056990198</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="105"/>
-        <v>0.11999999999999998</v>
+        <f t="shared" si="106"/>
+        <v>6.186953597848014E-2</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.12000000000000001</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" ref="T31:AJ31" si="106">T16/T15</f>
+        <f t="shared" ref="T31:AJ31" si="107">T16/T15</f>
         <v>4.1718815185648754E-4</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.31801582471089468</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>-5.8175773945564101E-3</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>-1.2229539040451558E-2</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>1.3275804845668793E-3</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>-1.1376500857632921</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" si="106"/>
-        <v>0.12120903800818253</v>
+        <f t="shared" si="107"/>
+        <v>0.10312713611103877</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15</v>
       </c>
     </row>
@@ -5058,132 +5050,132 @@
         <v>-0.31204070096099479</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" ref="D32:AJ32" si="107">D17/D7</f>
+        <f t="shared" ref="D32:AJ32" si="108">D17/D7</f>
         <v>-0.24665981500513884</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-0.16009480715363056</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-7.5787578757875951E-2</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-5.6935988152048499E-2</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-7.017284680159562E-2</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-0.35267680105750182</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>5.5109070034443347E-2</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>9.68949570579168E-2</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>2.0218452242621376E-2</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>6.1445174330469907E-2</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.32969540629030653</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>6.8479938271604868E-2</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>8.6232846392209003E-2</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.10141382857326263</v>
+        <f t="shared" si="108"/>
+        <v>0.11000709723207955</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="107"/>
-        <v>9.7512297692044531E-2</v>
+        <f t="shared" si="108"/>
+        <v>9.1866126143112972E-2</v>
       </c>
       <c r="T32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-0.33231622746185835</v>
       </c>
       <c r="U32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-0.29836240181067769</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-0.44510849577050388</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-0.18313854533076129</v>
       </c>
       <c r="X32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>-0.10332749562171618</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.13236153151717919</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" si="107"/>
-        <v>8.9141661069353506E-2</v>
+        <f t="shared" si="108"/>
+        <v>9.026852440247661E-2</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.11308562525684264</v>
+        <f t="shared" si="108"/>
+        <v>0.12389826416580403</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.12877307257994361</v>
+        <f t="shared" si="108"/>
+        <v>0.15807819520255462</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.14314749950953681</v>
+        <f t="shared" si="108"/>
+        <v>0.1830543136428614</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.1472977957718351</v>
+        <f t="shared" si="108"/>
+        <v>0.19327254054903029</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.14919738091290194</v>
+        <f t="shared" si="108"/>
+        <v>0.1999891057882355</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.14997493904750592</v>
+        <f t="shared" si="108"/>
+        <v>0.20447376198514092</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.15070536374379409</v>
+        <f t="shared" si="108"/>
+        <v>0.20625260394720438</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.1513842407655894</v>
+        <f t="shared" si="108"/>
+        <v>0.20798376304546715</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.15200678604350884</v>
+        <f t="shared" si="108"/>
+        <v>0.20966477787706275</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="107"/>
-        <v>0.15256781460421032</v>
+        <f t="shared" si="108"/>
+        <v>0.2112929965811387</v>
       </c>
     </row>
   </sheetData>
